--- a/SimonCani_glyphs.xlsx
+++ b/SimonCani_glyphs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12870" windowHeight="12765"/>
+    <workbookView windowWidth="12915" windowHeight="12765"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4184,7 +4184,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4207,13 +4207,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -4687,28 +4680,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4717,131 +4713,129 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5216,7 +5210,7 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
@@ -5233,7 +5227,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
@@ -5250,7 +5244,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
@@ -5267,7 +5261,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B5" t="s">
@@ -5284,7 +5278,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B6" t="s">
@@ -5301,7 +5295,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B7" t="s">
@@ -5318,7 +5312,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B8" t="s">
@@ -5335,7 +5329,7 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B9" t="s">
@@ -5352,7 +5346,7 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B10" t="s">
@@ -5369,7 +5363,7 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B11" t="s">
@@ -5386,7 +5380,7 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B12" t="s">
@@ -5403,7 +5397,7 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B13" t="s">
@@ -5420,7 +5414,7 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B14" t="s">
@@ -5437,7 +5431,7 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B15" t="s">
@@ -5454,7 +5448,7 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B16" t="s">
@@ -5471,7 +5465,7 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B17" t="s">
@@ -5488,7 +5482,7 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B18" t="s">
@@ -5505,7 +5499,7 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B19" t="s">
@@ -5522,7 +5516,7 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B20" t="s">
@@ -5539,7 +5533,7 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B21" t="s">
@@ -5556,7 +5550,7 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B22" t="s">
@@ -5573,7 +5567,7 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B23" t="s">
@@ -5590,7 +5584,7 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B24" t="s">
@@ -5607,7 +5601,7 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B25" t="s">
@@ -5624,7 +5618,7 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B26" t="s">
@@ -5641,7 +5635,7 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="1" t="s">
         <v>106</v>
       </c>
       <c r="B27" t="s">
@@ -5658,7 +5652,7 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B28" t="s">
@@ -5675,7 +5669,7 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="1" t="s">
         <v>114</v>
       </c>
       <c r="B29" t="s">
@@ -5692,7 +5686,7 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="1" t="s">
         <v>118</v>
       </c>
       <c r="B30" t="s">
@@ -5709,7 +5703,7 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="1" t="s">
         <v>122</v>
       </c>
       <c r="B31" t="s">
@@ -5726,7 +5720,7 @@
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="1" t="s">
         <v>126</v>
       </c>
       <c r="B32" t="s">
@@ -5743,7 +5737,7 @@
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="1" t="s">
         <v>130</v>
       </c>
       <c r="B33" t="s">
@@ -5760,7 +5754,7 @@
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="1" t="s">
         <v>134</v>
       </c>
       <c r="B34" t="s">
@@ -5777,7 +5771,7 @@
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="1" t="s">
         <v>138</v>
       </c>
       <c r="B35" t="s">
@@ -5794,7 +5788,7 @@
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B36" t="s">
@@ -5811,7 +5805,7 @@
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="1" t="s">
         <v>146</v>
       </c>
       <c r="B37" t="s">
@@ -5828,7 +5822,7 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="1" t="s">
         <v>150</v>
       </c>
       <c r="B38" t="s">
@@ -5845,7 +5839,7 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="1" t="s">
         <v>154</v>
       </c>
       <c r="B39" t="s">
@@ -5862,7 +5856,7 @@
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="1" t="s">
         <v>158</v>
       </c>
       <c r="B40" t="s">
@@ -5879,7 +5873,7 @@
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B41" t="s">
@@ -5896,7 +5890,7 @@
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="1" t="s">
         <v>166</v>
       </c>
       <c r="B42" t="s">
@@ -5913,7 +5907,7 @@
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="1" t="s">
         <v>170</v>
       </c>
       <c r="B43" t="s">
@@ -5930,7 +5924,7 @@
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B44" t="s">
@@ -5947,7 +5941,7 @@
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B45" t="s">
@@ -5964,7 +5958,7 @@
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="1" t="s">
         <v>182</v>
       </c>
       <c r="B46" t="s">
@@ -5981,7 +5975,7 @@
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="1" t="s">
         <v>186</v>
       </c>
       <c r="B47" t="s">
@@ -5998,7 +5992,7 @@
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="1" t="s">
         <v>190</v>
       </c>
       <c r="B48" t="s">
@@ -6015,7 +6009,7 @@
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="1" t="s">
         <v>194</v>
       </c>
       <c r="B49" t="s">
@@ -6032,7 +6026,7 @@
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="1" t="s">
         <v>198</v>
       </c>
       <c r="B50" t="s">
@@ -6049,7 +6043,7 @@
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="1" t="s">
         <v>202</v>
       </c>
       <c r="B51" t="s">
@@ -6066,7 +6060,7 @@
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="1" t="s">
         <v>206</v>
       </c>
       <c r="B52" t="s">
@@ -6083,7 +6077,7 @@
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="1" t="s">
         <v>210</v>
       </c>
       <c r="B53" t="s">
@@ -6100,7 +6094,7 @@
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="1" t="s">
         <v>214</v>
       </c>
       <c r="B54" t="s">
@@ -6117,7 +6111,7 @@
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="1" t="s">
         <v>218</v>
       </c>
       <c r="B55" t="s">
@@ -6134,7 +6128,7 @@
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="1" t="s">
         <v>222</v>
       </c>
       <c r="B56" t="s">
@@ -6151,7 +6145,7 @@
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="1" t="s">
         <v>226</v>
       </c>
       <c r="B57" t="s">
@@ -6168,7 +6162,7 @@
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="1" t="s">
         <v>230</v>
       </c>
       <c r="B58" t="s">
@@ -6185,7 +6179,7 @@
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="1" t="s">
         <v>234</v>
       </c>
       <c r="B59" t="s">
@@ -6202,7 +6196,7 @@
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="1" t="s">
         <v>238</v>
       </c>
       <c r="B60" t="s">
@@ -6219,7 +6213,7 @@
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="1" t="s">
         <v>242</v>
       </c>
       <c r="B61" t="s">
@@ -6236,7 +6230,7 @@
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="1" t="s">
         <v>246</v>
       </c>
       <c r="B62" t="s">
@@ -6253,7 +6247,7 @@
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="1" t="s">
         <v>250</v>
       </c>
       <c r="B63" t="s">
@@ -6270,7 +6264,7 @@
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="1" t="s">
         <v>254</v>
       </c>
       <c r="B64" t="s">
@@ -6287,7 +6281,7 @@
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="1" t="s">
         <v>258</v>
       </c>
       <c r="B65" t="s">
@@ -6304,7 +6298,7 @@
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="1" t="s">
         <v>262</v>
       </c>
       <c r="B66" t="s">
@@ -6321,7 +6315,7 @@
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="1" t="s">
         <v>266</v>
       </c>
       <c r="B67" t="s">
@@ -6338,7 +6332,7 @@
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="1" t="s">
         <v>270</v>
       </c>
       <c r="B68" t="s">
@@ -6355,7 +6349,7 @@
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="1" t="s">
         <v>274</v>
       </c>
       <c r="B69" t="s">
@@ -6372,7 +6366,7 @@
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="1" t="s">
         <v>278</v>
       </c>
       <c r="B70" t="s">
@@ -6389,7 +6383,7 @@
       </c>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="1" t="s">
         <v>282</v>
       </c>
       <c r="B71" t="s">
@@ -6406,7 +6400,7 @@
       </c>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="1" t="s">
         <v>286</v>
       </c>
       <c r="B72" t="s">
@@ -6423,7 +6417,7 @@
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="1" t="s">
         <v>290</v>
       </c>
       <c r="B73" t="s">
@@ -6440,7 +6434,7 @@
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="1" t="s">
         <v>294</v>
       </c>
       <c r="B74" t="s">
@@ -6457,7 +6451,7 @@
       </c>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="1" t="s">
         <v>298</v>
       </c>
       <c r="B75" t="s">
@@ -6474,7 +6468,7 @@
       </c>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="1" t="s">
         <v>302</v>
       </c>
       <c r="B76" t="s">
@@ -6491,7 +6485,7 @@
       </c>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="1" t="s">
         <v>306</v>
       </c>
       <c r="B77" t="s">
@@ -6508,7 +6502,7 @@
       </c>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="1" t="s">
         <v>310</v>
       </c>
       <c r="B78" t="s">
@@ -6525,7 +6519,7 @@
       </c>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="1" t="s">
         <v>314</v>
       </c>
       <c r="B79" t="s">
@@ -6542,7 +6536,7 @@
       </c>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="1" t="s">
         <v>318</v>
       </c>
       <c r="B80" t="s">
@@ -6559,7 +6553,7 @@
       </c>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="1" t="s">
         <v>323</v>
       </c>
       <c r="B81" t="s">
@@ -6576,7 +6570,7 @@
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="1" t="s">
         <v>327</v>
       </c>
       <c r="B82" t="s">
@@ -6593,7 +6587,7 @@
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="1" t="s">
         <v>331</v>
       </c>
       <c r="B83" t="s">
@@ -6610,7 +6604,7 @@
       </c>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="1" t="s">
         <v>335</v>
       </c>
       <c r="B84" t="s">
@@ -6627,7 +6621,7 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="1" t="s">
         <v>339</v>
       </c>
       <c r="B85" t="s">
@@ -6644,7 +6638,7 @@
       </c>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="1" t="s">
         <v>343</v>
       </c>
       <c r="B86" t="s">
@@ -6661,7 +6655,7 @@
       </c>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="1" t="s">
         <v>347</v>
       </c>
       <c r="B87" t="s">
@@ -6678,7 +6672,7 @@
       </c>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="1" t="s">
         <v>351</v>
       </c>
       <c r="B88" t="s">
@@ -6695,7 +6689,7 @@
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="1" t="s">
         <v>355</v>
       </c>
       <c r="B89" t="s">
@@ -6712,7 +6706,7 @@
       </c>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="1" t="s">
         <v>359</v>
       </c>
       <c r="B90" t="s">
@@ -6729,7 +6723,7 @@
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B91" t="s">
@@ -6746,7 +6740,7 @@
       </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="1" t="s">
         <v>366</v>
       </c>
       <c r="B92" t="s">
@@ -6763,7 +6757,7 @@
       </c>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="1" t="s">
         <v>370</v>
       </c>
       <c r="B93" t="s">
@@ -6780,7 +6774,7 @@
       </c>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="1" t="s">
         <v>374</v>
       </c>
       <c r="B94" t="s">
@@ -6797,7 +6791,7 @@
       </c>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="4" t="s">
+      <c r="A95" s="1" t="s">
         <v>378</v>
       </c>
       <c r="B95" t="s">
@@ -6814,7 +6808,7 @@
       </c>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="1" t="s">
         <v>382</v>
       </c>
       <c r="B96" t="s">
@@ -6831,7 +6825,7 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="1" t="s">
         <v>386</v>
       </c>
       <c r="B97" t="s">
@@ -6848,7 +6842,7 @@
       </c>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="1" t="s">
         <v>390</v>
       </c>
       <c r="B98" t="s">
@@ -6865,7 +6859,7 @@
       </c>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="1" t="s">
         <v>394</v>
       </c>
       <c r="B99" t="s">
@@ -6882,7 +6876,7 @@
       </c>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="1" t="s">
         <v>398</v>
       </c>
       <c r="B100" t="s">
@@ -6899,7 +6893,7 @@
       </c>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="4" t="s">
+      <c r="A101" s="1" t="s">
         <v>402</v>
       </c>
       <c r="B101" t="s">
@@ -6916,7 +6910,7 @@
       </c>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="1" t="s">
         <v>406</v>
       </c>
       <c r="B102" t="s">
@@ -6933,7 +6927,7 @@
       </c>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="4" t="s">
+      <c r="A103" s="1" t="s">
         <v>410</v>
       </c>
       <c r="B103" t="s">
@@ -6950,7 +6944,7 @@
       </c>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="4" t="s">
+      <c r="A104" s="1" t="s">
         <v>414</v>
       </c>
       <c r="B104" t="s">
@@ -6967,7 +6961,7 @@
       </c>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="4" t="s">
+      <c r="A105" s="1" t="s">
         <v>418</v>
       </c>
       <c r="B105" t="s">
@@ -6984,7 +6978,7 @@
       </c>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="4" t="s">
+      <c r="A106" s="1" t="s">
         <v>422</v>
       </c>
       <c r="B106" t="s">
@@ -7001,7 +6995,7 @@
       </c>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="1" t="s">
         <v>426</v>
       </c>
       <c r="B107" t="s">
@@ -7018,7 +7012,7 @@
       </c>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="1" t="s">
         <v>430</v>
       </c>
       <c r="B108" t="s">
@@ -7035,7 +7029,7 @@
       </c>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="1" t="s">
         <v>434</v>
       </c>
       <c r="B109" t="s">
@@ -7052,7 +7046,7 @@
       </c>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="1" t="s">
         <v>438</v>
       </c>
       <c r="B110" t="s">
@@ -7069,7 +7063,7 @@
       </c>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="1" t="s">
         <v>442</v>
       </c>
       <c r="B111" t="s">
@@ -7086,7 +7080,7 @@
       </c>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="4" t="s">
+      <c r="A112" s="1" t="s">
         <v>446</v>
       </c>
       <c r="B112" t="s">
@@ -7103,7 +7097,7 @@
       </c>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="1" t="s">
         <v>450</v>
       </c>
       <c r="B113" t="s">
@@ -7120,7 +7114,7 @@
       </c>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="4" t="s">
+      <c r="A114" s="1" t="s">
         <v>454</v>
       </c>
       <c r="B114" t="s">
@@ -7137,7 +7131,7 @@
       </c>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="1" t="s">
         <v>458</v>
       </c>
       <c r="B115" t="s">
@@ -7154,7 +7148,7 @@
       </c>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="1" t="s">
         <v>463</v>
       </c>
       <c r="B116" t="s">
@@ -7171,7 +7165,7 @@
       </c>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="1" t="s">
         <v>467</v>
       </c>
       <c r="B117" t="s">
@@ -7188,7 +7182,7 @@
       </c>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="4" t="s">
+      <c r="A118" s="1" t="s">
         <v>471</v>
       </c>
       <c r="B118" t="s">
@@ -7205,7 +7199,7 @@
       </c>
     </row>
     <row r="119" spans="1:5">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="1" t="s">
         <v>475</v>
       </c>
       <c r="B119" t="s">
@@ -7222,7 +7216,7 @@
       </c>
     </row>
     <row r="120" spans="1:5">
-      <c r="A120" s="4" t="s">
+      <c r="A120" s="1" t="s">
         <v>479</v>
       </c>
       <c r="B120" t="s">
@@ -7239,7 +7233,7 @@
       </c>
     </row>
     <row r="121" spans="1:5">
-      <c r="A121" s="4" t="s">
+      <c r="A121" s="1" t="s">
         <v>484</v>
       </c>
       <c r="B121" t="s">
@@ -7256,7 +7250,7 @@
       </c>
     </row>
     <row r="122" spans="1:5">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="1" t="s">
         <v>488</v>
       </c>
       <c r="B122" t="s">
@@ -7273,7 +7267,7 @@
       </c>
     </row>
     <row r="123" spans="1:5">
-      <c r="A123" s="4" t="s">
+      <c r="A123" s="1" t="s">
         <v>492</v>
       </c>
       <c r="B123" t="s">
@@ -7290,7 +7284,7 @@
       </c>
     </row>
     <row r="124" spans="1:5">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="1" t="s">
         <v>497</v>
       </c>
       <c r="B124" t="s">
@@ -7307,7 +7301,7 @@
       </c>
     </row>
     <row r="125" spans="1:5">
-      <c r="A125" s="4" t="s">
+      <c r="A125" s="1" t="s">
         <v>501</v>
       </c>
       <c r="B125" t="s">
@@ -7324,7 +7318,7 @@
       </c>
     </row>
     <row r="126" spans="1:5">
-      <c r="A126" s="4" t="s">
+      <c r="A126" s="1" t="s">
         <v>505</v>
       </c>
       <c r="B126" t="s">
@@ -7341,7 +7335,7 @@
       </c>
     </row>
     <row r="127" spans="1:5">
-      <c r="A127" s="4" t="s">
+      <c r="A127" s="1" t="s">
         <v>509</v>
       </c>
       <c r="B127" t="s">
@@ -7358,7 +7352,7 @@
       </c>
     </row>
     <row r="128" spans="1:5">
-      <c r="A128" s="4" t="s">
+      <c r="A128" s="1" t="s">
         <v>513</v>
       </c>
       <c r="B128" t="s">
@@ -7375,7 +7369,7 @@
       </c>
     </row>
     <row r="129" spans="1:5">
-      <c r="A129" s="4" t="s">
+      <c r="A129" s="1" t="s">
         <v>517</v>
       </c>
       <c r="B129" t="s">
@@ -7392,7 +7386,7 @@
       </c>
     </row>
     <row r="130" spans="1:5">
-      <c r="A130" s="4" t="s">
+      <c r="A130" s="1" t="s">
         <v>521</v>
       </c>
       <c r="B130" t="s">
@@ -7409,7 +7403,7 @@
       </c>
     </row>
     <row r="131" spans="1:5">
-      <c r="A131" s="4" t="s">
+      <c r="A131" s="1" t="s">
         <v>525</v>
       </c>
       <c r="B131" t="s">
@@ -7426,7 +7420,7 @@
       </c>
     </row>
     <row r="132" spans="1:5">
-      <c r="A132" s="4" t="s">
+      <c r="A132" s="1" t="s">
         <v>529</v>
       </c>
       <c r="B132" t="s">
@@ -7443,7 +7437,7 @@
       </c>
     </row>
     <row r="133" spans="1:5">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="1" t="s">
         <v>533</v>
       </c>
       <c r="B133" t="s">
@@ -7460,7 +7454,7 @@
       </c>
     </row>
     <row r="134" spans="1:5">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="1" t="s">
         <v>537</v>
       </c>
       <c r="B134" t="s">
@@ -7477,7 +7471,7 @@
       </c>
     </row>
     <row r="135" spans="1:5">
-      <c r="A135" s="4" t="s">
+      <c r="A135" s="1" t="s">
         <v>541</v>
       </c>
       <c r="B135" t="s">
@@ -7494,7 +7488,7 @@
       </c>
     </row>
     <row r="136" spans="1:5">
-      <c r="A136" s="4" t="s">
+      <c r="A136" s="1" t="s">
         <v>545</v>
       </c>
       <c r="B136" t="s">
@@ -7511,7 +7505,7 @@
       </c>
     </row>
     <row r="137" spans="1:5">
-      <c r="A137" s="4" t="s">
+      <c r="A137" s="1" t="s">
         <v>549</v>
       </c>
       <c r="B137" t="s">
@@ -7528,7 +7522,7 @@
       </c>
     </row>
     <row r="138" spans="1:5">
-      <c r="A138" s="4" t="s">
+      <c r="A138" s="1" t="s">
         <v>553</v>
       </c>
       <c r="B138" t="s">
@@ -7545,7 +7539,7 @@
       </c>
     </row>
     <row r="139" spans="1:5">
-      <c r="A139" s="4" t="s">
+      <c r="A139" s="1" t="s">
         <v>557</v>
       </c>
       <c r="B139" t="s">
@@ -7562,7 +7556,7 @@
       </c>
     </row>
     <row r="140" spans="1:5">
-      <c r="A140" s="4" t="s">
+      <c r="A140" s="1" t="s">
         <v>561</v>
       </c>
       <c r="B140" t="s">
@@ -7579,7 +7573,7 @@
       </c>
     </row>
     <row r="141" spans="1:5">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="1" t="s">
         <v>565</v>
       </c>
       <c r="B141" t="s">
@@ -7596,7 +7590,7 @@
       </c>
     </row>
     <row r="142" spans="1:5">
-      <c r="A142" s="4" t="s">
+      <c r="A142" s="1" t="s">
         <v>569</v>
       </c>
       <c r="B142" t="s">
@@ -7613,7 +7607,7 @@
       </c>
     </row>
     <row r="143" spans="1:5">
-      <c r="A143" s="4" t="s">
+      <c r="A143" s="1" t="s">
         <v>573</v>
       </c>
       <c r="B143" t="s">
@@ -7630,7 +7624,7 @@
       </c>
     </row>
     <row r="144" spans="1:5">
-      <c r="A144" s="4" t="s">
+      <c r="A144" s="1" t="s">
         <v>577</v>
       </c>
       <c r="B144" t="s">
@@ -7647,7 +7641,7 @@
       </c>
     </row>
     <row r="145" spans="1:5">
-      <c r="A145" s="4" t="s">
+      <c r="A145" s="1" t="s">
         <v>581</v>
       </c>
       <c r="B145" t="s">
@@ -7664,7 +7658,7 @@
       </c>
     </row>
     <row r="146" spans="1:5">
-      <c r="A146" s="4" t="s">
+      <c r="A146" s="1" t="s">
         <v>585</v>
       </c>
       <c r="B146" t="s">
@@ -7681,7 +7675,7 @@
       </c>
     </row>
     <row r="147" spans="1:5">
-      <c r="A147" s="4" t="s">
+      <c r="A147" s="1" t="s">
         <v>589</v>
       </c>
       <c r="B147" t="s">
@@ -7698,7 +7692,7 @@
       </c>
     </row>
     <row r="148" spans="1:5">
-      <c r="A148" s="4" t="s">
+      <c r="A148" s="1" t="s">
         <v>593</v>
       </c>
       <c r="B148" t="s">
@@ -7715,7 +7709,7 @@
       </c>
     </row>
     <row r="149" spans="1:5">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="1" t="s">
         <v>597</v>
       </c>
       <c r="B149" t="s">
@@ -7732,7 +7726,7 @@
       </c>
     </row>
     <row r="150" spans="1:5">
-      <c r="A150" s="4" t="s">
+      <c r="A150" s="1" t="s">
         <v>601</v>
       </c>
       <c r="B150" t="s">
@@ -7749,7 +7743,7 @@
       </c>
     </row>
     <row r="151" spans="1:5">
-      <c r="A151" s="4" t="s">
+      <c r="A151" s="1" t="s">
         <v>605</v>
       </c>
       <c r="B151" t="s">
@@ -7766,7 +7760,7 @@
       </c>
     </row>
     <row r="152" spans="1:5">
-      <c r="A152" s="4" t="s">
+      <c r="A152" s="1" t="s">
         <v>609</v>
       </c>
       <c r="B152" t="s">
@@ -7783,7 +7777,7 @@
       </c>
     </row>
     <row r="153" spans="1:5">
-      <c r="A153" s="4" t="s">
+      <c r="A153" s="1" t="s">
         <v>613</v>
       </c>
       <c r="B153" t="s">
@@ -7800,7 +7794,7 @@
       </c>
     </row>
     <row r="154" spans="1:5">
-      <c r="A154" s="4" t="s">
+      <c r="A154" s="1" t="s">
         <v>617</v>
       </c>
       <c r="B154" t="s">
@@ -7817,7 +7811,7 @@
       </c>
     </row>
     <row r="155" spans="1:5">
-      <c r="A155" s="4" t="s">
+      <c r="A155" s="1" t="s">
         <v>621</v>
       </c>
       <c r="B155" t="s">
@@ -7834,7 +7828,7 @@
       </c>
     </row>
     <row r="156" spans="1:5">
-      <c r="A156" s="4" t="s">
+      <c r="A156" s="1" t="s">
         <v>625</v>
       </c>
       <c r="B156" t="s">
@@ -7851,7 +7845,7 @@
       </c>
     </row>
     <row r="157" spans="1:5">
-      <c r="A157" s="4" t="s">
+      <c r="A157" s="1" t="s">
         <v>629</v>
       </c>
       <c r="B157" t="s">
@@ -7868,7 +7862,7 @@
       </c>
     </row>
     <row r="158" spans="1:5">
-      <c r="A158" s="4" t="s">
+      <c r="A158" s="1" t="s">
         <v>633</v>
       </c>
       <c r="B158" t="s">
@@ -7885,7 +7879,7 @@
       </c>
     </row>
     <row r="159" spans="1:5">
-      <c r="A159" s="4" t="s">
+      <c r="A159" s="1" t="s">
         <v>637</v>
       </c>
       <c r="B159" t="s">
@@ -7902,7 +7896,7 @@
       </c>
     </row>
     <row r="160" spans="1:5">
-      <c r="A160" s="4" t="s">
+      <c r="A160" s="1" t="s">
         <v>641</v>
       </c>
       <c r="B160" t="s">
@@ -7919,7 +7913,7 @@
       </c>
     </row>
     <row r="161" spans="1:5">
-      <c r="A161" s="4" t="s">
+      <c r="A161" s="1" t="s">
         <v>645</v>
       </c>
       <c r="B161" t="s">
@@ -7936,7 +7930,7 @@
       </c>
     </row>
     <row r="162" spans="1:5">
-      <c r="A162" s="4" t="s">
+      <c r="A162" s="1" t="s">
         <v>649</v>
       </c>
       <c r="B162" t="s">
@@ -7953,7 +7947,7 @@
       </c>
     </row>
     <row r="163" spans="1:5">
-      <c r="A163" s="4" t="s">
+      <c r="A163" s="1" t="s">
         <v>653</v>
       </c>
       <c r="B163" t="s">
@@ -7970,7 +7964,7 @@
       </c>
     </row>
     <row r="164" spans="1:5">
-      <c r="A164" s="4" t="s">
+      <c r="A164" s="1" t="s">
         <v>657</v>
       </c>
       <c r="B164" t="s">
@@ -7987,7 +7981,7 @@
       </c>
     </row>
     <row r="165" spans="1:5">
-      <c r="A165" s="4" t="s">
+      <c r="A165" s="1" t="s">
         <v>661</v>
       </c>
       <c r="B165" t="s">
@@ -8004,7 +7998,7 @@
       </c>
     </row>
     <row r="166" spans="1:5">
-      <c r="A166" s="4" t="s">
+      <c r="A166" s="1" t="s">
         <v>665</v>
       </c>
       <c r="B166" t="s">
@@ -8021,7 +8015,7 @@
       </c>
     </row>
     <row r="167" spans="1:5">
-      <c r="A167" s="4" t="s">
+      <c r="A167" s="1" t="s">
         <v>669</v>
       </c>
       <c r="B167" t="s">
@@ -8038,7 +8032,7 @@
       </c>
     </row>
     <row r="168" spans="1:5">
-      <c r="A168" s="4" t="s">
+      <c r="A168" s="1" t="s">
         <v>673</v>
       </c>
       <c r="B168" t="s">
@@ -8055,7 +8049,7 @@
       </c>
     </row>
     <row r="169" spans="1:5">
-      <c r="A169" s="4" t="s">
+      <c r="A169" s="1" t="s">
         <v>677</v>
       </c>
       <c r="B169" t="s">
@@ -8072,7 +8066,7 @@
       </c>
     </row>
     <row r="170" spans="1:5">
-      <c r="A170" s="4" t="s">
+      <c r="A170" s="1" t="s">
         <v>681</v>
       </c>
       <c r="B170" t="s">
@@ -8089,7 +8083,7 @@
       </c>
     </row>
     <row r="171" spans="1:5">
-      <c r="A171" s="4" t="s">
+      <c r="A171" s="1" t="s">
         <v>685</v>
       </c>
       <c r="B171" t="s">
@@ -8106,7 +8100,7 @@
       </c>
     </row>
     <row r="172" spans="1:5">
-      <c r="A172" s="4" t="s">
+      <c r="A172" s="1" t="s">
         <v>689</v>
       </c>
       <c r="B172" t="s">
@@ -8123,7 +8117,7 @@
       </c>
     </row>
     <row r="173" spans="1:5">
-      <c r="A173" s="4" t="s">
+      <c r="A173" s="1" t="s">
         <v>693</v>
       </c>
       <c r="B173" t="s">
@@ -8140,7 +8134,7 @@
       </c>
     </row>
     <row r="174" spans="1:5">
-      <c r="A174" s="4" t="s">
+      <c r="A174" s="1" t="s">
         <v>697</v>
       </c>
       <c r="B174" t="s">
@@ -8157,7 +8151,7 @@
       </c>
     </row>
     <row r="175" spans="1:5">
-      <c r="A175" s="4" t="s">
+      <c r="A175" s="1" t="s">
         <v>701</v>
       </c>
       <c r="B175" t="s">
@@ -8174,7 +8168,7 @@
       </c>
     </row>
     <row r="176" spans="1:5">
-      <c r="A176" s="4" t="s">
+      <c r="A176" s="1" t="s">
         <v>705</v>
       </c>
       <c r="B176" t="s">
@@ -8191,7 +8185,7 @@
       </c>
     </row>
     <row r="177" spans="1:5">
-      <c r="A177" s="4" t="s">
+      <c r="A177" s="1" t="s">
         <v>709</v>
       </c>
       <c r="B177" t="s">
@@ -8208,7 +8202,7 @@
       </c>
     </row>
     <row r="178" spans="1:5">
-      <c r="A178" s="4" t="s">
+      <c r="A178" s="1" t="s">
         <v>713</v>
       </c>
       <c r="B178" t="s">
@@ -8225,7 +8219,7 @@
       </c>
     </row>
     <row r="179" spans="1:5">
-      <c r="A179" s="4" t="s">
+      <c r="A179" s="1" t="s">
         <v>717</v>
       </c>
       <c r="B179" t="s">
@@ -8242,7 +8236,7 @@
       </c>
     </row>
     <row r="180" spans="1:5">
-      <c r="A180" s="4" t="s">
+      <c r="A180" s="1" t="s">
         <v>721</v>
       </c>
       <c r="B180" t="s">
@@ -8259,7 +8253,7 @@
       </c>
     </row>
     <row r="181" spans="1:5">
-      <c r="A181" s="4" t="s">
+      <c r="A181" s="1" t="s">
         <v>725</v>
       </c>
       <c r="B181" t="s">
@@ -8276,7 +8270,7 @@
       </c>
     </row>
     <row r="182" spans="1:5">
-      <c r="A182" s="4" t="s">
+      <c r="A182" s="1" t="s">
         <v>729</v>
       </c>
       <c r="B182" t="s">
@@ -8293,7 +8287,7 @@
       </c>
     </row>
     <row r="183" spans="1:5">
-      <c r="A183" s="4" t="s">
+      <c r="A183" s="1" t="s">
         <v>733</v>
       </c>
       <c r="B183" t="s">
@@ -8310,7 +8304,7 @@
       </c>
     </row>
     <row r="184" spans="1:5">
-      <c r="A184" s="4" t="s">
+      <c r="A184" s="1" t="s">
         <v>737</v>
       </c>
       <c r="B184" t="s">
@@ -8327,7 +8321,7 @@
       </c>
     </row>
     <row r="185" spans="1:5">
-      <c r="A185" s="4" t="s">
+      <c r="A185" s="1" t="s">
         <v>741</v>
       </c>
       <c r="B185" t="s">
@@ -8344,7 +8338,7 @@
       </c>
     </row>
     <row r="186" spans="1:5">
-      <c r="A186" s="4" t="s">
+      <c r="A186" s="1" t="s">
         <v>745</v>
       </c>
       <c r="B186" t="s">
@@ -8361,7 +8355,7 @@
       </c>
     </row>
     <row r="187" spans="1:5">
-      <c r="A187" s="4" t="s">
+      <c r="A187" s="1" t="s">
         <v>750</v>
       </c>
       <c r="B187" t="s">
@@ -8378,7 +8372,7 @@
       </c>
     </row>
     <row r="188" spans="1:5">
-      <c r="A188" s="4" t="s">
+      <c r="A188" s="1" t="s">
         <v>754</v>
       </c>
       <c r="B188" t="s">
@@ -8395,7 +8389,7 @@
       </c>
     </row>
     <row r="189" spans="1:5">
-      <c r="A189" s="4" t="s">
+      <c r="A189" s="1" t="s">
         <v>758</v>
       </c>
       <c r="B189" t="s">
@@ -8412,7 +8406,7 @@
       </c>
     </row>
     <row r="190" spans="1:5">
-      <c r="A190" s="4" t="s">
+      <c r="A190" s="1" t="s">
         <v>762</v>
       </c>
       <c r="B190" t="s">
@@ -8429,7 +8423,7 @@
       </c>
     </row>
     <row r="191" spans="1:5">
-      <c r="A191" s="4" t="s">
+      <c r="A191" s="1" t="s">
         <v>766</v>
       </c>
       <c r="B191" t="s">
@@ -8446,7 +8440,7 @@
       </c>
     </row>
     <row r="192" spans="1:5">
-      <c r="A192" s="4" t="s">
+      <c r="A192" s="1" t="s">
         <v>770</v>
       </c>
       <c r="B192" t="s">
@@ -8463,7 +8457,7 @@
       </c>
     </row>
     <row r="193" spans="1:5">
-      <c r="A193" s="4" t="s">
+      <c r="A193" s="1" t="s">
         <v>774</v>
       </c>
       <c r="B193" t="s">
@@ -8480,7 +8474,7 @@
       </c>
     </row>
     <row r="194" spans="1:5">
-      <c r="A194" s="4" t="s">
+      <c r="A194" s="1" t="s">
         <v>778</v>
       </c>
       <c r="B194" t="s">
@@ -8497,7 +8491,7 @@
       </c>
     </row>
     <row r="195" spans="1:5">
-      <c r="A195" s="4" t="s">
+      <c r="A195" s="1" t="s">
         <v>782</v>
       </c>
       <c r="B195" t="s">
@@ -8514,7 +8508,7 @@
       </c>
     </row>
     <row r="196" spans="1:5">
-      <c r="A196" s="4" t="s">
+      <c r="A196" s="1" t="s">
         <v>786</v>
       </c>
       <c r="B196" t="s">
@@ -8531,7 +8525,7 @@
       </c>
     </row>
     <row r="197" spans="1:5">
-      <c r="A197" s="4" t="s">
+      <c r="A197" s="1" t="s">
         <v>790</v>
       </c>
       <c r="B197" t="s">
@@ -8548,7 +8542,7 @@
       </c>
     </row>
     <row r="198" spans="1:5">
-      <c r="A198" s="4" t="s">
+      <c r="A198" s="1" t="s">
         <v>794</v>
       </c>
       <c r="B198" t="s">
@@ -8565,7 +8559,7 @@
       </c>
     </row>
     <row r="199" spans="1:5">
-      <c r="A199" s="4" t="s">
+      <c r="A199" s="1" t="s">
         <v>799</v>
       </c>
       <c r="B199" t="s">
@@ -8582,7 +8576,7 @@
       </c>
     </row>
     <row r="200" spans="1:5">
-      <c r="A200" s="4" t="s">
+      <c r="A200" s="1" t="s">
         <v>803</v>
       </c>
       <c r="B200" t="s">
@@ -8599,7 +8593,7 @@
       </c>
     </row>
     <row r="201" spans="1:5">
-      <c r="A201" s="4" t="s">
+      <c r="A201" s="1" t="s">
         <v>807</v>
       </c>
       <c r="B201" t="s">
@@ -8616,7 +8610,7 @@
       </c>
     </row>
     <row r="202" spans="1:5">
-      <c r="A202" s="4" t="s">
+      <c r="A202" s="1" t="s">
         <v>811</v>
       </c>
       <c r="B202" t="s">
@@ -8633,7 +8627,7 @@
       </c>
     </row>
     <row r="203" spans="1:5">
-      <c r="A203" s="4" t="s">
+      <c r="A203" s="1" t="s">
         <v>815</v>
       </c>
       <c r="B203" t="s">
@@ -8650,7 +8644,7 @@
       </c>
     </row>
     <row r="204" spans="1:5">
-      <c r="A204" s="4" t="s">
+      <c r="A204" s="1" t="s">
         <v>819</v>
       </c>
       <c r="B204" t="s">
@@ -8667,7 +8661,7 @@
       </c>
     </row>
     <row r="205" spans="1:5">
-      <c r="A205" s="4" t="s">
+      <c r="A205" s="1" t="s">
         <v>823</v>
       </c>
       <c r="B205" t="s">
@@ -8684,7 +8678,7 @@
       </c>
     </row>
     <row r="206" spans="1:5">
-      <c r="A206" s="4" t="s">
+      <c r="A206" s="1" t="s">
         <v>827</v>
       </c>
       <c r="B206" t="s">
@@ -8701,7 +8695,7 @@
       </c>
     </row>
     <row r="207" spans="1:5">
-      <c r="A207" s="4" t="s">
+      <c r="A207" s="1" t="s">
         <v>831</v>
       </c>
       <c r="B207" t="s">
@@ -8718,7 +8712,7 @@
       </c>
     </row>
     <row r="208" spans="1:5">
-      <c r="A208" s="4" t="s">
+      <c r="A208" s="1" t="s">
         <v>835</v>
       </c>
       <c r="B208" t="s">
@@ -8735,7 +8729,7 @@
       </c>
     </row>
     <row r="209" spans="1:5">
-      <c r="A209" s="4" t="s">
+      <c r="A209" s="1" t="s">
         <v>839</v>
       </c>
       <c r="B209" t="s">
@@ -8752,7 +8746,7 @@
       </c>
     </row>
     <row r="210" spans="1:5">
-      <c r="A210" s="4" t="s">
+      <c r="A210" s="1" t="s">
         <v>843</v>
       </c>
       <c r="B210" t="s">
@@ -8769,7 +8763,7 @@
       </c>
     </row>
     <row r="211" spans="1:5">
-      <c r="A211" s="4" t="s">
+      <c r="A211" s="1" t="s">
         <v>847</v>
       </c>
       <c r="B211" t="s">
@@ -8786,7 +8780,7 @@
       </c>
     </row>
     <row r="212" spans="1:5">
-      <c r="A212" s="4" t="s">
+      <c r="A212" s="1" t="s">
         <v>851</v>
       </c>
       <c r="B212" t="s">
@@ -8803,7 +8797,7 @@
       </c>
     </row>
     <row r="213" spans="1:5">
-      <c r="A213" s="4" t="s">
+      <c r="A213" s="1" t="s">
         <v>855</v>
       </c>
       <c r="B213" t="s">
@@ -8820,7 +8814,7 @@
       </c>
     </row>
     <row r="214" spans="1:5">
-      <c r="A214" s="4" t="s">
+      <c r="A214" s="1" t="s">
         <v>859</v>
       </c>
       <c r="B214" t="s">
@@ -8837,7 +8831,7 @@
       </c>
     </row>
     <row r="215" spans="1:5">
-      <c r="A215" s="4" t="s">
+      <c r="A215" s="1" t="s">
         <v>863</v>
       </c>
       <c r="B215" t="s">
@@ -8854,7 +8848,7 @@
       </c>
     </row>
     <row r="216" spans="1:5">
-      <c r="A216" s="4" t="s">
+      <c r="A216" s="1" t="s">
         <v>867</v>
       </c>
       <c r="B216" t="s">
@@ -8871,7 +8865,7 @@
       </c>
     </row>
     <row r="217" spans="1:5">
-      <c r="A217" s="4" t="s">
+      <c r="A217" s="1" t="s">
         <v>871</v>
       </c>
       <c r="B217" t="s">
@@ -8888,7 +8882,7 @@
       </c>
     </row>
     <row r="218" spans="1:5">
-      <c r="A218" s="4" t="s">
+      <c r="A218" s="1" t="s">
         <v>875</v>
       </c>
       <c r="B218" t="s">
@@ -8905,7 +8899,7 @@
       </c>
     </row>
     <row r="219" spans="1:5">
-      <c r="A219" s="4" t="s">
+      <c r="A219" s="1" t="s">
         <v>880</v>
       </c>
       <c r="B219" t="s">
@@ -8922,7 +8916,7 @@
       </c>
     </row>
     <row r="220" spans="1:5">
-      <c r="A220" s="4" t="s">
+      <c r="A220" s="1" t="s">
         <v>884</v>
       </c>
       <c r="B220" t="s">
@@ -8939,7 +8933,7 @@
       </c>
     </row>
     <row r="221" spans="1:5">
-      <c r="A221" s="4" t="s">
+      <c r="A221" s="1" t="s">
         <v>888</v>
       </c>
       <c r="B221" t="s">
@@ -8956,7 +8950,7 @@
       </c>
     </row>
     <row r="222" spans="1:5">
-      <c r="A222" s="4" t="s">
+      <c r="A222" s="1" t="s">
         <v>892</v>
       </c>
       <c r="B222" t="s">
@@ -8973,7 +8967,7 @@
       </c>
     </row>
     <row r="223" spans="1:5">
-      <c r="A223" s="4" t="s">
+      <c r="A223" s="1" t="s">
         <v>896</v>
       </c>
       <c r="B223" t="s">
@@ -8990,7 +8984,7 @@
       </c>
     </row>
     <row r="224" spans="1:5">
-      <c r="A224" s="4" t="s">
+      <c r="A224" s="1" t="s">
         <v>900</v>
       </c>
       <c r="B224" t="s">
@@ -9007,7 +9001,7 @@
       </c>
     </row>
     <row r="225" spans="1:5">
-      <c r="A225" s="4" t="s">
+      <c r="A225" s="1" t="s">
         <v>904</v>
       </c>
       <c r="B225" t="s">
@@ -9024,7 +9018,7 @@
       </c>
     </row>
     <row r="226" spans="1:5">
-      <c r="A226" s="4" t="s">
+      <c r="A226" s="1" t="s">
         <v>909</v>
       </c>
       <c r="B226" t="s">
@@ -9041,7 +9035,7 @@
       </c>
     </row>
     <row r="227" spans="1:5">
-      <c r="A227" s="4" t="s">
+      <c r="A227" s="1" t="s">
         <v>913</v>
       </c>
       <c r="B227" t="s">
@@ -9058,7 +9052,7 @@
       </c>
     </row>
     <row r="228" spans="1:5">
-      <c r="A228" s="4" t="s">
+      <c r="A228" s="1" t="s">
         <v>918</v>
       </c>
       <c r="B228" t="s">
@@ -9075,7 +9069,7 @@
       </c>
     </row>
     <row r="229" spans="1:5">
-      <c r="A229" s="4" t="s">
+      <c r="A229" s="1" t="s">
         <v>923</v>
       </c>
       <c r="B229" t="s">
@@ -9092,7 +9086,7 @@
       </c>
     </row>
     <row r="230" spans="1:5">
-      <c r="A230" s="4" t="s">
+      <c r="A230" s="1" t="s">
         <v>927</v>
       </c>
       <c r="B230" t="s">
@@ -9109,7 +9103,7 @@
       </c>
     </row>
     <row r="231" spans="1:5">
-      <c r="A231" s="4" t="s">
+      <c r="A231" s="1" t="s">
         <v>931</v>
       </c>
       <c r="B231" t="s">
@@ -9126,7 +9120,7 @@
       </c>
     </row>
     <row r="232" spans="1:5">
-      <c r="A232" s="4" t="s">
+      <c r="A232" s="1" t="s">
         <v>935</v>
       </c>
       <c r="B232" t="s">
@@ -9143,7 +9137,7 @@
       </c>
     </row>
     <row r="233" spans="1:5">
-      <c r="A233" s="4" t="s">
+      <c r="A233" s="1" t="s">
         <v>939</v>
       </c>
       <c r="B233" t="s">
@@ -9160,7 +9154,7 @@
       </c>
     </row>
     <row r="234" spans="1:5">
-      <c r="A234" s="4" t="s">
+      <c r="A234" s="1" t="s">
         <v>943</v>
       </c>
       <c r="B234" t="s">
@@ -9177,7 +9171,7 @@
       </c>
     </row>
     <row r="235" spans="1:5">
-      <c r="A235" s="4" t="s">
+      <c r="A235" s="1" t="s">
         <v>947</v>
       </c>
       <c r="B235" t="s">
@@ -9194,7 +9188,7 @@
       </c>
     </row>
     <row r="236" spans="1:5">
-      <c r="A236" s="4" t="s">
+      <c r="A236" s="1" t="s">
         <v>951</v>
       </c>
       <c r="B236" t="s">
@@ -9211,7 +9205,7 @@
       </c>
     </row>
     <row r="237" spans="1:5">
-      <c r="A237" s="4" t="s">
+      <c r="A237" s="1" t="s">
         <v>955</v>
       </c>
       <c r="B237" t="s">
@@ -9228,7 +9222,7 @@
       </c>
     </row>
     <row r="238" spans="1:5">
-      <c r="A238" s="4" t="s">
+      <c r="A238" s="1" t="s">
         <v>959</v>
       </c>
       <c r="B238" t="s">
@@ -9245,7 +9239,7 @@
       </c>
     </row>
     <row r="239" spans="1:5">
-      <c r="A239" s="4" t="s">
+      <c r="A239" s="1" t="s">
         <v>963</v>
       </c>
       <c r="B239" t="s">
@@ -9262,7 +9256,7 @@
       </c>
     </row>
     <row r="240" spans="1:5">
-      <c r="A240" s="4" t="s">
+      <c r="A240" s="1" t="s">
         <v>967</v>
       </c>
       <c r="B240" t="s">
@@ -9279,7 +9273,7 @@
       </c>
     </row>
     <row r="241" spans="1:5">
-      <c r="A241" s="4" t="s">
+      <c r="A241" s="1" t="s">
         <v>971</v>
       </c>
       <c r="B241" t="s">
@@ -9296,7 +9290,7 @@
       </c>
     </row>
     <row r="242" spans="1:5">
-      <c r="A242" s="4" t="s">
+      <c r="A242" s="1" t="s">
         <v>975</v>
       </c>
       <c r="B242" t="s">
@@ -9313,7 +9307,7 @@
       </c>
     </row>
     <row r="243" spans="1:5">
-      <c r="A243" s="4" t="s">
+      <c r="A243" s="1" t="s">
         <v>979</v>
       </c>
       <c r="B243" t="s">
@@ -9330,7 +9324,7 @@
       </c>
     </row>
     <row r="244" spans="1:5">
-      <c r="A244" s="4" t="s">
+      <c r="A244" s="1" t="s">
         <v>983</v>
       </c>
       <c r="B244" t="s">
@@ -9347,7 +9341,7 @@
       </c>
     </row>
     <row r="245" spans="1:5">
-      <c r="A245" s="4" t="s">
+      <c r="A245" s="1" t="s">
         <v>987</v>
       </c>
       <c r="B245" t="s">
@@ -9364,7 +9358,7 @@
       </c>
     </row>
     <row r="246" spans="1:5">
-      <c r="A246" s="4" t="s">
+      <c r="A246" s="1" t="s">
         <v>992</v>
       </c>
       <c r="B246" t="s">
@@ -9381,7 +9375,7 @@
       </c>
     </row>
     <row r="247" spans="1:5">
-      <c r="A247" s="4" t="s">
+      <c r="A247" s="1" t="s">
         <v>997</v>
       </c>
       <c r="B247" t="s">
@@ -9398,7 +9392,7 @@
       </c>
     </row>
     <row r="248" spans="1:5">
-      <c r="A248" s="4" t="s">
+      <c r="A248" s="1" t="s">
         <v>1001</v>
       </c>
       <c r="B248" t="s">
@@ -9415,7 +9409,7 @@
       </c>
     </row>
     <row r="249" spans="1:5">
-      <c r="A249" s="4" t="s">
+      <c r="A249" s="1" t="s">
         <v>1005</v>
       </c>
       <c r="B249" t="s">
@@ -9432,7 +9426,7 @@
       </c>
     </row>
     <row r="250" spans="1:5">
-      <c r="A250" s="4" t="s">
+      <c r="A250" s="1" t="s">
         <v>1009</v>
       </c>
       <c r="B250" t="s">
@@ -9449,7 +9443,7 @@
       </c>
     </row>
     <row r="251" spans="1:5">
-      <c r="A251" s="4" t="s">
+      <c r="A251" s="1" t="s">
         <v>1013</v>
       </c>
       <c r="B251" t="s">
@@ -9466,7 +9460,7 @@
       </c>
     </row>
     <row r="252" spans="1:5">
-      <c r="A252" s="4" t="s">
+      <c r="A252" s="1" t="s">
         <v>1017</v>
       </c>
       <c r="B252" t="s">
@@ -9483,7 +9477,7 @@
       </c>
     </row>
     <row r="253" spans="1:5">
-      <c r="A253" s="4" t="s">
+      <c r="A253" s="1" t="s">
         <v>1021</v>
       </c>
       <c r="B253" t="s">
@@ -9500,7 +9494,7 @@
       </c>
     </row>
     <row r="254" spans="1:5">
-      <c r="A254" s="4" t="s">
+      <c r="A254" s="1" t="s">
         <v>1025</v>
       </c>
       <c r="B254" t="s">
@@ -9517,7 +9511,7 @@
       </c>
     </row>
     <row r="255" spans="1:5">
-      <c r="A255" s="4" t="s">
+      <c r="A255" s="1" t="s">
         <v>1029</v>
       </c>
       <c r="B255" t="s">
@@ -9534,7 +9528,7 @@
       </c>
     </row>
     <row r="256" spans="1:5">
-      <c r="A256" s="4" t="s">
+      <c r="A256" s="1" t="s">
         <v>1033</v>
       </c>
       <c r="B256" t="s">
@@ -9551,7 +9545,7 @@
       </c>
     </row>
     <row r="257" spans="1:5">
-      <c r="A257" s="4" t="s">
+      <c r="A257" s="1" t="s">
         <v>1038</v>
       </c>
       <c r="B257" t="s">
@@ -9568,7 +9562,7 @@
       </c>
     </row>
     <row r="258" spans="1:5">
-      <c r="A258" s="4" t="s">
+      <c r="A258" s="1" t="s">
         <v>1042</v>
       </c>
       <c r="B258" t="s">
@@ -9585,7 +9579,7 @@
       </c>
     </row>
     <row r="259" spans="1:5">
-      <c r="A259" s="4" t="s">
+      <c r="A259" s="1" t="s">
         <v>1046</v>
       </c>
       <c r="B259" t="s">
@@ -9602,7 +9596,7 @@
       </c>
     </row>
     <row r="260" spans="1:5">
-      <c r="A260" s="4" t="s">
+      <c r="A260" s="1" t="s">
         <v>1050</v>
       </c>
       <c r="B260" t="s">
@@ -9619,7 +9613,7 @@
       </c>
     </row>
     <row r="261" spans="1:5">
-      <c r="A261" s="4" t="s">
+      <c r="A261" s="1" t="s">
         <v>1054</v>
       </c>
       <c r="B261" t="s">
@@ -9636,7 +9630,7 @@
       </c>
     </row>
     <row r="262" spans="1:5">
-      <c r="A262" s="4" t="s">
+      <c r="A262" s="1" t="s">
         <v>1058</v>
       </c>
       <c r="B262" t="s">
@@ -9653,7 +9647,7 @@
       </c>
     </row>
     <row r="263" spans="1:5">
-      <c r="A263" s="4" t="s">
+      <c r="A263" s="1" t="s">
         <v>1062</v>
       </c>
       <c r="B263" t="s">
@@ -9670,7 +9664,7 @@
       </c>
     </row>
     <row r="264" spans="1:5">
-      <c r="A264" s="4" t="s">
+      <c r="A264" s="1" t="s">
         <v>1066</v>
       </c>
       <c r="B264" t="s">
@@ -9687,7 +9681,7 @@
       </c>
     </row>
     <row r="265" spans="1:5">
-      <c r="A265" s="4" t="s">
+      <c r="A265" s="1" t="s">
         <v>1070</v>
       </c>
       <c r="B265" t="s">
@@ -9704,7 +9698,7 @@
       </c>
     </row>
     <row r="266" spans="1:5">
-      <c r="A266" s="4" t="s">
+      <c r="A266" s="1" t="s">
         <v>1074</v>
       </c>
       <c r="B266" t="s">
@@ -9721,7 +9715,7 @@
       </c>
     </row>
     <row r="267" spans="1:5">
-      <c r="A267" s="4" t="s">
+      <c r="A267" s="1" t="s">
         <v>1078</v>
       </c>
       <c r="B267" t="s">
@@ -9738,7 +9732,7 @@
       </c>
     </row>
     <row r="268" spans="1:5">
-      <c r="A268" s="4" t="s">
+      <c r="A268" s="1" t="s">
         <v>1082</v>
       </c>
       <c r="B268" t="s">
@@ -9755,7 +9749,7 @@
       </c>
     </row>
     <row r="269" spans="1:5">
-      <c r="A269" s="4" t="s">
+      <c r="A269" s="1" t="s">
         <v>1087</v>
       </c>
       <c r="B269" t="s">
@@ -9772,7 +9766,7 @@
       </c>
     </row>
     <row r="270" spans="1:5">
-      <c r="A270" s="4" t="s">
+      <c r="A270" s="1" t="s">
         <v>1092</v>
       </c>
       <c r="B270" t="s">
@@ -9789,7 +9783,7 @@
       </c>
     </row>
     <row r="271" spans="1:5">
-      <c r="A271" s="4" t="s">
+      <c r="A271" s="1" t="s">
         <v>1097</v>
       </c>
       <c r="B271" t="s">
@@ -9806,7 +9800,7 @@
       </c>
     </row>
     <row r="272" spans="1:5">
-      <c r="A272" s="4" t="s">
+      <c r="A272" s="1" t="s">
         <v>1101</v>
       </c>
       <c r="B272" t="s">
@@ -9823,7 +9817,7 @@
       </c>
     </row>
     <row r="273" spans="1:5">
-      <c r="A273" s="4" t="s">
+      <c r="A273" s="1" t="s">
         <v>1105</v>
       </c>
       <c r="B273" t="s">
@@ -9840,7 +9834,7 @@
       </c>
     </row>
     <row r="274" spans="1:5">
-      <c r="A274" s="4" t="s">
+      <c r="A274" s="1" t="s">
         <v>1109</v>
       </c>
       <c r="B274" t="s">
@@ -9857,7 +9851,7 @@
       </c>
     </row>
     <row r="275" spans="1:5">
-      <c r="A275" s="4" t="s">
+      <c r="A275" s="1" t="s">
         <v>1113</v>
       </c>
       <c r="B275" t="s">
@@ -9874,7 +9868,7 @@
       </c>
     </row>
     <row r="276" spans="1:5">
-      <c r="A276" s="4" t="s">
+      <c r="A276" s="1" t="s">
         <v>1117</v>
       </c>
       <c r="B276" t="s">
@@ -9891,7 +9885,7 @@
       </c>
     </row>
     <row r="277" spans="1:5">
-      <c r="A277" s="4" t="s">
+      <c r="A277" s="1" t="s">
         <v>1121</v>
       </c>
       <c r="B277" t="s">
@@ -9908,7 +9902,7 @@
       </c>
     </row>
     <row r="278" spans="1:5">
-      <c r="A278" s="4" t="s">
+      <c r="A278" s="1" t="s">
         <v>1125</v>
       </c>
       <c r="B278" t="s">
@@ -9925,7 +9919,7 @@
       </c>
     </row>
     <row r="279" spans="1:5">
-      <c r="A279" s="4" t="s">
+      <c r="A279" s="1" t="s">
         <v>1129</v>
       </c>
       <c r="B279" t="s">
@@ -9942,7 +9936,7 @@
       </c>
     </row>
     <row r="280" spans="1:5">
-      <c r="A280" s="4" t="s">
+      <c r="A280" s="1" t="s">
         <v>1133</v>
       </c>
       <c r="B280" t="s">
@@ -9959,7 +9953,7 @@
       </c>
     </row>
     <row r="281" spans="1:5">
-      <c r="A281" s="4" t="s">
+      <c r="A281" s="1" t="s">
         <v>1137</v>
       </c>
       <c r="B281" t="s">
@@ -9976,7 +9970,7 @@
       </c>
     </row>
     <row r="282" spans="1:5">
-      <c r="A282" s="4" t="s">
+      <c r="A282" s="1" t="s">
         <v>1141</v>
       </c>
       <c r="B282" t="s">
@@ -9993,7 +9987,7 @@
       </c>
     </row>
     <row r="283" spans="1:5">
-      <c r="A283" s="4" t="s">
+      <c r="A283" s="1" t="s">
         <v>1146</v>
       </c>
       <c r="B283" t="s">
@@ -10010,7 +10004,7 @@
       </c>
     </row>
     <row r="284" spans="1:5">
-      <c r="A284" s="4" t="s">
+      <c r="A284" s="1" t="s">
         <v>1150</v>
       </c>
       <c r="B284" t="s">
@@ -10027,7 +10021,7 @@
       </c>
     </row>
     <row r="285" spans="1:5">
-      <c r="A285" s="4" t="s">
+      <c r="A285" s="1" t="s">
         <v>1155</v>
       </c>
       <c r="B285" t="s">
@@ -10044,7 +10038,7 @@
       </c>
     </row>
     <row r="286" spans="1:5">
-      <c r="A286" s="4" t="s">
+      <c r="A286" s="1" t="s">
         <v>1160</v>
       </c>
       <c r="B286" t="s">
@@ -10061,7 +10055,7 @@
       </c>
     </row>
     <row r="287" spans="1:5">
-      <c r="A287" s="4" t="s">
+      <c r="A287" s="1" t="s">
         <v>1164</v>
       </c>
       <c r="B287" t="s">
@@ -10078,7 +10072,7 @@
       </c>
     </row>
     <row r="288" spans="1:5">
-      <c r="A288" s="4" t="s">
+      <c r="A288" s="1" t="s">
         <v>1169</v>
       </c>
       <c r="B288" t="s">
@@ -10095,7 +10089,7 @@
       </c>
     </row>
     <row r="289" spans="1:5">
-      <c r="A289" s="4" t="s">
+      <c r="A289" s="1" t="s">
         <v>1173</v>
       </c>
       <c r="B289" t="s">
@@ -10112,7 +10106,7 @@
       </c>
     </row>
     <row r="290" spans="1:5">
-      <c r="A290" s="4" t="s">
+      <c r="A290" s="1" t="s">
         <v>1178</v>
       </c>
       <c r="B290" t="s">
@@ -10129,7 +10123,7 @@
       </c>
     </row>
     <row r="291" spans="1:5">
-      <c r="A291" s="4" t="s">
+      <c r="A291" s="1" t="s">
         <v>1182</v>
       </c>
       <c r="B291" t="s">
@@ -10146,7 +10140,7 @@
       </c>
     </row>
     <row r="292" spans="1:5">
-      <c r="A292" s="4" t="s">
+      <c r="A292" s="1" t="s">
         <v>1186</v>
       </c>
       <c r="B292" t="s">
@@ -10163,7 +10157,7 @@
       </c>
     </row>
     <row r="293" spans="1:5">
-      <c r="A293" s="4" t="s">
+      <c r="A293" s="1" t="s">
         <v>1190</v>
       </c>
       <c r="B293" t="s">
@@ -10180,7 +10174,7 @@
       </c>
     </row>
     <row r="294" spans="1:5">
-      <c r="A294" s="4" t="s">
+      <c r="A294" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="B294" t="s">
@@ -10197,7 +10191,7 @@
       </c>
     </row>
     <row r="295" spans="1:5">
-      <c r="A295" s="4" t="s">
+      <c r="A295" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="B295" t="s">
@@ -10214,7 +10208,7 @@
       </c>
     </row>
     <row r="296" spans="1:5">
-      <c r="A296" s="4" t="s">
+      <c r="A296" s="1" t="s">
         <v>1203</v>
       </c>
       <c r="B296" t="s">
@@ -10231,7 +10225,7 @@
       </c>
     </row>
     <row r="297" spans="1:5">
-      <c r="A297" s="4" t="s">
+      <c r="A297" s="1" t="s">
         <v>1207</v>
       </c>
       <c r="B297" t="s">
@@ -10248,7 +10242,7 @@
       </c>
     </row>
     <row r="298" spans="1:5">
-      <c r="A298" s="4" t="s">
+      <c r="A298" s="1" t="s">
         <v>1211</v>
       </c>
       <c r="B298" t="s">
@@ -10265,7 +10259,7 @@
       </c>
     </row>
     <row r="299" spans="1:5">
-      <c r="A299" s="4" t="s">
+      <c r="A299" s="1" t="s">
         <v>1215</v>
       </c>
       <c r="B299" t="s">
@@ -10282,7 +10276,7 @@
       </c>
     </row>
     <row r="300" spans="1:5">
-      <c r="A300" s="4" t="s">
+      <c r="A300" s="1" t="s">
         <v>1219</v>
       </c>
       <c r="B300" t="s">
@@ -10299,7 +10293,7 @@
       </c>
     </row>
     <row r="301" spans="1:5">
-      <c r="A301" s="4" t="s">
+      <c r="A301" s="1" t="s">
         <v>1222</v>
       </c>
       <c r="B301" t="s">
@@ -10316,7 +10310,7 @@
       </c>
     </row>
     <row r="302" spans="1:5">
-      <c r="A302" s="4" t="s">
+      <c r="A302" s="1" t="s">
         <v>1225</v>
       </c>
       <c r="B302" t="s">
@@ -10333,7 +10327,7 @@
       </c>
     </row>
     <row r="303" spans="1:5">
-      <c r="A303" s="4" t="s">
+      <c r="A303" s="1" t="s">
         <v>1228</v>
       </c>
       <c r="B303" t="s">
@@ -10350,7 +10344,7 @@
       </c>
     </row>
     <row r="304" spans="1:5">
-      <c r="A304" s="4" t="s">
+      <c r="A304" s="1" t="s">
         <v>1231</v>
       </c>
       <c r="B304" t="s">
@@ -10367,7 +10361,7 @@
       </c>
     </row>
     <row r="305" spans="1:5">
-      <c r="A305" s="4" t="s">
+      <c r="A305" s="1" t="s">
         <v>1234</v>
       </c>
       <c r="B305" t="s">
@@ -10384,7 +10378,7 @@
       </c>
     </row>
     <row r="306" spans="1:5">
-      <c r="A306" s="4" t="s">
+      <c r="A306" s="1" t="s">
         <v>1237</v>
       </c>
       <c r="B306" t="s">
@@ -10401,7 +10395,7 @@
       </c>
     </row>
     <row r="307" spans="1:5">
-      <c r="A307" s="4" t="s">
+      <c r="A307" s="1" t="s">
         <v>1240</v>
       </c>
       <c r="B307" t="s">
@@ -10418,7 +10412,7 @@
       </c>
     </row>
     <row r="308" spans="1:5">
-      <c r="A308" s="4" t="s">
+      <c r="A308" s="1" t="s">
         <v>1243</v>
       </c>
       <c r="B308" t="s">
@@ -10435,7 +10429,7 @@
       </c>
     </row>
     <row r="309" spans="1:5">
-      <c r="A309" s="4" t="s">
+      <c r="A309" s="1" t="s">
         <v>1246</v>
       </c>
       <c r="B309" t="s">
@@ -10452,7 +10446,7 @@
       </c>
     </row>
     <row r="310" spans="1:5">
-      <c r="A310" s="4" t="s">
+      <c r="A310" s="1" t="s">
         <v>1249</v>
       </c>
       <c r="B310" t="s">
@@ -10469,7 +10463,7 @@
       </c>
     </row>
     <row r="311" spans="1:5">
-      <c r="A311" s="4" t="s">
+      <c r="A311" s="1" t="s">
         <v>1252</v>
       </c>
       <c r="B311" t="s">
@@ -10486,7 +10480,7 @@
       </c>
     </row>
     <row r="312" spans="1:5">
-      <c r="A312" s="4" t="s">
+      <c r="A312" s="1" t="s">
         <v>1255</v>
       </c>
       <c r="B312" t="s">
@@ -10503,7 +10497,7 @@
       </c>
     </row>
     <row r="313" spans="1:5">
-      <c r="A313" s="4" t="s">
+      <c r="A313" s="1" t="s">
         <v>1258</v>
       </c>
       <c r="B313" t="s">
@@ -10520,7 +10514,7 @@
       </c>
     </row>
     <row r="314" spans="1:5">
-      <c r="A314" s="4" t="s">
+      <c r="A314" s="1" t="s">
         <v>1261</v>
       </c>
       <c r="B314" t="s">
@@ -10537,7 +10531,7 @@
       </c>
     </row>
     <row r="315" spans="1:5">
-      <c r="A315" s="4" t="s">
+      <c r="A315" s="1" t="s">
         <v>1264</v>
       </c>
       <c r="B315" t="s">
@@ -10554,7 +10548,7 @@
       </c>
     </row>
     <row r="316" spans="1:5">
-      <c r="A316" s="4" t="s">
+      <c r="A316" s="1" t="s">
         <v>1267</v>
       </c>
       <c r="B316" t="s">
@@ -10571,7 +10565,7 @@
       </c>
     </row>
     <row r="317" spans="1:5">
-      <c r="A317" s="4" t="s">
+      <c r="A317" s="1" t="s">
         <v>1270</v>
       </c>
       <c r="B317" t="s">
@@ -10588,7 +10582,7 @@
       </c>
     </row>
     <row r="318" spans="1:5">
-      <c r="A318" s="4" t="s">
+      <c r="A318" s="1" t="s">
         <v>1273</v>
       </c>
       <c r="B318" t="s">
@@ -10605,7 +10599,7 @@
       </c>
     </row>
     <row r="319" spans="1:5">
-      <c r="A319" s="4" t="s">
+      <c r="A319" s="1" t="s">
         <v>1276</v>
       </c>
       <c r="B319" t="s">
@@ -10622,7 +10616,7 @@
       </c>
     </row>
     <row r="320" spans="1:5">
-      <c r="A320" s="4" t="s">
+      <c r="A320" s="1" t="s">
         <v>1279</v>
       </c>
       <c r="B320" t="s">
@@ -10639,7 +10633,7 @@
       </c>
     </row>
     <row r="321" spans="1:5">
-      <c r="A321" s="4" t="s">
+      <c r="A321" s="1" t="s">
         <v>1282</v>
       </c>
       <c r="B321" t="s">
@@ -10656,7 +10650,7 @@
       </c>
     </row>
     <row r="322" spans="1:5">
-      <c r="A322" s="4" t="s">
+      <c r="A322" s="1" t="s">
         <v>1285</v>
       </c>
       <c r="B322" t="s">
@@ -10673,7 +10667,7 @@
       </c>
     </row>
     <row r="323" spans="1:5">
-      <c r="A323" s="4" t="s">
+      <c r="A323" s="1" t="s">
         <v>1288</v>
       </c>
       <c r="B323" t="s">
@@ -10690,7 +10684,7 @@
       </c>
     </row>
     <row r="324" spans="1:5">
-      <c r="A324" s="4" t="s">
+      <c r="A324" s="1" t="s">
         <v>1291</v>
       </c>
       <c r="B324" t="s">
@@ -10707,7 +10701,7 @@
       </c>
     </row>
     <row r="325" spans="1:5">
-      <c r="A325" s="4" t="s">
+      <c r="A325" s="1" t="s">
         <v>1294</v>
       </c>
       <c r="B325" t="s">
@@ -10724,7 +10718,7 @@
       </c>
     </row>
     <row r="326" spans="1:5">
-      <c r="A326" s="4" t="s">
+      <c r="A326" s="1" t="s">
         <v>1297</v>
       </c>
       <c r="B326" t="s">
@@ -10741,7 +10735,7 @@
       </c>
     </row>
     <row r="327" spans="1:5">
-      <c r="A327" s="4" t="s">
+      <c r="A327" s="1" t="s">
         <v>1300</v>
       </c>
       <c r="B327" t="s">
@@ -10758,7 +10752,7 @@
       </c>
     </row>
     <row r="328" spans="1:5">
-      <c r="A328" s="4" t="s">
+      <c r="A328" s="1" t="s">
         <v>1303</v>
       </c>
       <c r="B328" t="s">
@@ -10775,7 +10769,7 @@
       </c>
     </row>
     <row r="329" spans="1:5">
-      <c r="A329" s="4" t="s">
+      <c r="A329" s="1" t="s">
         <v>1306</v>
       </c>
       <c r="B329" t="s">
@@ -10792,7 +10786,7 @@
       </c>
     </row>
     <row r="330" spans="1:5">
-      <c r="A330" s="4" t="s">
+      <c r="A330" s="1" t="s">
         <v>1309</v>
       </c>
       <c r="B330" t="s">
@@ -10809,7 +10803,7 @@
       </c>
     </row>
     <row r="331" spans="1:5">
-      <c r="A331" s="4" t="s">
+      <c r="A331" s="1" t="s">
         <v>1312</v>
       </c>
       <c r="B331" t="s">
@@ -10826,7 +10820,7 @@
       </c>
     </row>
     <row r="332" spans="1:5">
-      <c r="A332" s="4" t="s">
+      <c r="A332" s="1" t="s">
         <v>1315</v>
       </c>
       <c r="B332" t="s">
@@ -10843,7 +10837,7 @@
       </c>
     </row>
     <row r="333" spans="1:5">
-      <c r="A333" s="4" t="s">
+      <c r="A333" s="1" t="s">
         <v>1318</v>
       </c>
       <c r="B333" t="s">
@@ -10860,7 +10854,7 @@
       </c>
     </row>
     <row r="334" spans="1:5">
-      <c r="A334" s="4" t="s">
+      <c r="A334" s="1" t="s">
         <v>1321</v>
       </c>
       <c r="B334" t="s">
@@ -10877,7 +10871,7 @@
       </c>
     </row>
     <row r="335" spans="1:5">
-      <c r="A335" s="4" t="s">
+      <c r="A335" s="1" t="s">
         <v>1324</v>
       </c>
       <c r="B335" t="s">
@@ -10894,7 +10888,7 @@
       </c>
     </row>
     <row r="336" spans="1:5">
-      <c r="A336" s="4" t="s">
+      <c r="A336" s="1" t="s">
         <v>1327</v>
       </c>
       <c r="B336" t="s">
@@ -10911,7 +10905,7 @@
       </c>
     </row>
     <row r="337" spans="1:5">
-      <c r="A337" s="4" t="s">
+      <c r="A337" s="1" t="s">
         <v>1330</v>
       </c>
       <c r="B337" t="s">
@@ -10928,7 +10922,7 @@
       </c>
     </row>
     <row r="338" spans="1:5">
-      <c r="A338" s="4" t="s">
+      <c r="A338" s="1" t="s">
         <v>1333</v>
       </c>
       <c r="B338" t="s">
@@ -10945,7 +10939,7 @@
       </c>
     </row>
     <row r="339" spans="1:5">
-      <c r="A339" s="4" t="s">
+      <c r="A339" s="1" t="s">
         <v>1336</v>
       </c>
       <c r="B339" t="s">
@@ -10962,7 +10956,7 @@
       </c>
     </row>
     <row r="340" spans="1:5">
-      <c r="A340" s="4" t="s">
+      <c r="A340" s="1" t="s">
         <v>1339</v>
       </c>
       <c r="B340" t="s">
@@ -10979,7 +10973,7 @@
       </c>
     </row>
     <row r="341" spans="1:5">
-      <c r="A341" s="4" t="s">
+      <c r="A341" s="1" t="s">
         <v>1342</v>
       </c>
       <c r="B341" t="s">
@@ -10996,7 +10990,7 @@
       </c>
     </row>
     <row r="342" spans="1:5">
-      <c r="A342" s="4" t="s">
+      <c r="A342" s="1" t="s">
         <v>1345</v>
       </c>
       <c r="B342" t="s">
@@ -11013,7 +11007,7 @@
       </c>
     </row>
     <row r="343" spans="1:5">
-      <c r="A343" s="4" t="s">
+      <c r="A343" s="1" t="s">
         <v>1348</v>
       </c>
       <c r="B343" t="s">
@@ -11030,7 +11024,7 @@
       </c>
     </row>
     <row r="344" spans="1:5">
-      <c r="A344" s="4" t="s">
+      <c r="A344" s="1" t="s">
         <v>1351</v>
       </c>
       <c r="B344" t="s">
@@ -11047,7 +11041,7 @@
       </c>
     </row>
     <row r="345" spans="1:5">
-      <c r="A345" s="4" t="s">
+      <c r="A345" s="1" t="s">
         <v>1354</v>
       </c>
       <c r="B345" t="s">
@@ -11064,7 +11058,7 @@
       </c>
     </row>
     <row r="346" spans="1:5">
-      <c r="A346" s="4" t="s">
+      <c r="A346" s="1" t="s">
         <v>1357</v>
       </c>
       <c r="B346" t="s">
@@ -11081,7 +11075,7 @@
       </c>
     </row>
     <row r="347" spans="1:5">
-      <c r="A347" s="4" t="s">
+      <c r="A347" s="1" t="s">
         <v>1360</v>
       </c>
       <c r="B347" t="s">
@@ -11098,7 +11092,7 @@
       </c>
     </row>
     <row r="348" spans="1:5">
-      <c r="A348" s="4" t="s">
+      <c r="A348" s="1" t="s">
         <v>1363</v>
       </c>
       <c r="B348" t="s">
@@ -11115,7 +11109,7 @@
       </c>
     </row>
     <row r="349" spans="1:5">
-      <c r="A349" s="4" t="s">
+      <c r="A349" s="1" t="s">
         <v>1366</v>
       </c>
       <c r="B349" t="s">
@@ -11132,7 +11126,7 @@
       </c>
     </row>
     <row r="350" spans="1:5">
-      <c r="A350" s="4" t="s">
+      <c r="A350" s="1" t="s">
         <v>1369</v>
       </c>
       <c r="B350" t="s">
@@ -11149,7 +11143,7 @@
       </c>
     </row>
     <row r="351" spans="1:5">
-      <c r="A351" s="4" t="s">
+      <c r="A351" s="1" t="s">
         <v>1372</v>
       </c>
       <c r="B351" t="s">
@@ -11166,7 +11160,7 @@
       </c>
     </row>
     <row r="352" spans="1:5">
-      <c r="A352" s="4" t="s">
+      <c r="A352" s="1" t="s">
         <v>1375</v>
       </c>
       <c r="B352" t="s">

--- a/SimonCani_glyphs.xlsx
+++ b/SimonCani_glyphs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12915" windowHeight="12765"/>
+    <workbookView windowWidth="26670" windowHeight="12765"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5209,7 +5209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" ht="13.5" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" ht="13.5" spans="1:5">
       <c r="A91" s="1" t="s">
         <v>5</v>
       </c>

--- a/SimonCani_glyphs.xlsx
+++ b/SimonCani_glyphs.xlsx
@@ -44,15 +44,7 @@
     <t>GlyphName</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>□</t>
-    </r>
+    <t>□</t>
   </si>
   <si>
     <t>\u0000</t>
@@ -4210,6 +4202,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -4354,12 +4352,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -4695,16 +4687,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4713,119 +4702,122 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4835,6 +4827,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -5183,7 +5178,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E352"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" customWidth="1"/>
@@ -5192,7 +5187,7 @@
     <col min="5" max="5" width="29.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5209,8 +5204,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="13.5" spans="1:5">
-      <c r="A2" s="1" t="s">
+    <row r="2" customHeight="1" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
@@ -5226,7 +5221,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" customHeight="1" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -5243,7 +5238,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" customHeight="1" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -5260,7 +5255,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" customHeight="1" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -5277,7 +5272,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" customHeight="1" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -5294,7 +5289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" customHeight="1" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
@@ -5311,7 +5306,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" customHeight="1" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
@@ -5328,7 +5323,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" customHeight="1" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
@@ -5345,7 +5340,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" customHeight="1" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>38</v>
       </c>
@@ -5362,7 +5357,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" customHeight="1" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>42</v>
       </c>
@@ -5379,7 +5374,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" customHeight="1" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>46</v>
       </c>
@@ -5396,7 +5391,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" customHeight="1" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>50</v>
       </c>
@@ -5413,7 +5408,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" customHeight="1" spans="1:5">
       <c r="A14" s="1" t="s">
         <v>54</v>
       </c>
@@ -5430,7 +5425,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" customHeight="1" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>58</v>
       </c>
@@ -5447,7 +5442,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" customHeight="1" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>62</v>
       </c>
@@ -5464,7 +5459,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" customHeight="1" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>66</v>
       </c>
@@ -5481,7 +5476,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" customHeight="1" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>70</v>
       </c>
@@ -5498,7 +5493,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" customHeight="1" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>74</v>
       </c>
@@ -5515,7 +5510,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" customHeight="1" spans="1:5">
       <c r="A20" s="1" t="s">
         <v>78</v>
       </c>
@@ -5532,7 +5527,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" customHeight="1" spans="1:5">
       <c r="A21" s="1" t="s">
         <v>82</v>
       </c>
@@ -5549,7 +5544,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" customHeight="1" spans="1:5">
       <c r="A22" s="1" t="s">
         <v>86</v>
       </c>
@@ -5566,7 +5561,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" customHeight="1" spans="1:5">
       <c r="A23" s="1" t="s">
         <v>90</v>
       </c>
@@ -5583,7 +5578,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" customHeight="1" spans="1:5">
       <c r="A24" s="1" t="s">
         <v>94</v>
       </c>
@@ -5600,7 +5595,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" customHeight="1" spans="1:5">
       <c r="A25" s="1" t="s">
         <v>98</v>
       </c>
@@ -5617,7 +5612,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" customHeight="1" spans="1:5">
       <c r="A26" s="1" t="s">
         <v>102</v>
       </c>
@@ -5634,7 +5629,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" customHeight="1" spans="1:5">
       <c r="A27" s="1" t="s">
         <v>106</v>
       </c>
@@ -5651,7 +5646,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" customHeight="1" spans="1:5">
       <c r="A28" s="1" t="s">
         <v>110</v>
       </c>
@@ -5668,7 +5663,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" customHeight="1" spans="1:5">
       <c r="A29" s="1" t="s">
         <v>114</v>
       </c>
@@ -5685,7 +5680,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" customHeight="1" spans="1:5">
       <c r="A30" s="1" t="s">
         <v>118</v>
       </c>
@@ -5702,7 +5697,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" customHeight="1" spans="1:5">
       <c r="A31" s="1" t="s">
         <v>122</v>
       </c>
@@ -5719,7 +5714,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" customHeight="1" spans="1:5">
       <c r="A32" s="1" t="s">
         <v>126</v>
       </c>
@@ -5736,7 +5731,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" customHeight="1" spans="1:5">
       <c r="A33" s="1" t="s">
         <v>130</v>
       </c>
@@ -5753,7 +5748,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" customHeight="1" spans="1:5">
       <c r="A34" s="1" t="s">
         <v>134</v>
       </c>
@@ -5770,7 +5765,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" customHeight="1" spans="1:5">
       <c r="A35" s="1" t="s">
         <v>138</v>
       </c>
@@ -5787,7 +5782,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" customHeight="1" spans="1:5">
       <c r="A36" s="1" t="s">
         <v>142</v>
       </c>
@@ -5804,7 +5799,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" customHeight="1" spans="1:5">
       <c r="A37" s="1" t="s">
         <v>146</v>
       </c>
@@ -5821,7 +5816,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" customHeight="1" spans="1:5">
       <c r="A38" s="1" t="s">
         <v>150</v>
       </c>
@@ -5838,7 +5833,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" customHeight="1" spans="1:5">
       <c r="A39" s="1" t="s">
         <v>154</v>
       </c>
@@ -5855,7 +5850,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" customHeight="1" spans="1:5">
       <c r="A40" s="1" t="s">
         <v>158</v>
       </c>
@@ -5872,7 +5867,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" customHeight="1" spans="1:5">
       <c r="A41" s="1" t="s">
         <v>162</v>
       </c>
@@ -5889,7 +5884,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" customHeight="1" spans="1:5">
       <c r="A42" s="1" t="s">
         <v>166</v>
       </c>
@@ -5906,7 +5901,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" customHeight="1" spans="1:5">
       <c r="A43" s="1" t="s">
         <v>170</v>
       </c>
@@ -5923,7 +5918,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" customHeight="1" spans="1:5">
       <c r="A44" s="1" t="s">
         <v>174</v>
       </c>
@@ -5940,7 +5935,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" customHeight="1" spans="1:5">
       <c r="A45" s="1" t="s">
         <v>178</v>
       </c>
@@ -5957,7 +5952,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" customHeight="1" spans="1:5">
       <c r="A46" s="1" t="s">
         <v>182</v>
       </c>
@@ -5974,7 +5969,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" customHeight="1" spans="1:5">
       <c r="A47" s="1" t="s">
         <v>186</v>
       </c>
@@ -5991,7 +5986,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" customHeight="1" spans="1:5">
       <c r="A48" s="1" t="s">
         <v>190</v>
       </c>
@@ -6008,7 +6003,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" customHeight="1" spans="1:5">
       <c r="A49" s="1" t="s">
         <v>194</v>
       </c>
@@ -6025,7 +6020,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" customHeight="1" spans="1:5">
       <c r="A50" s="1" t="s">
         <v>198</v>
       </c>
@@ -6042,7 +6037,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" customHeight="1" spans="1:5">
       <c r="A51" s="1" t="s">
         <v>202</v>
       </c>
@@ -6059,7 +6054,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" customHeight="1" spans="1:5">
       <c r="A52" s="1" t="s">
         <v>206</v>
       </c>
@@ -6076,7 +6071,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" customHeight="1" spans="1:5">
       <c r="A53" s="1" t="s">
         <v>210</v>
       </c>
@@ -6093,7 +6088,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" customHeight="1" spans="1:5">
       <c r="A54" s="1" t="s">
         <v>214</v>
       </c>
@@ -6110,7 +6105,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" customHeight="1" spans="1:5">
       <c r="A55" s="1" t="s">
         <v>218</v>
       </c>
@@ -6127,7 +6122,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" customHeight="1" spans="1:5">
       <c r="A56" s="1" t="s">
         <v>222</v>
       </c>
@@ -6144,7 +6139,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" customHeight="1" spans="1:5">
       <c r="A57" s="1" t="s">
         <v>226</v>
       </c>
@@ -6161,7 +6156,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" customHeight="1" spans="1:5">
       <c r="A58" s="1" t="s">
         <v>230</v>
       </c>
@@ -6178,7 +6173,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" customHeight="1" spans="1:5">
       <c r="A59" s="1" t="s">
         <v>234</v>
       </c>
@@ -6195,7 +6190,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" customHeight="1" spans="1:5">
       <c r="A60" s="1" t="s">
         <v>238</v>
       </c>
@@ -6212,7 +6207,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" customHeight="1" spans="1:5">
       <c r="A61" s="1" t="s">
         <v>242</v>
       </c>
@@ -6229,7 +6224,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" customHeight="1" spans="1:5">
       <c r="A62" s="1" t="s">
         <v>246</v>
       </c>
@@ -6246,7 +6241,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" customHeight="1" spans="1:5">
       <c r="A63" s="1" t="s">
         <v>250</v>
       </c>
@@ -6263,7 +6258,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" customHeight="1" spans="1:5">
       <c r="A64" s="1" t="s">
         <v>254</v>
       </c>
@@ -6280,7 +6275,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" customHeight="1" spans="1:5">
       <c r="A65" s="1" t="s">
         <v>258</v>
       </c>
@@ -6297,7 +6292,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" customHeight="1" spans="1:5">
       <c r="A66" s="1" t="s">
         <v>262</v>
       </c>
@@ -6314,7 +6309,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" customHeight="1" spans="1:5">
       <c r="A67" s="1" t="s">
         <v>266</v>
       </c>
@@ -6331,7 +6326,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" customHeight="1" spans="1:5">
       <c r="A68" s="1" t="s">
         <v>270</v>
       </c>
@@ -6348,7 +6343,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" customHeight="1" spans="1:5">
       <c r="A69" s="1" t="s">
         <v>274</v>
       </c>
@@ -6365,7 +6360,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" customHeight="1" spans="1:5">
       <c r="A70" s="1" t="s">
         <v>278</v>
       </c>
@@ -6382,7 +6377,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" customHeight="1" spans="1:5">
       <c r="A71" s="1" t="s">
         <v>282</v>
       </c>
@@ -6399,7 +6394,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" customHeight="1" spans="1:5">
       <c r="A72" s="1" t="s">
         <v>286</v>
       </c>
@@ -6416,7 +6411,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" customHeight="1" spans="1:5">
       <c r="A73" s="1" t="s">
         <v>290</v>
       </c>
@@ -6433,7 +6428,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" customHeight="1" spans="1:5">
       <c r="A74" s="1" t="s">
         <v>294</v>
       </c>
@@ -6450,7 +6445,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" customHeight="1" spans="1:5">
       <c r="A75" s="1" t="s">
         <v>298</v>
       </c>
@@ -6467,7 +6462,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" customHeight="1" spans="1:5">
       <c r="A76" s="1" t="s">
         <v>302</v>
       </c>
@@ -6484,7 +6479,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" customHeight="1" spans="1:5">
       <c r="A77" s="1" t="s">
         <v>306</v>
       </c>
@@ -6501,7 +6496,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" customHeight="1" spans="1:5">
       <c r="A78" s="1" t="s">
         <v>310</v>
       </c>
@@ -6518,7 +6513,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" customHeight="1" spans="1:5">
       <c r="A79" s="1" t="s">
         <v>314</v>
       </c>
@@ -6535,7 +6530,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" customHeight="1" spans="1:5">
       <c r="A80" s="1" t="s">
         <v>318</v>
       </c>
@@ -6552,7 +6547,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" customHeight="1" spans="1:5">
       <c r="A81" s="1" t="s">
         <v>323</v>
       </c>
@@ -6569,7 +6564,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" customHeight="1" spans="1:5">
       <c r="A82" s="1" t="s">
         <v>327</v>
       </c>
@@ -6586,7 +6581,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" customHeight="1" spans="1:5">
       <c r="A83" s="1" t="s">
         <v>331</v>
       </c>
@@ -6603,7 +6598,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" customHeight="1" spans="1:5">
       <c r="A84" s="1" t="s">
         <v>335</v>
       </c>
@@ -6620,7 +6615,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" customHeight="1" spans="1:5">
       <c r="A85" s="1" t="s">
         <v>339</v>
       </c>
@@ -6637,7 +6632,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" customHeight="1" spans="1:5">
       <c r="A86" s="1" t="s">
         <v>343</v>
       </c>
@@ -6654,7 +6649,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" customHeight="1" spans="1:5">
       <c r="A87" s="1" t="s">
         <v>347</v>
       </c>
@@ -6671,7 +6666,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" customHeight="1" spans="1:5">
       <c r="A88" s="1" t="s">
         <v>351</v>
       </c>
@@ -6688,7 +6683,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" customHeight="1" spans="1:5">
       <c r="A89" s="1" t="s">
         <v>355</v>
       </c>
@@ -6705,7 +6700,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" customHeight="1" spans="1:5">
       <c r="A90" s="1" t="s">
         <v>359</v>
       </c>
@@ -6722,8 +6717,8 @@
         <v>362</v>
       </c>
     </row>
-    <row r="91" ht="13.5" spans="1:5">
-      <c r="A91" s="1" t="s">
+    <row r="91" customHeight="1" spans="1:5">
+      <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B91" t="s">
@@ -6739,7 +6734,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" customHeight="1" spans="1:5">
       <c r="A92" s="1" t="s">
         <v>366</v>
       </c>
@@ -6756,7 +6751,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" customHeight="1" spans="1:5">
       <c r="A93" s="1" t="s">
         <v>370</v>
       </c>
@@ -6773,7 +6768,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" customHeight="1" spans="1:5">
       <c r="A94" s="1" t="s">
         <v>374</v>
       </c>
@@ -6790,7 +6785,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" customHeight="1" spans="1:5">
       <c r="A95" s="1" t="s">
         <v>378</v>
       </c>
@@ -6807,7 +6802,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" customHeight="1" spans="1:5">
       <c r="A96" s="1" t="s">
         <v>382</v>
       </c>
@@ -6824,7 +6819,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" customHeight="1" spans="1:5">
       <c r="A97" s="1" t="s">
         <v>386</v>
       </c>
@@ -6841,7 +6836,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" customHeight="1" spans="1:5">
       <c r="A98" s="1" t="s">
         <v>390</v>
       </c>
@@ -6858,7 +6853,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" customHeight="1" spans="1:5">
       <c r="A99" s="1" t="s">
         <v>394</v>
       </c>
@@ -6875,7 +6870,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" customHeight="1" spans="1:5">
       <c r="A100" s="1" t="s">
         <v>398</v>
       </c>
@@ -6892,7 +6887,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" customHeight="1" spans="1:5">
       <c r="A101" s="1" t="s">
         <v>402</v>
       </c>
@@ -6909,7 +6904,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" customHeight="1" spans="1:5">
       <c r="A102" s="1" t="s">
         <v>406</v>
       </c>
@@ -6926,7 +6921,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" customHeight="1" spans="1:5">
       <c r="A103" s="1" t="s">
         <v>410</v>
       </c>
@@ -6943,7 +6938,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" customHeight="1" spans="1:5">
       <c r="A104" s="1" t="s">
         <v>414</v>
       </c>
@@ -6960,7 +6955,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" customHeight="1" spans="1:5">
       <c r="A105" s="1" t="s">
         <v>418</v>
       </c>
@@ -6977,7 +6972,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" customHeight="1" spans="1:5">
       <c r="A106" s="1" t="s">
         <v>422</v>
       </c>
@@ -6994,7 +6989,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" customHeight="1" spans="1:5">
       <c r="A107" s="1" t="s">
         <v>426</v>
       </c>
@@ -7011,7 +7006,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" customHeight="1" spans="1:5">
       <c r="A108" s="1" t="s">
         <v>430</v>
       </c>
@@ -7028,7 +7023,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" customHeight="1" spans="1:5">
       <c r="A109" s="1" t="s">
         <v>434</v>
       </c>
@@ -7045,7 +7040,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" customHeight="1" spans="1:5">
       <c r="A110" s="1" t="s">
         <v>438</v>
       </c>
@@ -7062,7 +7057,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" customHeight="1" spans="1:5">
       <c r="A111" s="1" t="s">
         <v>442</v>
       </c>
@@ -7079,7 +7074,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" customHeight="1" spans="1:5">
       <c r="A112" s="1" t="s">
         <v>446</v>
       </c>
@@ -7096,7 +7091,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" customHeight="1" spans="1:5">
       <c r="A113" s="1" t="s">
         <v>450</v>
       </c>
@@ -7113,7 +7108,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" customHeight="1" spans="1:5">
       <c r="A114" s="1" t="s">
         <v>454</v>
       </c>
@@ -7130,7 +7125,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" customHeight="1" spans="1:5">
       <c r="A115" s="1" t="s">
         <v>458</v>
       </c>
@@ -7147,7 +7142,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" customHeight="1" spans="1:5">
       <c r="A116" s="1" t="s">
         <v>463</v>
       </c>
@@ -7164,7 +7159,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" customHeight="1" spans="1:5">
       <c r="A117" s="1" t="s">
         <v>467</v>
       </c>
@@ -7181,7 +7176,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" customHeight="1" spans="1:5">
       <c r="A118" s="1" t="s">
         <v>471</v>
       </c>
@@ -7198,7 +7193,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" customHeight="1" spans="1:5">
       <c r="A119" s="1" t="s">
         <v>475</v>
       </c>
@@ -7215,7 +7210,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" customHeight="1" spans="1:5">
       <c r="A120" s="1" t="s">
         <v>479</v>
       </c>
@@ -7232,7 +7227,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" customHeight="1" spans="1:5">
       <c r="A121" s="1" t="s">
         <v>484</v>
       </c>
@@ -7249,7 +7244,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" customHeight="1" spans="1:5">
       <c r="A122" s="1" t="s">
         <v>488</v>
       </c>
@@ -7266,7 +7261,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" customHeight="1" spans="1:5">
       <c r="A123" s="1" t="s">
         <v>492</v>
       </c>
@@ -7283,7 +7278,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" customHeight="1" spans="1:5">
       <c r="A124" s="1" t="s">
         <v>497</v>
       </c>
@@ -7300,7 +7295,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" customHeight="1" spans="1:5">
       <c r="A125" s="1" t="s">
         <v>501</v>
       </c>
@@ -7317,7 +7312,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" customHeight="1" spans="1:5">
       <c r="A126" s="1" t="s">
         <v>505</v>
       </c>
@@ -7334,7 +7329,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" customHeight="1" spans="1:5">
       <c r="A127" s="1" t="s">
         <v>509</v>
       </c>
@@ -7351,7 +7346,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" customHeight="1" spans="1:5">
       <c r="A128" s="1" t="s">
         <v>513</v>
       </c>
@@ -7368,7 +7363,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" customHeight="1" spans="1:5">
       <c r="A129" s="1" t="s">
         <v>517</v>
       </c>
@@ -7385,7 +7380,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" customHeight="1" spans="1:5">
       <c r="A130" s="1" t="s">
         <v>521</v>
       </c>
@@ -7402,7 +7397,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" customHeight="1" spans="1:5">
       <c r="A131" s="1" t="s">
         <v>525</v>
       </c>
@@ -7419,7 +7414,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" customHeight="1" spans="1:5">
       <c r="A132" s="1" t="s">
         <v>529</v>
       </c>
@@ -7436,7 +7431,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" customHeight="1" spans="1:5">
       <c r="A133" s="1" t="s">
         <v>533</v>
       </c>
@@ -7453,7 +7448,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" customHeight="1" spans="1:5">
       <c r="A134" s="1" t="s">
         <v>537</v>
       </c>
@@ -7470,7 +7465,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" customHeight="1" spans="1:5">
       <c r="A135" s="1" t="s">
         <v>541</v>
       </c>
@@ -7487,7 +7482,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" customHeight="1" spans="1:5">
       <c r="A136" s="1" t="s">
         <v>545</v>
       </c>
@@ -7504,7 +7499,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" customHeight="1" spans="1:5">
       <c r="A137" s="1" t="s">
         <v>549</v>
       </c>
@@ -7521,7 +7516,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" customHeight="1" spans="1:5">
       <c r="A138" s="1" t="s">
         <v>553</v>
       </c>
@@ -7538,7 +7533,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" customHeight="1" spans="1:5">
       <c r="A139" s="1" t="s">
         <v>557</v>
       </c>
@@ -7555,7 +7550,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" customHeight="1" spans="1:5">
       <c r="A140" s="1" t="s">
         <v>561</v>
       </c>
@@ -7572,7 +7567,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" customHeight="1" spans="1:5">
       <c r="A141" s="1" t="s">
         <v>565</v>
       </c>
@@ -7589,7 +7584,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" customHeight="1" spans="1:5">
       <c r="A142" s="1" t="s">
         <v>569</v>
       </c>
@@ -7606,7 +7601,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" customHeight="1" spans="1:5">
       <c r="A143" s="1" t="s">
         <v>573</v>
       </c>
@@ -7623,7 +7618,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" customHeight="1" spans="1:5">
       <c r="A144" s="1" t="s">
         <v>577</v>
       </c>
@@ -7640,7 +7635,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" customHeight="1" spans="1:5">
       <c r="A145" s="1" t="s">
         <v>581</v>
       </c>
@@ -7657,7 +7652,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" customHeight="1" spans="1:5">
       <c r="A146" s="1" t="s">
         <v>585</v>
       </c>
@@ -7674,7 +7669,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" customHeight="1" spans="1:5">
       <c r="A147" s="1" t="s">
         <v>589</v>
       </c>
@@ -7691,7 +7686,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" customHeight="1" spans="1:5">
       <c r="A148" s="1" t="s">
         <v>593</v>
       </c>
@@ -7708,7 +7703,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" customHeight="1" spans="1:5">
       <c r="A149" s="1" t="s">
         <v>597</v>
       </c>
@@ -7725,7 +7720,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" customHeight="1" spans="1:5">
       <c r="A150" s="1" t="s">
         <v>601</v>
       </c>
@@ -7742,7 +7737,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" customHeight="1" spans="1:5">
       <c r="A151" s="1" t="s">
         <v>605</v>
       </c>
@@ -7759,7 +7754,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" customHeight="1" spans="1:5">
       <c r="A152" s="1" t="s">
         <v>609</v>
       </c>
@@ -7776,7 +7771,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" customHeight="1" spans="1:5">
       <c r="A153" s="1" t="s">
         <v>613</v>
       </c>
@@ -7793,7 +7788,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" customHeight="1" spans="1:5">
       <c r="A154" s="1" t="s">
         <v>617</v>
       </c>
@@ -7810,7 +7805,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" customHeight="1" spans="1:5">
       <c r="A155" s="1" t="s">
         <v>621</v>
       </c>
@@ -7827,7 +7822,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" customHeight="1" spans="1:5">
       <c r="A156" s="1" t="s">
         <v>625</v>
       </c>
@@ -7844,7 +7839,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" customHeight="1" spans="1:5">
       <c r="A157" s="1" t="s">
         <v>629</v>
       </c>
@@ -7861,7 +7856,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" customHeight="1" spans="1:5">
       <c r="A158" s="1" t="s">
         <v>633</v>
       </c>
@@ -7878,7 +7873,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" customHeight="1" spans="1:5">
       <c r="A159" s="1" t="s">
         <v>637</v>
       </c>
@@ -7895,7 +7890,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" customHeight="1" spans="1:5">
       <c r="A160" s="1" t="s">
         <v>641</v>
       </c>
@@ -7912,7 +7907,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" customHeight="1" spans="1:5">
       <c r="A161" s="1" t="s">
         <v>645</v>
       </c>
@@ -7929,7 +7924,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" customHeight="1" spans="1:5">
       <c r="A162" s="1" t="s">
         <v>649</v>
       </c>
@@ -7946,7 +7941,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" customHeight="1" spans="1:5">
       <c r="A163" s="1" t="s">
         <v>653</v>
       </c>
@@ -7963,7 +7958,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" customHeight="1" spans="1:5">
       <c r="A164" s="1" t="s">
         <v>657</v>
       </c>
@@ -7980,7 +7975,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" customHeight="1" spans="1:5">
       <c r="A165" s="1" t="s">
         <v>661</v>
       </c>
@@ -7997,7 +7992,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" customHeight="1" spans="1:5">
       <c r="A166" s="1" t="s">
         <v>665</v>
       </c>
@@ -8014,7 +8009,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" customHeight="1" spans="1:5">
       <c r="A167" s="1" t="s">
         <v>669</v>
       </c>
@@ -8031,7 +8026,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" customHeight="1" spans="1:5">
       <c r="A168" s="1" t="s">
         <v>673</v>
       </c>
@@ -8048,7 +8043,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" customHeight="1" spans="1:5">
       <c r="A169" s="1" t="s">
         <v>677</v>
       </c>
@@ -8065,7 +8060,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" customHeight="1" spans="1:5">
       <c r="A170" s="1" t="s">
         <v>681</v>
       </c>
@@ -8082,7 +8077,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" customHeight="1" spans="1:5">
       <c r="A171" s="1" t="s">
         <v>685</v>
       </c>
@@ -8099,7 +8094,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" customHeight="1" spans="1:5">
       <c r="A172" s="1" t="s">
         <v>689</v>
       </c>
@@ -8116,7 +8111,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" customHeight="1" spans="1:5">
       <c r="A173" s="1" t="s">
         <v>693</v>
       </c>
@@ -8133,7 +8128,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" customHeight="1" spans="1:5">
       <c r="A174" s="1" t="s">
         <v>697</v>
       </c>
@@ -8150,7 +8145,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" customHeight="1" spans="1:5">
       <c r="A175" s="1" t="s">
         <v>701</v>
       </c>
@@ -8167,7 +8162,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" customHeight="1" spans="1:5">
       <c r="A176" s="1" t="s">
         <v>705</v>
       </c>
@@ -8184,7 +8179,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" customHeight="1" spans="1:5">
       <c r="A177" s="1" t="s">
         <v>709</v>
       </c>
@@ -8201,7 +8196,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" customHeight="1" spans="1:5">
       <c r="A178" s="1" t="s">
         <v>713</v>
       </c>
@@ -8218,7 +8213,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" customHeight="1" spans="1:5">
       <c r="A179" s="1" t="s">
         <v>717</v>
       </c>
@@ -8235,7 +8230,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" customHeight="1" spans="1:5">
       <c r="A180" s="1" t="s">
         <v>721</v>
       </c>
@@ -8252,7 +8247,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" customHeight="1" spans="1:5">
       <c r="A181" s="1" t="s">
         <v>725</v>
       </c>
@@ -8269,7 +8264,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" customHeight="1" spans="1:5">
       <c r="A182" s="1" t="s">
         <v>729</v>
       </c>
@@ -8286,7 +8281,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" customHeight="1" spans="1:5">
       <c r="A183" s="1" t="s">
         <v>733</v>
       </c>
@@ -8303,7 +8298,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" customHeight="1" spans="1:5">
       <c r="A184" s="1" t="s">
         <v>737</v>
       </c>
@@ -8320,7 +8315,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" customHeight="1" spans="1:5">
       <c r="A185" s="1" t="s">
         <v>741</v>
       </c>
@@ -8337,7 +8332,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" customHeight="1" spans="1:5">
       <c r="A186" s="1" t="s">
         <v>745</v>
       </c>
@@ -8354,7 +8349,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" customHeight="1" spans="1:5">
       <c r="A187" s="1" t="s">
         <v>750</v>
       </c>
@@ -8371,7 +8366,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" customHeight="1" spans="1:5">
       <c r="A188" s="1" t="s">
         <v>754</v>
       </c>
@@ -8388,7 +8383,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" customHeight="1" spans="1:5">
       <c r="A189" s="1" t="s">
         <v>758</v>
       </c>
@@ -8405,7 +8400,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" customHeight="1" spans="1:5">
       <c r="A190" s="1" t="s">
         <v>762</v>
       </c>
@@ -8422,7 +8417,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" customHeight="1" spans="1:5">
       <c r="A191" s="1" t="s">
         <v>766</v>
       </c>
@@ -8439,7 +8434,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" customHeight="1" spans="1:5">
       <c r="A192" s="1" t="s">
         <v>770</v>
       </c>
@@ -8456,7 +8451,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" customHeight="1" spans="1:5">
       <c r="A193" s="1" t="s">
         <v>774</v>
       </c>
@@ -8473,7 +8468,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" customHeight="1" spans="1:5">
       <c r="A194" s="1" t="s">
         <v>778</v>
       </c>
@@ -8490,7 +8485,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" customHeight="1" spans="1:5">
       <c r="A195" s="1" t="s">
         <v>782</v>
       </c>
@@ -8507,7 +8502,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" customHeight="1" spans="1:5">
       <c r="A196" s="1" t="s">
         <v>786</v>
       </c>
@@ -8524,7 +8519,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" customHeight="1" spans="1:5">
       <c r="A197" s="1" t="s">
         <v>790</v>
       </c>
@@ -8541,7 +8536,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" customHeight="1" spans="1:5">
       <c r="A198" s="1" t="s">
         <v>794</v>
       </c>
@@ -8558,7 +8553,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" customHeight="1" spans="1:5">
       <c r="A199" s="1" t="s">
         <v>799</v>
       </c>
@@ -8575,7 +8570,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" customHeight="1" spans="1:5">
       <c r="A200" s="1" t="s">
         <v>803</v>
       </c>
@@ -8592,7 +8587,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" customHeight="1" spans="1:5">
       <c r="A201" s="1" t="s">
         <v>807</v>
       </c>
@@ -8609,7 +8604,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" customHeight="1" spans="1:5">
       <c r="A202" s="1" t="s">
         <v>811</v>
       </c>
@@ -8626,7 +8621,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" customHeight="1" spans="1:5">
       <c r="A203" s="1" t="s">
         <v>815</v>
       </c>
@@ -8643,7 +8638,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" customHeight="1" spans="1:5">
       <c r="A204" s="1" t="s">
         <v>819</v>
       </c>
@@ -8660,7 +8655,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" customHeight="1" spans="1:5">
       <c r="A205" s="1" t="s">
         <v>823</v>
       </c>
@@ -8677,7 +8672,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" customHeight="1" spans="1:5">
       <c r="A206" s="1" t="s">
         <v>827</v>
       </c>
@@ -8694,7 +8689,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" customHeight="1" spans="1:5">
       <c r="A207" s="1" t="s">
         <v>831</v>
       </c>
@@ -8711,7 +8706,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" customHeight="1" spans="1:5">
       <c r="A208" s="1" t="s">
         <v>835</v>
       </c>
@@ -8728,7 +8723,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" customHeight="1" spans="1:5">
       <c r="A209" s="1" t="s">
         <v>839</v>
       </c>
@@ -8745,7 +8740,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" customHeight="1" spans="1:5">
       <c r="A210" s="1" t="s">
         <v>843</v>
       </c>
@@ -8762,7 +8757,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" customHeight="1" spans="1:5">
       <c r="A211" s="1" t="s">
         <v>847</v>
       </c>
@@ -8779,7 +8774,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" customHeight="1" spans="1:5">
       <c r="A212" s="1" t="s">
         <v>851</v>
       </c>
@@ -8796,7 +8791,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" customHeight="1" spans="1:5">
       <c r="A213" s="1" t="s">
         <v>855</v>
       </c>
@@ -8813,7 +8808,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" customHeight="1" spans="1:5">
       <c r="A214" s="1" t="s">
         <v>859</v>
       </c>
@@ -8830,7 +8825,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" customHeight="1" spans="1:5">
       <c r="A215" s="1" t="s">
         <v>863</v>
       </c>
@@ -8847,7 +8842,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" customHeight="1" spans="1:5">
       <c r="A216" s="1" t="s">
         <v>867</v>
       </c>
@@ -8864,7 +8859,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" customHeight="1" spans="1:5">
       <c r="A217" s="1" t="s">
         <v>871</v>
       </c>
@@ -8881,7 +8876,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" customHeight="1" spans="1:5">
       <c r="A218" s="1" t="s">
         <v>875</v>
       </c>
@@ -8898,7 +8893,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" customHeight="1" spans="1:5">
       <c r="A219" s="1" t="s">
         <v>880</v>
       </c>
@@ -8915,7 +8910,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" customHeight="1" spans="1:5">
       <c r="A220" s="1" t="s">
         <v>884</v>
       </c>
@@ -8932,7 +8927,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" customHeight="1" spans="1:5">
       <c r="A221" s="1" t="s">
         <v>888</v>
       </c>
@@ -8949,7 +8944,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" customHeight="1" spans="1:5">
       <c r="A222" s="1" t="s">
         <v>892</v>
       </c>
@@ -8966,7 +8961,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" customHeight="1" spans="1:5">
       <c r="A223" s="1" t="s">
         <v>896</v>
       </c>
@@ -8983,7 +8978,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" customHeight="1" spans="1:5">
       <c r="A224" s="1" t="s">
         <v>900</v>
       </c>
@@ -9000,7 +8995,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" customHeight="1" spans="1:5">
       <c r="A225" s="1" t="s">
         <v>904</v>
       </c>
@@ -9017,7 +9012,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" customHeight="1" spans="1:5">
       <c r="A226" s="1" t="s">
         <v>909</v>
       </c>
@@ -9034,7 +9029,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" customHeight="1" spans="1:5">
       <c r="A227" s="1" t="s">
         <v>913</v>
       </c>
@@ -9051,7 +9046,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" customHeight="1" spans="1:5">
       <c r="A228" s="1" t="s">
         <v>918</v>
       </c>
@@ -9068,7 +9063,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" customHeight="1" spans="1:5">
       <c r="A229" s="1" t="s">
         <v>923</v>
       </c>
@@ -9085,7 +9080,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" customHeight="1" spans="1:5">
       <c r="A230" s="1" t="s">
         <v>927</v>
       </c>
@@ -9102,7 +9097,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" customHeight="1" spans="1:5">
       <c r="A231" s="1" t="s">
         <v>931</v>
       </c>
@@ -9119,7 +9114,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" customHeight="1" spans="1:5">
       <c r="A232" s="1" t="s">
         <v>935</v>
       </c>
@@ -9136,7 +9131,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" customHeight="1" spans="1:5">
       <c r="A233" s="1" t="s">
         <v>939</v>
       </c>
@@ -9153,7 +9148,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" customHeight="1" spans="1:5">
       <c r="A234" s="1" t="s">
         <v>943</v>
       </c>
@@ -9170,7 +9165,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" customHeight="1" spans="1:5">
       <c r="A235" s="1" t="s">
         <v>947</v>
       </c>
@@ -9187,7 +9182,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" customHeight="1" spans="1:5">
       <c r="A236" s="1" t="s">
         <v>951</v>
       </c>
@@ -9204,7 +9199,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" customHeight="1" spans="1:5">
       <c r="A237" s="1" t="s">
         <v>955</v>
       </c>
@@ -9221,7 +9216,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" customHeight="1" spans="1:5">
       <c r="A238" s="1" t="s">
         <v>959</v>
       </c>
@@ -9238,7 +9233,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" customHeight="1" spans="1:5">
       <c r="A239" s="1" t="s">
         <v>963</v>
       </c>
@@ -9255,7 +9250,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" customHeight="1" spans="1:5">
       <c r="A240" s="1" t="s">
         <v>967</v>
       </c>
@@ -9272,7 +9267,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" customHeight="1" spans="1:5">
       <c r="A241" s="1" t="s">
         <v>971</v>
       </c>
@@ -9289,7 +9284,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" customHeight="1" spans="1:5">
       <c r="A242" s="1" t="s">
         <v>975</v>
       </c>
@@ -9306,7 +9301,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" customHeight="1" spans="1:5">
       <c r="A243" s="1" t="s">
         <v>979</v>
       </c>
@@ -9323,7 +9318,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" customHeight="1" spans="1:5">
       <c r="A244" s="1" t="s">
         <v>983</v>
       </c>
@@ -9340,7 +9335,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" customHeight="1" spans="1:5">
       <c r="A245" s="1" t="s">
         <v>987</v>
       </c>
@@ -9357,7 +9352,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" customHeight="1" spans="1:5">
       <c r="A246" s="1" t="s">
         <v>992</v>
       </c>
@@ -9374,7 +9369,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" customHeight="1" spans="1:5">
       <c r="A247" s="1" t="s">
         <v>997</v>
       </c>
@@ -9391,7 +9386,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" customHeight="1" spans="1:5">
       <c r="A248" s="1" t="s">
         <v>1001</v>
       </c>
@@ -9408,7 +9403,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" customHeight="1" spans="1:5">
       <c r="A249" s="1" t="s">
         <v>1005</v>
       </c>
@@ -9425,7 +9420,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" customHeight="1" spans="1:5">
       <c r="A250" s="1" t="s">
         <v>1009</v>
       </c>
@@ -9442,7 +9437,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" customHeight="1" spans="1:5">
       <c r="A251" s="1" t="s">
         <v>1013</v>
       </c>
@@ -9459,7 +9454,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" customHeight="1" spans="1:5">
       <c r="A252" s="1" t="s">
         <v>1017</v>
       </c>
@@ -9476,7 +9471,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" customHeight="1" spans="1:5">
       <c r="A253" s="1" t="s">
         <v>1021</v>
       </c>
@@ -9493,7 +9488,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" customHeight="1" spans="1:5">
       <c r="A254" s="1" t="s">
         <v>1025</v>
       </c>
@@ -9510,7 +9505,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" customHeight="1" spans="1:5">
       <c r="A255" s="1" t="s">
         <v>1029</v>
       </c>
@@ -9527,7 +9522,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" customHeight="1" spans="1:5">
       <c r="A256" s="1" t="s">
         <v>1033</v>
       </c>
@@ -9544,7 +9539,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" customHeight="1" spans="1:5">
       <c r="A257" s="1" t="s">
         <v>1038</v>
       </c>
@@ -9561,7 +9556,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" customHeight="1" spans="1:5">
       <c r="A258" s="1" t="s">
         <v>1042</v>
       </c>
@@ -9578,7 +9573,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" customHeight="1" spans="1:5">
       <c r="A259" s="1" t="s">
         <v>1046</v>
       </c>
@@ -9595,7 +9590,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" customHeight="1" spans="1:5">
       <c r="A260" s="1" t="s">
         <v>1050</v>
       </c>
@@ -9612,7 +9607,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" customHeight="1" spans="1:5">
       <c r="A261" s="1" t="s">
         <v>1054</v>
       </c>
@@ -9629,7 +9624,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" customHeight="1" spans="1:5">
       <c r="A262" s="1" t="s">
         <v>1058</v>
       </c>
@@ -9646,7 +9641,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" customHeight="1" spans="1:5">
       <c r="A263" s="1" t="s">
         <v>1062</v>
       </c>
@@ -9663,7 +9658,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" customHeight="1" spans="1:5">
       <c r="A264" s="1" t="s">
         <v>1066</v>
       </c>
@@ -9680,7 +9675,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" customHeight="1" spans="1:5">
       <c r="A265" s="1" t="s">
         <v>1070</v>
       </c>
@@ -9697,7 +9692,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" customHeight="1" spans="1:5">
       <c r="A266" s="1" t="s">
         <v>1074</v>
       </c>
@@ -9714,7 +9709,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" customHeight="1" spans="1:5">
       <c r="A267" s="1" t="s">
         <v>1078</v>
       </c>
@@ -9731,7 +9726,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" customHeight="1" spans="1:5">
       <c r="A268" s="1" t="s">
         <v>1082</v>
       </c>
@@ -9748,7 +9743,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" customHeight="1" spans="1:5">
       <c r="A269" s="1" t="s">
         <v>1087</v>
       </c>
@@ -9765,7 +9760,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" customHeight="1" spans="1:5">
       <c r="A270" s="1" t="s">
         <v>1092</v>
       </c>
@@ -9782,7 +9777,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" customHeight="1" spans="1:5">
       <c r="A271" s="1" t="s">
         <v>1097</v>
       </c>
@@ -9799,7 +9794,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" customHeight="1" spans="1:5">
       <c r="A272" s="1" t="s">
         <v>1101</v>
       </c>
@@ -9816,7 +9811,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" customHeight="1" spans="1:5">
       <c r="A273" s="1" t="s">
         <v>1105</v>
       </c>
@@ -9833,7 +9828,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" customHeight="1" spans="1:5">
       <c r="A274" s="1" t="s">
         <v>1109</v>
       </c>
@@ -9850,7 +9845,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" customHeight="1" spans="1:5">
       <c r="A275" s="1" t="s">
         <v>1113</v>
       </c>
@@ -9867,7 +9862,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" customHeight="1" spans="1:5">
       <c r="A276" s="1" t="s">
         <v>1117</v>
       </c>
@@ -9884,7 +9879,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" customHeight="1" spans="1:5">
       <c r="A277" s="1" t="s">
         <v>1121</v>
       </c>
@@ -9901,7 +9896,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" customHeight="1" spans="1:5">
       <c r="A278" s="1" t="s">
         <v>1125</v>
       </c>
@@ -9918,7 +9913,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" customHeight="1" spans="1:5">
       <c r="A279" s="1" t="s">
         <v>1129</v>
       </c>
@@ -9935,7 +9930,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" customHeight="1" spans="1:5">
       <c r="A280" s="1" t="s">
         <v>1133</v>
       </c>
@@ -9952,7 +9947,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" customHeight="1" spans="1:5">
       <c r="A281" s="1" t="s">
         <v>1137</v>
       </c>
@@ -9969,7 +9964,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" customHeight="1" spans="1:5">
       <c r="A282" s="1" t="s">
         <v>1141</v>
       </c>
@@ -9986,7 +9981,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" customHeight="1" spans="1:5">
       <c r="A283" s="1" t="s">
         <v>1146</v>
       </c>
@@ -10003,7 +9998,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" customHeight="1" spans="1:5">
       <c r="A284" s="1" t="s">
         <v>1150</v>
       </c>
@@ -10020,7 +10015,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" customHeight="1" spans="1:5">
       <c r="A285" s="1" t="s">
         <v>1155</v>
       </c>
@@ -10037,7 +10032,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" customHeight="1" spans="1:5">
       <c r="A286" s="1" t="s">
         <v>1160</v>
       </c>
@@ -10054,7 +10049,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" customHeight="1" spans="1:5">
       <c r="A287" s="1" t="s">
         <v>1164</v>
       </c>
@@ -10071,7 +10066,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" customHeight="1" spans="1:5">
       <c r="A288" s="1" t="s">
         <v>1169</v>
       </c>
@@ -10088,7 +10083,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="289" spans="1:5">
+    <row r="289" customHeight="1" spans="1:5">
       <c r="A289" s="1" t="s">
         <v>1173</v>
       </c>
@@ -10105,7 +10100,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="290" spans="1:5">
+    <row r="290" customHeight="1" spans="1:5">
       <c r="A290" s="1" t="s">
         <v>1178</v>
       </c>
@@ -10122,7 +10117,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="291" spans="1:5">
+    <row r="291" customHeight="1" spans="1:5">
       <c r="A291" s="1" t="s">
         <v>1182</v>
       </c>
@@ -10139,7 +10134,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="292" spans="1:5">
+    <row r="292" customHeight="1" spans="1:5">
       <c r="A292" s="1" t="s">
         <v>1186</v>
       </c>
@@ -10156,7 +10151,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="293" spans="1:5">
+    <row r="293" customHeight="1" spans="1:5">
       <c r="A293" s="1" t="s">
         <v>1190</v>
       </c>
@@ -10173,7 +10168,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="294" spans="1:5">
+    <row r="294" customHeight="1" spans="1:5">
       <c r="A294" s="1" t="s">
         <v>1195</v>
       </c>
@@ -10190,7 +10185,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="295" spans="1:5">
+    <row r="295" customHeight="1" spans="1:5">
       <c r="A295" s="1" t="s">
         <v>1199</v>
       </c>
@@ -10207,7 +10202,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="296" spans="1:5">
+    <row r="296" customHeight="1" spans="1:5">
       <c r="A296" s="1" t="s">
         <v>1203</v>
       </c>
@@ -10224,7 +10219,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="297" spans="1:5">
+    <row r="297" customHeight="1" spans="1:5">
       <c r="A297" s="1" t="s">
         <v>1207</v>
       </c>
@@ -10241,7 +10236,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="298" spans="1:5">
+    <row r="298" customHeight="1" spans="1:5">
       <c r="A298" s="1" t="s">
         <v>1211</v>
       </c>
@@ -10258,7 +10253,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="299" spans="1:5">
+    <row r="299" customHeight="1" spans="1:5">
       <c r="A299" s="1" t="s">
         <v>1215</v>
       </c>
@@ -10275,7 +10270,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="300" spans="1:5">
+    <row r="300" customHeight="1" spans="1:5">
       <c r="A300" s="1" t="s">
         <v>1219</v>
       </c>
@@ -10292,7 +10287,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="301" spans="1:5">
+    <row r="301" customHeight="1" spans="1:5">
       <c r="A301" s="1" t="s">
         <v>1222</v>
       </c>
@@ -10309,7 +10304,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="302" spans="1:5">
+    <row r="302" customHeight="1" spans="1:5">
       <c r="A302" s="1" t="s">
         <v>1225</v>
       </c>
@@ -10326,7 +10321,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="303" spans="1:5">
+    <row r="303" customHeight="1" spans="1:5">
       <c r="A303" s="1" t="s">
         <v>1228</v>
       </c>
@@ -10343,7 +10338,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="304" spans="1:5">
+    <row r="304" customHeight="1" spans="1:5">
       <c r="A304" s="1" t="s">
         <v>1231</v>
       </c>
@@ -10360,7 +10355,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="305" spans="1:5">
+    <row r="305" customHeight="1" spans="1:5">
       <c r="A305" s="1" t="s">
         <v>1234</v>
       </c>
@@ -10377,7 +10372,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="306" spans="1:5">
+    <row r="306" customHeight="1" spans="1:5">
       <c r="A306" s="1" t="s">
         <v>1237</v>
       </c>
@@ -10394,7 +10389,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="307" spans="1:5">
+    <row r="307" customHeight="1" spans="1:5">
       <c r="A307" s="1" t="s">
         <v>1240</v>
       </c>
@@ -10411,7 +10406,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="308" spans="1:5">
+    <row r="308" customHeight="1" spans="1:5">
       <c r="A308" s="1" t="s">
         <v>1243</v>
       </c>
@@ -10428,7 +10423,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="309" spans="1:5">
+    <row r="309" customHeight="1" spans="1:5">
       <c r="A309" s="1" t="s">
         <v>1246</v>
       </c>
@@ -10445,7 +10440,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="310" spans="1:5">
+    <row r="310" customHeight="1" spans="1:5">
       <c r="A310" s="1" t="s">
         <v>1249</v>
       </c>
@@ -10462,7 +10457,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="311" spans="1:5">
+    <row r="311" customHeight="1" spans="1:5">
       <c r="A311" s="1" t="s">
         <v>1252</v>
       </c>
@@ -10479,7 +10474,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="312" spans="1:5">
+    <row r="312" customHeight="1" spans="1:5">
       <c r="A312" s="1" t="s">
         <v>1255</v>
       </c>
@@ -10496,7 +10491,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="313" spans="1:5">
+    <row r="313" customHeight="1" spans="1:5">
       <c r="A313" s="1" t="s">
         <v>1258</v>
       </c>
@@ -10513,7 +10508,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="314" spans="1:5">
+    <row r="314" customHeight="1" spans="1:5">
       <c r="A314" s="1" t="s">
         <v>1261</v>
       </c>
@@ -10530,7 +10525,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="315" spans="1:5">
+    <row r="315" customHeight="1" spans="1:5">
       <c r="A315" s="1" t="s">
         <v>1264</v>
       </c>
@@ -10547,7 +10542,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="316" spans="1:5">
+    <row r="316" customHeight="1" spans="1:5">
       <c r="A316" s="1" t="s">
         <v>1267</v>
       </c>
@@ -10564,7 +10559,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="317" spans="1:5">
+    <row r="317" customHeight="1" spans="1:5">
       <c r="A317" s="1" t="s">
         <v>1270</v>
       </c>
@@ -10581,7 +10576,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="318" spans="1:5">
+    <row r="318" customHeight="1" spans="1:5">
       <c r="A318" s="1" t="s">
         <v>1273</v>
       </c>
@@ -10598,7 +10593,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="319" spans="1:5">
+    <row r="319" customHeight="1" spans="1:5">
       <c r="A319" s="1" t="s">
         <v>1276</v>
       </c>
@@ -10615,7 +10610,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="320" spans="1:5">
+    <row r="320" customHeight="1" spans="1:5">
       <c r="A320" s="1" t="s">
         <v>1279</v>
       </c>
@@ -10632,7 +10627,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="321" spans="1:5">
+    <row r="321" customHeight="1" spans="1:5">
       <c r="A321" s="1" t="s">
         <v>1282</v>
       </c>
@@ -10649,7 +10644,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="322" spans="1:5">
+    <row r="322" customHeight="1" spans="1:5">
       <c r="A322" s="1" t="s">
         <v>1285</v>
       </c>
@@ -10666,7 +10661,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="323" spans="1:5">
+    <row r="323" customHeight="1" spans="1:5">
       <c r="A323" s="1" t="s">
         <v>1288</v>
       </c>
@@ -10683,7 +10678,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="324" spans="1:5">
+    <row r="324" customHeight="1" spans="1:5">
       <c r="A324" s="1" t="s">
         <v>1291</v>
       </c>
@@ -10700,7 +10695,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="325" spans="1:5">
+    <row r="325" customHeight="1" spans="1:5">
       <c r="A325" s="1" t="s">
         <v>1294</v>
       </c>
@@ -10717,7 +10712,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="326" spans="1:5">
+    <row r="326" customHeight="1" spans="1:5">
       <c r="A326" s="1" t="s">
         <v>1297</v>
       </c>
@@ -10734,7 +10729,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="327" spans="1:5">
+    <row r="327" customHeight="1" spans="1:5">
       <c r="A327" s="1" t="s">
         <v>1300</v>
       </c>
@@ -10751,7 +10746,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="328" spans="1:5">
+    <row r="328" customHeight="1" spans="1:5">
       <c r="A328" s="1" t="s">
         <v>1303</v>
       </c>
@@ -10768,7 +10763,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="329" spans="1:5">
+    <row r="329" customHeight="1" spans="1:5">
       <c r="A329" s="1" t="s">
         <v>1306</v>
       </c>
@@ -10785,7 +10780,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="330" spans="1:5">
+    <row r="330" customHeight="1" spans="1:5">
       <c r="A330" s="1" t="s">
         <v>1309</v>
       </c>
@@ -10802,7 +10797,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="331" spans="1:5">
+    <row r="331" customHeight="1" spans="1:5">
       <c r="A331" s="1" t="s">
         <v>1312</v>
       </c>
@@ -10819,7 +10814,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="332" spans="1:5">
+    <row r="332" customHeight="1" spans="1:5">
       <c r="A332" s="1" t="s">
         <v>1315</v>
       </c>
@@ -10836,7 +10831,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="333" spans="1:5">
+    <row r="333" customHeight="1" spans="1:5">
       <c r="A333" s="1" t="s">
         <v>1318</v>
       </c>
@@ -10853,7 +10848,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="334" spans="1:5">
+    <row r="334" customHeight="1" spans="1:5">
       <c r="A334" s="1" t="s">
         <v>1321</v>
       </c>
@@ -10870,7 +10865,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="335" spans="1:5">
+    <row r="335" customHeight="1" spans="1:5">
       <c r="A335" s="1" t="s">
         <v>1324</v>
       </c>
@@ -10887,7 +10882,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="336" spans="1:5">
+    <row r="336" customHeight="1" spans="1:5">
       <c r="A336" s="1" t="s">
         <v>1327</v>
       </c>
@@ -10904,7 +10899,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="337" spans="1:5">
+    <row r="337" customHeight="1" spans="1:5">
       <c r="A337" s="1" t="s">
         <v>1330</v>
       </c>
@@ -10921,7 +10916,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="338" spans="1:5">
+    <row r="338" customHeight="1" spans="1:5">
       <c r="A338" s="1" t="s">
         <v>1333</v>
       </c>
@@ -10938,7 +10933,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="339" spans="1:5">
+    <row r="339" customHeight="1" spans="1:5">
       <c r="A339" s="1" t="s">
         <v>1336</v>
       </c>
@@ -10955,7 +10950,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="340" spans="1:5">
+    <row r="340" customHeight="1" spans="1:5">
       <c r="A340" s="1" t="s">
         <v>1339</v>
       </c>
@@ -10972,7 +10967,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="341" spans="1:5">
+    <row r="341" customHeight="1" spans="1:5">
       <c r="A341" s="1" t="s">
         <v>1342</v>
       </c>
@@ -10989,7 +10984,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="342" spans="1:5">
+    <row r="342" customHeight="1" spans="1:5">
       <c r="A342" s="1" t="s">
         <v>1345</v>
       </c>
@@ -11006,7 +11001,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="343" spans="1:5">
+    <row r="343" customHeight="1" spans="1:5">
       <c r="A343" s="1" t="s">
         <v>1348</v>
       </c>
@@ -11023,7 +11018,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="344" spans="1:5">
+    <row r="344" customHeight="1" spans="1:5">
       <c r="A344" s="1" t="s">
         <v>1351</v>
       </c>
@@ -11040,7 +11035,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="345" spans="1:5">
+    <row r="345" customHeight="1" spans="1:5">
       <c r="A345" s="1" t="s">
         <v>1354</v>
       </c>
@@ -11057,7 +11052,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="346" spans="1:5">
+    <row r="346" customHeight="1" spans="1:5">
       <c r="A346" s="1" t="s">
         <v>1357</v>
       </c>
@@ -11074,7 +11069,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="347" spans="1:5">
+    <row r="347" customHeight="1" spans="1:5">
       <c r="A347" s="1" t="s">
         <v>1360</v>
       </c>
@@ -11091,7 +11086,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="348" spans="1:5">
+    <row r="348" customHeight="1" spans="1:5">
       <c r="A348" s="1" t="s">
         <v>1363</v>
       </c>
@@ -11108,7 +11103,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="349" spans="1:5">
+    <row r="349" customHeight="1" spans="1:5">
       <c r="A349" s="1" t="s">
         <v>1366</v>
       </c>
@@ -11125,7 +11120,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="350" spans="1:5">
+    <row r="350" customHeight="1" spans="1:5">
       <c r="A350" s="1" t="s">
         <v>1369</v>
       </c>
@@ -11142,7 +11137,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="351" spans="1:5">
+    <row r="351" customHeight="1" spans="1:5">
       <c r="A351" s="1" t="s">
         <v>1372</v>
       </c>
@@ -11159,7 +11154,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="352" spans="1:5">
+    <row r="352" customHeight="1" spans="1:5">
       <c r="A352" s="1" t="s">
         <v>1375</v>
       </c>

--- a/SimonCani_glyphs.xlsx
+++ b/SimonCani_glyphs.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26670" windowHeight="12765"/>
+    <workbookView windowWidth="26670" windowHeight="12765" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="1379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="1399">
   <si>
     <t>Character</t>
   </si>
@@ -4164,6 +4165,66 @@
   </si>
   <si>
     <t>glyph_Ksmallcapturn</t>
+  </si>
+  <si>
+    <t>ị</t>
+  </si>
+  <si>
+    <t>ụ</t>
+  </si>
+  <si>
+    <t>i̜</t>
+  </si>
+  <si>
+    <t>u̜</t>
+  </si>
+  <si>
+    <t>i̠</t>
+  </si>
+  <si>
+    <t>u̠</t>
+  </si>
+  <si>
+    <t>e̤</t>
+  </si>
+  <si>
+    <t>o̤</t>
+  </si>
+  <si>
+    <t>ẹ</t>
+  </si>
+  <si>
+    <t>ọ</t>
+  </si>
+  <si>
+    <t>e̜</t>
+  </si>
+  <si>
+    <t>o̜</t>
+  </si>
+  <si>
+    <t>e̜̜</t>
+  </si>
+  <si>
+    <t>o̜̜</t>
+  </si>
+  <si>
+    <t>e̠</t>
+  </si>
+  <si>
+    <t>o̠</t>
+  </si>
+  <si>
+    <t>ɑ̈</t>
+  </si>
+  <si>
+    <t>ɑ̜</t>
+  </si>
+  <si>
+    <t>ɑ̣</t>
+  </si>
+  <si>
+    <t>ɑ̊</t>
   </si>
 </sst>
 </file>
@@ -4176,13 +4237,25 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="TH-Times"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="TH-Times"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4687,148 +4760,157 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5180,7 +5262,7 @@
   <dimension ref="A1:E352"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.25" style="4" customWidth="1"/>
     <col min="2" max="2" width="9.25" customWidth="1"/>
     <col min="3" max="3" width="54.875" customWidth="1"/>
     <col min="4" max="4" width="40.375" customWidth="1"/>
@@ -5188,24 +5270,24 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
@@ -5222,7 +5304,7 @@
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:5">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
@@ -5239,7 +5321,7 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:5">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
@@ -5256,7 +5338,7 @@
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B5" t="s">
@@ -5273,7 +5355,7 @@
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:5">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B6" t="s">
@@ -5290,7 +5372,7 @@
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:5">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B7" t="s">
@@ -5307,7 +5389,7 @@
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:5">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B8" t="s">
@@ -5324,7 +5406,7 @@
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:5">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B9" t="s">
@@ -5341,7 +5423,7 @@
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:5">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B10" t="s">
@@ -5358,7 +5440,7 @@
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:5">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B11" t="s">
@@ -5375,7 +5457,7 @@
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:5">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B12" t="s">
@@ -5392,7 +5474,7 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:5">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="4" t="s">
         <v>50</v>
       </c>
       <c r="B13" t="s">
@@ -5409,7 +5491,7 @@
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:5">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B14" t="s">
@@ -5426,7 +5508,7 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:5">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B15" t="s">
@@ -5443,7 +5525,7 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:5">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="4" t="s">
         <v>62</v>
       </c>
       <c r="B16" t="s">
@@ -5460,7 +5542,7 @@
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:5">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="4" t="s">
         <v>66</v>
       </c>
       <c r="B17" t="s">
@@ -5477,7 +5559,7 @@
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:5">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B18" t="s">
@@ -5494,7 +5576,7 @@
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:5">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="4" t="s">
         <v>74</v>
       </c>
       <c r="B19" t="s">
@@ -5511,7 +5593,7 @@
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:5">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="4" t="s">
         <v>78</v>
       </c>
       <c r="B20" t="s">
@@ -5528,7 +5610,7 @@
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:5">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="4" t="s">
         <v>82</v>
       </c>
       <c r="B21" t="s">
@@ -5545,7 +5627,7 @@
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:5">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B22" t="s">
@@ -5562,7 +5644,7 @@
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:5">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="4" t="s">
         <v>90</v>
       </c>
       <c r="B23" t="s">
@@ -5579,7 +5661,7 @@
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:5">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B24" t="s">
@@ -5596,7 +5678,7 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:5">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="4" t="s">
         <v>98</v>
       </c>
       <c r="B25" t="s">
@@ -5613,7 +5695,7 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:5">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B26" t="s">
@@ -5630,7 +5712,7 @@
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:5">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="4" t="s">
         <v>106</v>
       </c>
       <c r="B27" t="s">
@@ -5647,7 +5729,7 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:5">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="4" t="s">
         <v>110</v>
       </c>
       <c r="B28" t="s">
@@ -5664,7 +5746,7 @@
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:5">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B29" t="s">
@@ -5681,7 +5763,7 @@
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:5">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B30" t="s">
@@ -5698,7 +5780,7 @@
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:5">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="4" t="s">
         <v>122</v>
       </c>
       <c r="B31" t="s">
@@ -5715,7 +5797,7 @@
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:5">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="4" t="s">
         <v>126</v>
       </c>
       <c r="B32" t="s">
@@ -5732,7 +5814,7 @@
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:5">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="4" t="s">
         <v>130</v>
       </c>
       <c r="B33" t="s">
@@ -5749,7 +5831,7 @@
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:5">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="4" t="s">
         <v>134</v>
       </c>
       <c r="B34" t="s">
@@ -5766,7 +5848,7 @@
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:5">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="4" t="s">
         <v>138</v>
       </c>
       <c r="B35" t="s">
@@ -5783,7 +5865,7 @@
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:5">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="4" t="s">
         <v>142</v>
       </c>
       <c r="B36" t="s">
@@ -5800,7 +5882,7 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:5">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="4" t="s">
         <v>146</v>
       </c>
       <c r="B37" t="s">
@@ -5817,7 +5899,7 @@
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:5">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="4" t="s">
         <v>150</v>
       </c>
       <c r="B38" t="s">
@@ -5834,7 +5916,7 @@
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:5">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="4" t="s">
         <v>154</v>
       </c>
       <c r="B39" t="s">
@@ -5851,7 +5933,7 @@
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:5">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="4" t="s">
         <v>158</v>
       </c>
       <c r="B40" t="s">
@@ -5868,7 +5950,7 @@
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:5">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="4" t="s">
         <v>162</v>
       </c>
       <c r="B41" t="s">
@@ -5885,7 +5967,7 @@
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:5">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="4" t="s">
         <v>166</v>
       </c>
       <c r="B42" t="s">
@@ -5902,7 +5984,7 @@
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:5">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="4" t="s">
         <v>170</v>
       </c>
       <c r="B43" t="s">
@@ -5919,7 +6001,7 @@
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:5">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="4" t="s">
         <v>174</v>
       </c>
       <c r="B44" t="s">
@@ -5936,7 +6018,7 @@
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:5">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="4" t="s">
         <v>178</v>
       </c>
       <c r="B45" t="s">
@@ -5953,7 +6035,7 @@
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:5">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="4" t="s">
         <v>182</v>
       </c>
       <c r="B46" t="s">
@@ -5970,7 +6052,7 @@
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:5">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="4" t="s">
         <v>186</v>
       </c>
       <c r="B47" t="s">
@@ -5987,7 +6069,7 @@
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:5">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="4" t="s">
         <v>190</v>
       </c>
       <c r="B48" t="s">
@@ -6004,7 +6086,7 @@
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:5">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="4" t="s">
         <v>194</v>
       </c>
       <c r="B49" t="s">
@@ -6021,7 +6103,7 @@
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:5">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="4" t="s">
         <v>198</v>
       </c>
       <c r="B50" t="s">
@@ -6038,7 +6120,7 @@
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:5">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="4" t="s">
         <v>202</v>
       </c>
       <c r="B51" t="s">
@@ -6055,7 +6137,7 @@
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:5">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="4" t="s">
         <v>206</v>
       </c>
       <c r="B52" t="s">
@@ -6072,7 +6154,7 @@
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:5">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="4" t="s">
         <v>210</v>
       </c>
       <c r="B53" t="s">
@@ -6089,7 +6171,7 @@
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:5">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="4" t="s">
         <v>214</v>
       </c>
       <c r="B54" t="s">
@@ -6106,7 +6188,7 @@
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:5">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="4" t="s">
         <v>218</v>
       </c>
       <c r="B55" t="s">
@@ -6123,7 +6205,7 @@
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:5">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="4" t="s">
         <v>222</v>
       </c>
       <c r="B56" t="s">
@@ -6140,7 +6222,7 @@
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:5">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="4" t="s">
         <v>226</v>
       </c>
       <c r="B57" t="s">
@@ -6157,7 +6239,7 @@
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:5">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="4" t="s">
         <v>230</v>
       </c>
       <c r="B58" t="s">
@@ -6174,7 +6256,7 @@
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:5">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="4" t="s">
         <v>234</v>
       </c>
       <c r="B59" t="s">
@@ -6191,7 +6273,7 @@
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:5">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="4" t="s">
         <v>238</v>
       </c>
       <c r="B60" t="s">
@@ -6208,7 +6290,7 @@
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:5">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="4" t="s">
         <v>242</v>
       </c>
       <c r="B61" t="s">
@@ -6225,7 +6307,7 @@
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:5">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="4" t="s">
         <v>246</v>
       </c>
       <c r="B62" t="s">
@@ -6242,7 +6324,7 @@
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:5">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="4" t="s">
         <v>250</v>
       </c>
       <c r="B63" t="s">
@@ -6259,7 +6341,7 @@
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:5">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="4" t="s">
         <v>254</v>
       </c>
       <c r="B64" t="s">
@@ -6276,7 +6358,7 @@
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:5">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="4" t="s">
         <v>258</v>
       </c>
       <c r="B65" t="s">
@@ -6293,7 +6375,7 @@
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:5">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="4" t="s">
         <v>262</v>
       </c>
       <c r="B66" t="s">
@@ -6310,7 +6392,7 @@
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:5">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="4" t="s">
         <v>266</v>
       </c>
       <c r="B67" t="s">
@@ -6327,7 +6409,7 @@
       </c>
     </row>
     <row r="68" customHeight="1" spans="1:5">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="4" t="s">
         <v>270</v>
       </c>
       <c r="B68" t="s">
@@ -6344,7 +6426,7 @@
       </c>
     </row>
     <row r="69" customHeight="1" spans="1:5">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="4" t="s">
         <v>274</v>
       </c>
       <c r="B69" t="s">
@@ -6361,7 +6443,7 @@
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:5">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="4" t="s">
         <v>278</v>
       </c>
       <c r="B70" t="s">
@@ -6378,7 +6460,7 @@
       </c>
     </row>
     <row r="71" customHeight="1" spans="1:5">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="4" t="s">
         <v>282</v>
       </c>
       <c r="B71" t="s">
@@ -6395,7 +6477,7 @@
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:5">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="4" t="s">
         <v>286</v>
       </c>
       <c r="B72" t="s">
@@ -6412,7 +6494,7 @@
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:5">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="4" t="s">
         <v>290</v>
       </c>
       <c r="B73" t="s">
@@ -6429,7 +6511,7 @@
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:5">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="4" t="s">
         <v>294</v>
       </c>
       <c r="B74" t="s">
@@ -6446,7 +6528,7 @@
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:5">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="4" t="s">
         <v>298</v>
       </c>
       <c r="B75" t="s">
@@ -6463,7 +6545,7 @@
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:5">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="4" t="s">
         <v>302</v>
       </c>
       <c r="B76" t="s">
@@ -6480,7 +6562,7 @@
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:5">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="4" t="s">
         <v>306</v>
       </c>
       <c r="B77" t="s">
@@ -6497,7 +6579,7 @@
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:5">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="4" t="s">
         <v>310</v>
       </c>
       <c r="B78" t="s">
@@ -6514,7 +6596,7 @@
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:5">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="4" t="s">
         <v>314</v>
       </c>
       <c r="B79" t="s">
@@ -6531,7 +6613,7 @@
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:5">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="4" t="s">
         <v>318</v>
       </c>
       <c r="B80" t="s">
@@ -6548,7 +6630,7 @@
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:5">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="4" t="s">
         <v>323</v>
       </c>
       <c r="B81" t="s">
@@ -6565,7 +6647,7 @@
       </c>
     </row>
     <row r="82" customHeight="1" spans="1:5">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="4" t="s">
         <v>327</v>
       </c>
       <c r="B82" t="s">
@@ -6582,7 +6664,7 @@
       </c>
     </row>
     <row r="83" customHeight="1" spans="1:5">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="4" t="s">
         <v>331</v>
       </c>
       <c r="B83" t="s">
@@ -6599,7 +6681,7 @@
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:5">
-      <c r="A84" s="1" t="s">
+      <c r="A84" s="4" t="s">
         <v>335</v>
       </c>
       <c r="B84" t="s">
@@ -6616,7 +6698,7 @@
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:5">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="4" t="s">
         <v>339</v>
       </c>
       <c r="B85" t="s">
@@ -6633,7 +6715,7 @@
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:5">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="4" t="s">
         <v>343</v>
       </c>
       <c r="B86" t="s">
@@ -6650,7 +6732,7 @@
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:5">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="4" t="s">
         <v>347</v>
       </c>
       <c r="B87" t="s">
@@ -6667,7 +6749,7 @@
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:5">
-      <c r="A88" s="1" t="s">
+      <c r="A88" s="4" t="s">
         <v>351</v>
       </c>
       <c r="B88" t="s">
@@ -6684,7 +6766,7 @@
       </c>
     </row>
     <row r="89" customHeight="1" spans="1:5">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="4" t="s">
         <v>355</v>
       </c>
       <c r="B89" t="s">
@@ -6701,7 +6783,7 @@
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:5">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="4" t="s">
         <v>359</v>
       </c>
       <c r="B90" t="s">
@@ -6718,7 +6800,7 @@
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:5">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B91" t="s">
@@ -6735,7 +6817,7 @@
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:5">
-      <c r="A92" s="1" t="s">
+      <c r="A92" s="4" t="s">
         <v>366</v>
       </c>
       <c r="B92" t="s">
@@ -6752,7 +6834,7 @@
       </c>
     </row>
     <row r="93" customHeight="1" spans="1:5">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="4" t="s">
         <v>370</v>
       </c>
       <c r="B93" t="s">
@@ -6769,7 +6851,7 @@
       </c>
     </row>
     <row r="94" customHeight="1" spans="1:5">
-      <c r="A94" s="1" t="s">
+      <c r="A94" s="4" t="s">
         <v>374</v>
       </c>
       <c r="B94" t="s">
@@ -6786,7 +6868,7 @@
       </c>
     </row>
     <row r="95" customHeight="1" spans="1:5">
-      <c r="A95" s="1" t="s">
+      <c r="A95" s="4" t="s">
         <v>378</v>
       </c>
       <c r="B95" t="s">
@@ -6803,7 +6885,7 @@
       </c>
     </row>
     <row r="96" customHeight="1" spans="1:5">
-      <c r="A96" s="1" t="s">
+      <c r="A96" s="4" t="s">
         <v>382</v>
       </c>
       <c r="B96" t="s">
@@ -6820,7 +6902,7 @@
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:5">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="4" t="s">
         <v>386</v>
       </c>
       <c r="B97" t="s">
@@ -6837,7 +6919,7 @@
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:5">
-      <c r="A98" s="1" t="s">
+      <c r="A98" s="4" t="s">
         <v>390</v>
       </c>
       <c r="B98" t="s">
@@ -6854,7 +6936,7 @@
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:5">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="4" t="s">
         <v>394</v>
       </c>
       <c r="B99" t="s">
@@ -6871,7 +6953,7 @@
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:5">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="4" t="s">
         <v>398</v>
       </c>
       <c r="B100" t="s">
@@ -6888,7 +6970,7 @@
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:5">
-      <c r="A101" s="1" t="s">
+      <c r="A101" s="4" t="s">
         <v>402</v>
       </c>
       <c r="B101" t="s">
@@ -6905,7 +6987,7 @@
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:5">
-      <c r="A102" s="1" t="s">
+      <c r="A102" s="4" t="s">
         <v>406</v>
       </c>
       <c r="B102" t="s">
@@ -6922,7 +7004,7 @@
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:5">
-      <c r="A103" s="1" t="s">
+      <c r="A103" s="4" t="s">
         <v>410</v>
       </c>
       <c r="B103" t="s">
@@ -6939,7 +7021,7 @@
       </c>
     </row>
     <row r="104" customHeight="1" spans="1:5">
-      <c r="A104" s="1" t="s">
+      <c r="A104" s="4" t="s">
         <v>414</v>
       </c>
       <c r="B104" t="s">
@@ -6956,7 +7038,7 @@
       </c>
     </row>
     <row r="105" customHeight="1" spans="1:5">
-      <c r="A105" s="1" t="s">
+      <c r="A105" s="4" t="s">
         <v>418</v>
       </c>
       <c r="B105" t="s">
@@ -6973,7 +7055,7 @@
       </c>
     </row>
     <row r="106" customHeight="1" spans="1:5">
-      <c r="A106" s="1" t="s">
+      <c r="A106" s="4" t="s">
         <v>422</v>
       </c>
       <c r="B106" t="s">
@@ -6990,7 +7072,7 @@
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:5">
-      <c r="A107" s="1" t="s">
+      <c r="A107" s="4" t="s">
         <v>426</v>
       </c>
       <c r="B107" t="s">
@@ -7007,7 +7089,7 @@
       </c>
     </row>
     <row r="108" customHeight="1" spans="1:5">
-      <c r="A108" s="1" t="s">
+      <c r="A108" s="4" t="s">
         <v>430</v>
       </c>
       <c r="B108" t="s">
@@ -7024,7 +7106,7 @@
       </c>
     </row>
     <row r="109" customHeight="1" spans="1:5">
-      <c r="A109" s="1" t="s">
+      <c r="A109" s="4" t="s">
         <v>434</v>
       </c>
       <c r="B109" t="s">
@@ -7041,7 +7123,7 @@
       </c>
     </row>
     <row r="110" customHeight="1" spans="1:5">
-      <c r="A110" s="1" t="s">
+      <c r="A110" s="4" t="s">
         <v>438</v>
       </c>
       <c r="B110" t="s">
@@ -7058,7 +7140,7 @@
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:5">
-      <c r="A111" s="1" t="s">
+      <c r="A111" s="4" t="s">
         <v>442</v>
       </c>
       <c r="B111" t="s">
@@ -7075,7 +7157,7 @@
       </c>
     </row>
     <row r="112" customHeight="1" spans="1:5">
-      <c r="A112" s="1" t="s">
+      <c r="A112" s="4" t="s">
         <v>446</v>
       </c>
       <c r="B112" t="s">
@@ -7092,7 +7174,7 @@
       </c>
     </row>
     <row r="113" customHeight="1" spans="1:5">
-      <c r="A113" s="1" t="s">
+      <c r="A113" s="4" t="s">
         <v>450</v>
       </c>
       <c r="B113" t="s">
@@ -7109,7 +7191,7 @@
       </c>
     </row>
     <row r="114" customHeight="1" spans="1:5">
-      <c r="A114" s="1" t="s">
+      <c r="A114" s="4" t="s">
         <v>454</v>
       </c>
       <c r="B114" t="s">
@@ -7126,7 +7208,7 @@
       </c>
     </row>
     <row r="115" customHeight="1" spans="1:5">
-      <c r="A115" s="1" t="s">
+      <c r="A115" s="4" t="s">
         <v>458</v>
       </c>
       <c r="B115" t="s">
@@ -7143,7 +7225,7 @@
       </c>
     </row>
     <row r="116" customHeight="1" spans="1:5">
-      <c r="A116" s="1" t="s">
+      <c r="A116" s="4" t="s">
         <v>463</v>
       </c>
       <c r="B116" t="s">
@@ -7160,7 +7242,7 @@
       </c>
     </row>
     <row r="117" customHeight="1" spans="1:5">
-      <c r="A117" s="1" t="s">
+      <c r="A117" s="4" t="s">
         <v>467</v>
       </c>
       <c r="B117" t="s">
@@ -7177,7 +7259,7 @@
       </c>
     </row>
     <row r="118" customHeight="1" spans="1:5">
-      <c r="A118" s="1" t="s">
+      <c r="A118" s="4" t="s">
         <v>471</v>
       </c>
       <c r="B118" t="s">
@@ -7194,7 +7276,7 @@
       </c>
     </row>
     <row r="119" customHeight="1" spans="1:5">
-      <c r="A119" s="1" t="s">
+      <c r="A119" s="4" t="s">
         <v>475</v>
       </c>
       <c r="B119" t="s">
@@ -7211,7 +7293,7 @@
       </c>
     </row>
     <row r="120" customHeight="1" spans="1:5">
-      <c r="A120" s="1" t="s">
+      <c r="A120" s="4" t="s">
         <v>479</v>
       </c>
       <c r="B120" t="s">
@@ -7228,7 +7310,7 @@
       </c>
     </row>
     <row r="121" customHeight="1" spans="1:5">
-      <c r="A121" s="1" t="s">
+      <c r="A121" s="4" t="s">
         <v>484</v>
       </c>
       <c r="B121" t="s">
@@ -7245,7 +7327,7 @@
       </c>
     </row>
     <row r="122" customHeight="1" spans="1:5">
-      <c r="A122" s="1" t="s">
+      <c r="A122" s="4" t="s">
         <v>488</v>
       </c>
       <c r="B122" t="s">
@@ -7262,7 +7344,7 @@
       </c>
     </row>
     <row r="123" customHeight="1" spans="1:5">
-      <c r="A123" s="1" t="s">
+      <c r="A123" s="4" t="s">
         <v>492</v>
       </c>
       <c r="B123" t="s">
@@ -7279,7 +7361,7 @@
       </c>
     </row>
     <row r="124" customHeight="1" spans="1:5">
-      <c r="A124" s="1" t="s">
+      <c r="A124" s="4" t="s">
         <v>497</v>
       </c>
       <c r="B124" t="s">
@@ -7296,7 +7378,7 @@
       </c>
     </row>
     <row r="125" customHeight="1" spans="1:5">
-      <c r="A125" s="1" t="s">
+      <c r="A125" s="4" t="s">
         <v>501</v>
       </c>
       <c r="B125" t="s">
@@ -7313,7 +7395,7 @@
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:5">
-      <c r="A126" s="1" t="s">
+      <c r="A126" s="4" t="s">
         <v>505</v>
       </c>
       <c r="B126" t="s">
@@ -7330,7 +7412,7 @@
       </c>
     </row>
     <row r="127" customHeight="1" spans="1:5">
-      <c r="A127" s="1" t="s">
+      <c r="A127" s="4" t="s">
         <v>509</v>
       </c>
       <c r="B127" t="s">
@@ -7347,7 +7429,7 @@
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:5">
-      <c r="A128" s="1" t="s">
+      <c r="A128" s="4" t="s">
         <v>513</v>
       </c>
       <c r="B128" t="s">
@@ -7364,7 +7446,7 @@
       </c>
     </row>
     <row r="129" customHeight="1" spans="1:5">
-      <c r="A129" s="1" t="s">
+      <c r="A129" s="4" t="s">
         <v>517</v>
       </c>
       <c r="B129" t="s">
@@ -7381,7 +7463,7 @@
       </c>
     </row>
     <row r="130" customHeight="1" spans="1:5">
-      <c r="A130" s="1" t="s">
+      <c r="A130" s="4" t="s">
         <v>521</v>
       </c>
       <c r="B130" t="s">
@@ -7398,7 +7480,7 @@
       </c>
     </row>
     <row r="131" customHeight="1" spans="1:5">
-      <c r="A131" s="1" t="s">
+      <c r="A131" s="4" t="s">
         <v>525</v>
       </c>
       <c r="B131" t="s">
@@ -7415,7 +7497,7 @@
       </c>
     </row>
     <row r="132" customHeight="1" spans="1:5">
-      <c r="A132" s="1" t="s">
+      <c r="A132" s="4" t="s">
         <v>529</v>
       </c>
       <c r="B132" t="s">
@@ -7432,7 +7514,7 @@
       </c>
     </row>
     <row r="133" customHeight="1" spans="1:5">
-      <c r="A133" s="1" t="s">
+      <c r="A133" s="4" t="s">
         <v>533</v>
       </c>
       <c r="B133" t="s">
@@ -7449,7 +7531,7 @@
       </c>
     </row>
     <row r="134" customHeight="1" spans="1:5">
-      <c r="A134" s="1" t="s">
+      <c r="A134" s="4" t="s">
         <v>537</v>
       </c>
       <c r="B134" t="s">
@@ -7466,7 +7548,7 @@
       </c>
     </row>
     <row r="135" customHeight="1" spans="1:5">
-      <c r="A135" s="1" t="s">
+      <c r="A135" s="4" t="s">
         <v>541</v>
       </c>
       <c r="B135" t="s">
@@ -7483,7 +7565,7 @@
       </c>
     </row>
     <row r="136" customHeight="1" spans="1:5">
-      <c r="A136" s="1" t="s">
+      <c r="A136" s="4" t="s">
         <v>545</v>
       </c>
       <c r="B136" t="s">
@@ -7500,7 +7582,7 @@
       </c>
     </row>
     <row r="137" customHeight="1" spans="1:5">
-      <c r="A137" s="1" t="s">
+      <c r="A137" s="4" t="s">
         <v>549</v>
       </c>
       <c r="B137" t="s">
@@ -7517,7 +7599,7 @@
       </c>
     </row>
     <row r="138" customHeight="1" spans="1:5">
-      <c r="A138" s="1" t="s">
+      <c r="A138" s="4" t="s">
         <v>553</v>
       </c>
       <c r="B138" t="s">
@@ -7534,7 +7616,7 @@
       </c>
     </row>
     <row r="139" customHeight="1" spans="1:5">
-      <c r="A139" s="1" t="s">
+      <c r="A139" s="4" t="s">
         <v>557</v>
       </c>
       <c r="B139" t="s">
@@ -7551,7 +7633,7 @@
       </c>
     </row>
     <row r="140" customHeight="1" spans="1:5">
-      <c r="A140" s="1" t="s">
+      <c r="A140" s="4" t="s">
         <v>561</v>
       </c>
       <c r="B140" t="s">
@@ -7568,7 +7650,7 @@
       </c>
     </row>
     <row r="141" customHeight="1" spans="1:5">
-      <c r="A141" s="1" t="s">
+      <c r="A141" s="4" t="s">
         <v>565</v>
       </c>
       <c r="B141" t="s">
@@ -7585,7 +7667,7 @@
       </c>
     </row>
     <row r="142" customHeight="1" spans="1:5">
-      <c r="A142" s="1" t="s">
+      <c r="A142" s="4" t="s">
         <v>569</v>
       </c>
       <c r="B142" t="s">
@@ -7602,7 +7684,7 @@
       </c>
     </row>
     <row r="143" customHeight="1" spans="1:5">
-      <c r="A143" s="1" t="s">
+      <c r="A143" s="4" t="s">
         <v>573</v>
       </c>
       <c r="B143" t="s">
@@ -7619,7 +7701,7 @@
       </c>
     </row>
     <row r="144" customHeight="1" spans="1:5">
-      <c r="A144" s="1" t="s">
+      <c r="A144" s="4" t="s">
         <v>577</v>
       </c>
       <c r="B144" t="s">
@@ -7636,7 +7718,7 @@
       </c>
     </row>
     <row r="145" customHeight="1" spans="1:5">
-      <c r="A145" s="1" t="s">
+      <c r="A145" s="4" t="s">
         <v>581</v>
       </c>
       <c r="B145" t="s">
@@ -7653,7 +7735,7 @@
       </c>
     </row>
     <row r="146" customHeight="1" spans="1:5">
-      <c r="A146" s="1" t="s">
+      <c r="A146" s="4" t="s">
         <v>585</v>
       </c>
       <c r="B146" t="s">
@@ -7670,7 +7752,7 @@
       </c>
     </row>
     <row r="147" customHeight="1" spans="1:5">
-      <c r="A147" s="1" t="s">
+      <c r="A147" s="4" t="s">
         <v>589</v>
       </c>
       <c r="B147" t="s">
@@ -7687,7 +7769,7 @@
       </c>
     </row>
     <row r="148" customHeight="1" spans="1:5">
-      <c r="A148" s="1" t="s">
+      <c r="A148" s="4" t="s">
         <v>593</v>
       </c>
       <c r="B148" t="s">
@@ -7704,7 +7786,7 @@
       </c>
     </row>
     <row r="149" customHeight="1" spans="1:5">
-      <c r="A149" s="1" t="s">
+      <c r="A149" s="4" t="s">
         <v>597</v>
       </c>
       <c r="B149" t="s">
@@ -7721,7 +7803,7 @@
       </c>
     </row>
     <row r="150" customHeight="1" spans="1:5">
-      <c r="A150" s="1" t="s">
+      <c r="A150" s="4" t="s">
         <v>601</v>
       </c>
       <c r="B150" t="s">
@@ -7738,7 +7820,7 @@
       </c>
     </row>
     <row r="151" customHeight="1" spans="1:5">
-      <c r="A151" s="1" t="s">
+      <c r="A151" s="4" t="s">
         <v>605</v>
       </c>
       <c r="B151" t="s">
@@ -7755,7 +7837,7 @@
       </c>
     </row>
     <row r="152" customHeight="1" spans="1:5">
-      <c r="A152" s="1" t="s">
+      <c r="A152" s="4" t="s">
         <v>609</v>
       </c>
       <c r="B152" t="s">
@@ -7772,7 +7854,7 @@
       </c>
     </row>
     <row r="153" customHeight="1" spans="1:5">
-      <c r="A153" s="1" t="s">
+      <c r="A153" s="4" t="s">
         <v>613</v>
       </c>
       <c r="B153" t="s">
@@ -7789,7 +7871,7 @@
       </c>
     </row>
     <row r="154" customHeight="1" spans="1:5">
-      <c r="A154" s="1" t="s">
+      <c r="A154" s="4" t="s">
         <v>617</v>
       </c>
       <c r="B154" t="s">
@@ -7806,7 +7888,7 @@
       </c>
     </row>
     <row r="155" customHeight="1" spans="1:5">
-      <c r="A155" s="1" t="s">
+      <c r="A155" s="4" t="s">
         <v>621</v>
       </c>
       <c r="B155" t="s">
@@ -7823,7 +7905,7 @@
       </c>
     </row>
     <row r="156" customHeight="1" spans="1:5">
-      <c r="A156" s="1" t="s">
+      <c r="A156" s="4" t="s">
         <v>625</v>
       </c>
       <c r="B156" t="s">
@@ -7840,7 +7922,7 @@
       </c>
     </row>
     <row r="157" customHeight="1" spans="1:5">
-      <c r="A157" s="1" t="s">
+      <c r="A157" s="4" t="s">
         <v>629</v>
       </c>
       <c r="B157" t="s">
@@ -7857,7 +7939,7 @@
       </c>
     </row>
     <row r="158" customHeight="1" spans="1:5">
-      <c r="A158" s="1" t="s">
+      <c r="A158" s="4" t="s">
         <v>633</v>
       </c>
       <c r="B158" t="s">
@@ -7874,7 +7956,7 @@
       </c>
     </row>
     <row r="159" customHeight="1" spans="1:5">
-      <c r="A159" s="1" t="s">
+      <c r="A159" s="4" t="s">
         <v>637</v>
       </c>
       <c r="B159" t="s">
@@ -7891,7 +7973,7 @@
       </c>
     </row>
     <row r="160" customHeight="1" spans="1:5">
-      <c r="A160" s="1" t="s">
+      <c r="A160" s="4" t="s">
         <v>641</v>
       </c>
       <c r="B160" t="s">
@@ -7908,7 +7990,7 @@
       </c>
     </row>
     <row r="161" customHeight="1" spans="1:5">
-      <c r="A161" s="1" t="s">
+      <c r="A161" s="4" t="s">
         <v>645</v>
       </c>
       <c r="B161" t="s">
@@ -7925,7 +8007,7 @@
       </c>
     </row>
     <row r="162" customHeight="1" spans="1:5">
-      <c r="A162" s="1" t="s">
+      <c r="A162" s="4" t="s">
         <v>649</v>
       </c>
       <c r="B162" t="s">
@@ -7942,7 +8024,7 @@
       </c>
     </row>
     <row r="163" customHeight="1" spans="1:5">
-      <c r="A163" s="1" t="s">
+      <c r="A163" s="4" t="s">
         <v>653</v>
       </c>
       <c r="B163" t="s">
@@ -7959,7 +8041,7 @@
       </c>
     </row>
     <row r="164" customHeight="1" spans="1:5">
-      <c r="A164" s="1" t="s">
+      <c r="A164" s="4" t="s">
         <v>657</v>
       </c>
       <c r="B164" t="s">
@@ -7976,7 +8058,7 @@
       </c>
     </row>
     <row r="165" customHeight="1" spans="1:5">
-      <c r="A165" s="1" t="s">
+      <c r="A165" s="4" t="s">
         <v>661</v>
       </c>
       <c r="B165" t="s">
@@ -7993,7 +8075,7 @@
       </c>
     </row>
     <row r="166" customHeight="1" spans="1:5">
-      <c r="A166" s="1" t="s">
+      <c r="A166" s="4" t="s">
         <v>665</v>
       </c>
       <c r="B166" t="s">
@@ -8010,7 +8092,7 @@
       </c>
     </row>
     <row r="167" customHeight="1" spans="1:5">
-      <c r="A167" s="1" t="s">
+      <c r="A167" s="4" t="s">
         <v>669</v>
       </c>
       <c r="B167" t="s">
@@ -8027,7 +8109,7 @@
       </c>
     </row>
     <row r="168" customHeight="1" spans="1:5">
-      <c r="A168" s="1" t="s">
+      <c r="A168" s="4" t="s">
         <v>673</v>
       </c>
       <c r="B168" t="s">
@@ -8044,7 +8126,7 @@
       </c>
     </row>
     <row r="169" customHeight="1" spans="1:5">
-      <c r="A169" s="1" t="s">
+      <c r="A169" s="4" t="s">
         <v>677</v>
       </c>
       <c r="B169" t="s">
@@ -8061,7 +8143,7 @@
       </c>
     </row>
     <row r="170" customHeight="1" spans="1:5">
-      <c r="A170" s="1" t="s">
+      <c r="A170" s="4" t="s">
         <v>681</v>
       </c>
       <c r="B170" t="s">
@@ -8078,7 +8160,7 @@
       </c>
     </row>
     <row r="171" customHeight="1" spans="1:5">
-      <c r="A171" s="1" t="s">
+      <c r="A171" s="4" t="s">
         <v>685</v>
       </c>
       <c r="B171" t="s">
@@ -8095,7 +8177,7 @@
       </c>
     </row>
     <row r="172" customHeight="1" spans="1:5">
-      <c r="A172" s="1" t="s">
+      <c r="A172" s="4" t="s">
         <v>689</v>
       </c>
       <c r="B172" t="s">
@@ -8112,7 +8194,7 @@
       </c>
     </row>
     <row r="173" customHeight="1" spans="1:5">
-      <c r="A173" s="1" t="s">
+      <c r="A173" s="4" t="s">
         <v>693</v>
       </c>
       <c r="B173" t="s">
@@ -8129,7 +8211,7 @@
       </c>
     </row>
     <row r="174" customHeight="1" spans="1:5">
-      <c r="A174" s="1" t="s">
+      <c r="A174" s="4" t="s">
         <v>697</v>
       </c>
       <c r="B174" t="s">
@@ -8146,7 +8228,7 @@
       </c>
     </row>
     <row r="175" customHeight="1" spans="1:5">
-      <c r="A175" s="1" t="s">
+      <c r="A175" s="4" t="s">
         <v>701</v>
       </c>
       <c r="B175" t="s">
@@ -8163,7 +8245,7 @@
       </c>
     </row>
     <row r="176" customHeight="1" spans="1:5">
-      <c r="A176" s="1" t="s">
+      <c r="A176" s="4" t="s">
         <v>705</v>
       </c>
       <c r="B176" t="s">
@@ -8180,7 +8262,7 @@
       </c>
     </row>
     <row r="177" customHeight="1" spans="1:5">
-      <c r="A177" s="1" t="s">
+      <c r="A177" s="4" t="s">
         <v>709</v>
       </c>
       <c r="B177" t="s">
@@ -8197,7 +8279,7 @@
       </c>
     </row>
     <row r="178" customHeight="1" spans="1:5">
-      <c r="A178" s="1" t="s">
+      <c r="A178" s="4" t="s">
         <v>713</v>
       </c>
       <c r="B178" t="s">
@@ -8214,7 +8296,7 @@
       </c>
     </row>
     <row r="179" customHeight="1" spans="1:5">
-      <c r="A179" s="1" t="s">
+      <c r="A179" s="4" t="s">
         <v>717</v>
       </c>
       <c r="B179" t="s">
@@ -8231,7 +8313,7 @@
       </c>
     </row>
     <row r="180" customHeight="1" spans="1:5">
-      <c r="A180" s="1" t="s">
+      <c r="A180" s="4" t="s">
         <v>721</v>
       </c>
       <c r="B180" t="s">
@@ -8248,7 +8330,7 @@
       </c>
     </row>
     <row r="181" customHeight="1" spans="1:5">
-      <c r="A181" s="1" t="s">
+      <c r="A181" s="4" t="s">
         <v>725</v>
       </c>
       <c r="B181" t="s">
@@ -8265,7 +8347,7 @@
       </c>
     </row>
     <row r="182" customHeight="1" spans="1:5">
-      <c r="A182" s="1" t="s">
+      <c r="A182" s="4" t="s">
         <v>729</v>
       </c>
       <c r="B182" t="s">
@@ -8282,7 +8364,7 @@
       </c>
     </row>
     <row r="183" customHeight="1" spans="1:5">
-      <c r="A183" s="1" t="s">
+      <c r="A183" s="4" t="s">
         <v>733</v>
       </c>
       <c r="B183" t="s">
@@ -8299,7 +8381,7 @@
       </c>
     </row>
     <row r="184" customHeight="1" spans="1:5">
-      <c r="A184" s="1" t="s">
+      <c r="A184" s="4" t="s">
         <v>737</v>
       </c>
       <c r="B184" t="s">
@@ -8316,7 +8398,7 @@
       </c>
     </row>
     <row r="185" customHeight="1" spans="1:5">
-      <c r="A185" s="1" t="s">
+      <c r="A185" s="4" t="s">
         <v>741</v>
       </c>
       <c r="B185" t="s">
@@ -8333,7 +8415,7 @@
       </c>
     </row>
     <row r="186" customHeight="1" spans="1:5">
-      <c r="A186" s="1" t="s">
+      <c r="A186" s="4" t="s">
         <v>745</v>
       </c>
       <c r="B186" t="s">
@@ -8350,7 +8432,7 @@
       </c>
     </row>
     <row r="187" customHeight="1" spans="1:5">
-      <c r="A187" s="1" t="s">
+      <c r="A187" s="4" t="s">
         <v>750</v>
       </c>
       <c r="B187" t="s">
@@ -8367,7 +8449,7 @@
       </c>
     </row>
     <row r="188" customHeight="1" spans="1:5">
-      <c r="A188" s="1" t="s">
+      <c r="A188" s="4" t="s">
         <v>754</v>
       </c>
       <c r="B188" t="s">
@@ -8384,7 +8466,7 @@
       </c>
     </row>
     <row r="189" customHeight="1" spans="1:5">
-      <c r="A189" s="1" t="s">
+      <c r="A189" s="4" t="s">
         <v>758</v>
       </c>
       <c r="B189" t="s">
@@ -8401,7 +8483,7 @@
       </c>
     </row>
     <row r="190" customHeight="1" spans="1:5">
-      <c r="A190" s="1" t="s">
+      <c r="A190" s="4" t="s">
         <v>762</v>
       </c>
       <c r="B190" t="s">
@@ -8418,7 +8500,7 @@
       </c>
     </row>
     <row r="191" customHeight="1" spans="1:5">
-      <c r="A191" s="1" t="s">
+      <c r="A191" s="4" t="s">
         <v>766</v>
       </c>
       <c r="B191" t="s">
@@ -8435,7 +8517,7 @@
       </c>
     </row>
     <row r="192" customHeight="1" spans="1:5">
-      <c r="A192" s="1" t="s">
+      <c r="A192" s="4" t="s">
         <v>770</v>
       </c>
       <c r="B192" t="s">
@@ -8452,7 +8534,7 @@
       </c>
     </row>
     <row r="193" customHeight="1" spans="1:5">
-      <c r="A193" s="1" t="s">
+      <c r="A193" s="4" t="s">
         <v>774</v>
       </c>
       <c r="B193" t="s">
@@ -8469,7 +8551,7 @@
       </c>
     </row>
     <row r="194" customHeight="1" spans="1:5">
-      <c r="A194" s="1" t="s">
+      <c r="A194" s="4" t="s">
         <v>778</v>
       </c>
       <c r="B194" t="s">
@@ -8486,7 +8568,7 @@
       </c>
     </row>
     <row r="195" customHeight="1" spans="1:5">
-      <c r="A195" s="1" t="s">
+      <c r="A195" s="4" t="s">
         <v>782</v>
       </c>
       <c r="B195" t="s">
@@ -8503,7 +8585,7 @@
       </c>
     </row>
     <row r="196" customHeight="1" spans="1:5">
-      <c r="A196" s="1" t="s">
+      <c r="A196" s="4" t="s">
         <v>786</v>
       </c>
       <c r="B196" t="s">
@@ -8520,7 +8602,7 @@
       </c>
     </row>
     <row r="197" customHeight="1" spans="1:5">
-      <c r="A197" s="1" t="s">
+      <c r="A197" s="4" t="s">
         <v>790</v>
       </c>
       <c r="B197" t="s">
@@ -8537,7 +8619,7 @@
       </c>
     </row>
     <row r="198" customHeight="1" spans="1:5">
-      <c r="A198" s="1" t="s">
+      <c r="A198" s="4" t="s">
         <v>794</v>
       </c>
       <c r="B198" t="s">
@@ -8554,7 +8636,7 @@
       </c>
     </row>
     <row r="199" customHeight="1" spans="1:5">
-      <c r="A199" s="1" t="s">
+      <c r="A199" s="4" t="s">
         <v>799</v>
       </c>
       <c r="B199" t="s">
@@ -8571,7 +8653,7 @@
       </c>
     </row>
     <row r="200" customHeight="1" spans="1:5">
-      <c r="A200" s="1" t="s">
+      <c r="A200" s="4" t="s">
         <v>803</v>
       </c>
       <c r="B200" t="s">
@@ -8588,7 +8670,7 @@
       </c>
     </row>
     <row r="201" customHeight="1" spans="1:5">
-      <c r="A201" s="1" t="s">
+      <c r="A201" s="4" t="s">
         <v>807</v>
       </c>
       <c r="B201" t="s">
@@ -8605,7 +8687,7 @@
       </c>
     </row>
     <row r="202" customHeight="1" spans="1:5">
-      <c r="A202" s="1" t="s">
+      <c r="A202" s="4" t="s">
         <v>811</v>
       </c>
       <c r="B202" t="s">
@@ -8622,7 +8704,7 @@
       </c>
     </row>
     <row r="203" customHeight="1" spans="1:5">
-      <c r="A203" s="1" t="s">
+      <c r="A203" s="4" t="s">
         <v>815</v>
       </c>
       <c r="B203" t="s">
@@ -8639,7 +8721,7 @@
       </c>
     </row>
     <row r="204" customHeight="1" spans="1:5">
-      <c r="A204" s="1" t="s">
+      <c r="A204" s="4" t="s">
         <v>819</v>
       </c>
       <c r="B204" t="s">
@@ -8656,7 +8738,7 @@
       </c>
     </row>
     <row r="205" customHeight="1" spans="1:5">
-      <c r="A205" s="1" t="s">
+      <c r="A205" s="4" t="s">
         <v>823</v>
       </c>
       <c r="B205" t="s">
@@ -8673,7 +8755,7 @@
       </c>
     </row>
     <row r="206" customHeight="1" spans="1:5">
-      <c r="A206" s="1" t="s">
+      <c r="A206" s="4" t="s">
         <v>827</v>
       </c>
       <c r="B206" t="s">
@@ -8690,7 +8772,7 @@
       </c>
     </row>
     <row r="207" customHeight="1" spans="1:5">
-      <c r="A207" s="1" t="s">
+      <c r="A207" s="4" t="s">
         <v>831</v>
       </c>
       <c r="B207" t="s">
@@ -8707,7 +8789,7 @@
       </c>
     </row>
     <row r="208" customHeight="1" spans="1:5">
-      <c r="A208" s="1" t="s">
+      <c r="A208" s="4" t="s">
         <v>835</v>
       </c>
       <c r="B208" t="s">
@@ -8724,7 +8806,7 @@
       </c>
     </row>
     <row r="209" customHeight="1" spans="1:5">
-      <c r="A209" s="1" t="s">
+      <c r="A209" s="4" t="s">
         <v>839</v>
       </c>
       <c r="B209" t="s">
@@ -8741,7 +8823,7 @@
       </c>
     </row>
     <row r="210" customHeight="1" spans="1:5">
-      <c r="A210" s="1" t="s">
+      <c r="A210" s="4" t="s">
         <v>843</v>
       </c>
       <c r="B210" t="s">
@@ -8758,7 +8840,7 @@
       </c>
     </row>
     <row r="211" customHeight="1" spans="1:5">
-      <c r="A211" s="1" t="s">
+      <c r="A211" s="4" t="s">
         <v>847</v>
       </c>
       <c r="B211" t="s">
@@ -8775,7 +8857,7 @@
       </c>
     </row>
     <row r="212" customHeight="1" spans="1:5">
-      <c r="A212" s="1" t="s">
+      <c r="A212" s="4" t="s">
         <v>851</v>
       </c>
       <c r="B212" t="s">
@@ -8792,7 +8874,7 @@
       </c>
     </row>
     <row r="213" customHeight="1" spans="1:5">
-      <c r="A213" s="1" t="s">
+      <c r="A213" s="4" t="s">
         <v>855</v>
       </c>
       <c r="B213" t="s">
@@ -8809,7 +8891,7 @@
       </c>
     </row>
     <row r="214" customHeight="1" spans="1:5">
-      <c r="A214" s="1" t="s">
+      <c r="A214" s="4" t="s">
         <v>859</v>
       </c>
       <c r="B214" t="s">
@@ -8826,7 +8908,7 @@
       </c>
     </row>
     <row r="215" customHeight="1" spans="1:5">
-      <c r="A215" s="1" t="s">
+      <c r="A215" s="4" t="s">
         <v>863</v>
       </c>
       <c r="B215" t="s">
@@ -8843,7 +8925,7 @@
       </c>
     </row>
     <row r="216" customHeight="1" spans="1:5">
-      <c r="A216" s="1" t="s">
+      <c r="A216" s="4" t="s">
         <v>867</v>
       </c>
       <c r="B216" t="s">
@@ -8860,7 +8942,7 @@
       </c>
     </row>
     <row r="217" customHeight="1" spans="1:5">
-      <c r="A217" s="1" t="s">
+      <c r="A217" s="4" t="s">
         <v>871</v>
       </c>
       <c r="B217" t="s">
@@ -8877,7 +8959,7 @@
       </c>
     </row>
     <row r="218" customHeight="1" spans="1:5">
-      <c r="A218" s="1" t="s">
+      <c r="A218" s="4" t="s">
         <v>875</v>
       </c>
       <c r="B218" t="s">
@@ -8894,7 +8976,7 @@
       </c>
     </row>
     <row r="219" customHeight="1" spans="1:5">
-      <c r="A219" s="1" t="s">
+      <c r="A219" s="4" t="s">
         <v>880</v>
       </c>
       <c r="B219" t="s">
@@ -8911,7 +8993,7 @@
       </c>
     </row>
     <row r="220" customHeight="1" spans="1:5">
-      <c r="A220" s="1" t="s">
+      <c r="A220" s="4" t="s">
         <v>884</v>
       </c>
       <c r="B220" t="s">
@@ -8928,7 +9010,7 @@
       </c>
     </row>
     <row r="221" customHeight="1" spans="1:5">
-      <c r="A221" s="1" t="s">
+      <c r="A221" s="4" t="s">
         <v>888</v>
       </c>
       <c r="B221" t="s">
@@ -8945,7 +9027,7 @@
       </c>
     </row>
     <row r="222" customHeight="1" spans="1:5">
-      <c r="A222" s="1" t="s">
+      <c r="A222" s="4" t="s">
         <v>892</v>
       </c>
       <c r="B222" t="s">
@@ -8962,7 +9044,7 @@
       </c>
     </row>
     <row r="223" customHeight="1" spans="1:5">
-      <c r="A223" s="1" t="s">
+      <c r="A223" s="4" t="s">
         <v>896</v>
       </c>
       <c r="B223" t="s">
@@ -8979,7 +9061,7 @@
       </c>
     </row>
     <row r="224" customHeight="1" spans="1:5">
-      <c r="A224" s="1" t="s">
+      <c r="A224" s="4" t="s">
         <v>900</v>
       </c>
       <c r="B224" t="s">
@@ -8996,7 +9078,7 @@
       </c>
     </row>
     <row r="225" customHeight="1" spans="1:5">
-      <c r="A225" s="1" t="s">
+      <c r="A225" s="4" t="s">
         <v>904</v>
       </c>
       <c r="B225" t="s">
@@ -9013,7 +9095,7 @@
       </c>
     </row>
     <row r="226" customHeight="1" spans="1:5">
-      <c r="A226" s="1" t="s">
+      <c r="A226" s="4" t="s">
         <v>909</v>
       </c>
       <c r="B226" t="s">
@@ -9030,7 +9112,7 @@
       </c>
     </row>
     <row r="227" customHeight="1" spans="1:5">
-      <c r="A227" s="1" t="s">
+      <c r="A227" s="4" t="s">
         <v>913</v>
       </c>
       <c r="B227" t="s">
@@ -9047,7 +9129,7 @@
       </c>
     </row>
     <row r="228" customHeight="1" spans="1:5">
-      <c r="A228" s="1" t="s">
+      <c r="A228" s="4" t="s">
         <v>918</v>
       </c>
       <c r="B228" t="s">
@@ -9064,7 +9146,7 @@
       </c>
     </row>
     <row r="229" customHeight="1" spans="1:5">
-      <c r="A229" s="1" t="s">
+      <c r="A229" s="4" t="s">
         <v>923</v>
       </c>
       <c r="B229" t="s">
@@ -9081,7 +9163,7 @@
       </c>
     </row>
     <row r="230" customHeight="1" spans="1:5">
-      <c r="A230" s="1" t="s">
+      <c r="A230" s="4" t="s">
         <v>927</v>
       </c>
       <c r="B230" t="s">
@@ -9098,7 +9180,7 @@
       </c>
     </row>
     <row r="231" customHeight="1" spans="1:5">
-      <c r="A231" s="1" t="s">
+      <c r="A231" s="4" t="s">
         <v>931</v>
       </c>
       <c r="B231" t="s">
@@ -9115,7 +9197,7 @@
       </c>
     </row>
     <row r="232" customHeight="1" spans="1:5">
-      <c r="A232" s="1" t="s">
+      <c r="A232" s="4" t="s">
         <v>935</v>
       </c>
       <c r="B232" t="s">
@@ -9132,7 +9214,7 @@
       </c>
     </row>
     <row r="233" customHeight="1" spans="1:5">
-      <c r="A233" s="1" t="s">
+      <c r="A233" s="4" t="s">
         <v>939</v>
       </c>
       <c r="B233" t="s">
@@ -9149,7 +9231,7 @@
       </c>
     </row>
     <row r="234" customHeight="1" spans="1:5">
-      <c r="A234" s="1" t="s">
+      <c r="A234" s="4" t="s">
         <v>943</v>
       </c>
       <c r="B234" t="s">
@@ -9166,7 +9248,7 @@
       </c>
     </row>
     <row r="235" customHeight="1" spans="1:5">
-      <c r="A235" s="1" t="s">
+      <c r="A235" s="4" t="s">
         <v>947</v>
       </c>
       <c r="B235" t="s">
@@ -9183,7 +9265,7 @@
       </c>
     </row>
     <row r="236" customHeight="1" spans="1:5">
-      <c r="A236" s="1" t="s">
+      <c r="A236" s="4" t="s">
         <v>951</v>
       </c>
       <c r="B236" t="s">
@@ -9200,7 +9282,7 @@
       </c>
     </row>
     <row r="237" customHeight="1" spans="1:5">
-      <c r="A237" s="1" t="s">
+      <c r="A237" s="4" t="s">
         <v>955</v>
       </c>
       <c r="B237" t="s">
@@ -9217,7 +9299,7 @@
       </c>
     </row>
     <row r="238" customHeight="1" spans="1:5">
-      <c r="A238" s="1" t="s">
+      <c r="A238" s="4" t="s">
         <v>959</v>
       </c>
       <c r="B238" t="s">
@@ -9234,7 +9316,7 @@
       </c>
     </row>
     <row r="239" customHeight="1" spans="1:5">
-      <c r="A239" s="1" t="s">
+      <c r="A239" s="4" t="s">
         <v>963</v>
       </c>
       <c r="B239" t="s">
@@ -9251,7 +9333,7 @@
       </c>
     </row>
     <row r="240" customHeight="1" spans="1:5">
-      <c r="A240" s="1" t="s">
+      <c r="A240" s="4" t="s">
         <v>967</v>
       </c>
       <c r="B240" t="s">
@@ -9268,7 +9350,7 @@
       </c>
     </row>
     <row r="241" customHeight="1" spans="1:5">
-      <c r="A241" s="1" t="s">
+      <c r="A241" s="4" t="s">
         <v>971</v>
       </c>
       <c r="B241" t="s">
@@ -9285,7 +9367,7 @@
       </c>
     </row>
     <row r="242" customHeight="1" spans="1:5">
-      <c r="A242" s="1" t="s">
+      <c r="A242" s="4" t="s">
         <v>975</v>
       </c>
       <c r="B242" t="s">
@@ -9302,7 +9384,7 @@
       </c>
     </row>
     <row r="243" customHeight="1" spans="1:5">
-      <c r="A243" s="1" t="s">
+      <c r="A243" s="4" t="s">
         <v>979</v>
       </c>
       <c r="B243" t="s">
@@ -9319,7 +9401,7 @@
       </c>
     </row>
     <row r="244" customHeight="1" spans="1:5">
-      <c r="A244" s="1" t="s">
+      <c r="A244" s="4" t="s">
         <v>983</v>
       </c>
       <c r="B244" t="s">
@@ -9336,7 +9418,7 @@
       </c>
     </row>
     <row r="245" customHeight="1" spans="1:5">
-      <c r="A245" s="1" t="s">
+      <c r="A245" s="4" t="s">
         <v>987</v>
       </c>
       <c r="B245" t="s">
@@ -9353,7 +9435,7 @@
       </c>
     </row>
     <row r="246" customHeight="1" spans="1:5">
-      <c r="A246" s="1" t="s">
+      <c r="A246" s="4" t="s">
         <v>992</v>
       </c>
       <c r="B246" t="s">
@@ -9370,7 +9452,7 @@
       </c>
     </row>
     <row r="247" customHeight="1" spans="1:5">
-      <c r="A247" s="1" t="s">
+      <c r="A247" s="4" t="s">
         <v>997</v>
       </c>
       <c r="B247" t="s">
@@ -9387,7 +9469,7 @@
       </c>
     </row>
     <row r="248" customHeight="1" spans="1:5">
-      <c r="A248" s="1" t="s">
+      <c r="A248" s="4" t="s">
         <v>1001</v>
       </c>
       <c r="B248" t="s">
@@ -9404,7 +9486,7 @@
       </c>
     </row>
     <row r="249" customHeight="1" spans="1:5">
-      <c r="A249" s="1" t="s">
+      <c r="A249" s="4" t="s">
         <v>1005</v>
       </c>
       <c r="B249" t="s">
@@ -9421,7 +9503,7 @@
       </c>
     </row>
     <row r="250" customHeight="1" spans="1:5">
-      <c r="A250" s="1" t="s">
+      <c r="A250" s="4" t="s">
         <v>1009</v>
       </c>
       <c r="B250" t="s">
@@ -9438,7 +9520,7 @@
       </c>
     </row>
     <row r="251" customHeight="1" spans="1:5">
-      <c r="A251" s="1" t="s">
+      <c r="A251" s="4" t="s">
         <v>1013</v>
       </c>
       <c r="B251" t="s">
@@ -9455,7 +9537,7 @@
       </c>
     </row>
     <row r="252" customHeight="1" spans="1:5">
-      <c r="A252" s="1" t="s">
+      <c r="A252" s="4" t="s">
         <v>1017</v>
       </c>
       <c r="B252" t="s">
@@ -9472,7 +9554,7 @@
       </c>
     </row>
     <row r="253" customHeight="1" spans="1:5">
-      <c r="A253" s="1" t="s">
+      <c r="A253" s="4" t="s">
         <v>1021</v>
       </c>
       <c r="B253" t="s">
@@ -9489,7 +9571,7 @@
       </c>
     </row>
     <row r="254" customHeight="1" spans="1:5">
-      <c r="A254" s="1" t="s">
+      <c r="A254" s="4" t="s">
         <v>1025</v>
       </c>
       <c r="B254" t="s">
@@ -9506,7 +9588,7 @@
       </c>
     </row>
     <row r="255" customHeight="1" spans="1:5">
-      <c r="A255" s="1" t="s">
+      <c r="A255" s="4" t="s">
         <v>1029</v>
       </c>
       <c r="B255" t="s">
@@ -9523,7 +9605,7 @@
       </c>
     </row>
     <row r="256" customHeight="1" spans="1:5">
-      <c r="A256" s="1" t="s">
+      <c r="A256" s="4" t="s">
         <v>1033</v>
       </c>
       <c r="B256" t="s">
@@ -9540,7 +9622,7 @@
       </c>
     </row>
     <row r="257" customHeight="1" spans="1:5">
-      <c r="A257" s="1" t="s">
+      <c r="A257" s="4" t="s">
         <v>1038</v>
       </c>
       <c r="B257" t="s">
@@ -9557,7 +9639,7 @@
       </c>
     </row>
     <row r="258" customHeight="1" spans="1:5">
-      <c r="A258" s="1" t="s">
+      <c r="A258" s="4" t="s">
         <v>1042</v>
       </c>
       <c r="B258" t="s">
@@ -9574,7 +9656,7 @@
       </c>
     </row>
     <row r="259" customHeight="1" spans="1:5">
-      <c r="A259" s="1" t="s">
+      <c r="A259" s="4" t="s">
         <v>1046</v>
       </c>
       <c r="B259" t="s">
@@ -9591,7 +9673,7 @@
       </c>
     </row>
     <row r="260" customHeight="1" spans="1:5">
-      <c r="A260" s="1" t="s">
+      <c r="A260" s="4" t="s">
         <v>1050</v>
       </c>
       <c r="B260" t="s">
@@ -9608,7 +9690,7 @@
       </c>
     </row>
     <row r="261" customHeight="1" spans="1:5">
-      <c r="A261" s="1" t="s">
+      <c r="A261" s="4" t="s">
         <v>1054</v>
       </c>
       <c r="B261" t="s">
@@ -9625,7 +9707,7 @@
       </c>
     </row>
     <row r="262" customHeight="1" spans="1:5">
-      <c r="A262" s="1" t="s">
+      <c r="A262" s="4" t="s">
         <v>1058</v>
       </c>
       <c r="B262" t="s">
@@ -9642,7 +9724,7 @@
       </c>
     </row>
     <row r="263" customHeight="1" spans="1:5">
-      <c r="A263" s="1" t="s">
+      <c r="A263" s="4" t="s">
         <v>1062</v>
       </c>
       <c r="B263" t="s">
@@ -9659,7 +9741,7 @@
       </c>
     </row>
     <row r="264" customHeight="1" spans="1:5">
-      <c r="A264" s="1" t="s">
+      <c r="A264" s="4" t="s">
         <v>1066</v>
       </c>
       <c r="B264" t="s">
@@ -9676,7 +9758,7 @@
       </c>
     </row>
     <row r="265" customHeight="1" spans="1:5">
-      <c r="A265" s="1" t="s">
+      <c r="A265" s="4" t="s">
         <v>1070</v>
       </c>
       <c r="B265" t="s">
@@ -9693,7 +9775,7 @@
       </c>
     </row>
     <row r="266" customHeight="1" spans="1:5">
-      <c r="A266" s="1" t="s">
+      <c r="A266" s="4" t="s">
         <v>1074</v>
       </c>
       <c r="B266" t="s">
@@ -9710,7 +9792,7 @@
       </c>
     </row>
     <row r="267" customHeight="1" spans="1:5">
-      <c r="A267" s="1" t="s">
+      <c r="A267" s="4" t="s">
         <v>1078</v>
       </c>
       <c r="B267" t="s">
@@ -9727,7 +9809,7 @@
       </c>
     </row>
     <row r="268" customHeight="1" spans="1:5">
-      <c r="A268" s="1" t="s">
+      <c r="A268" s="4" t="s">
         <v>1082</v>
       </c>
       <c r="B268" t="s">
@@ -9744,7 +9826,7 @@
       </c>
     </row>
     <row r="269" customHeight="1" spans="1:5">
-      <c r="A269" s="1" t="s">
+      <c r="A269" s="4" t="s">
         <v>1087</v>
       </c>
       <c r="B269" t="s">
@@ -9761,7 +9843,7 @@
       </c>
     </row>
     <row r="270" customHeight="1" spans="1:5">
-      <c r="A270" s="1" t="s">
+      <c r="A270" s="4" t="s">
         <v>1092</v>
       </c>
       <c r="B270" t="s">
@@ -9778,7 +9860,7 @@
       </c>
     </row>
     <row r="271" customHeight="1" spans="1:5">
-      <c r="A271" s="1" t="s">
+      <c r="A271" s="4" t="s">
         <v>1097</v>
       </c>
       <c r="B271" t="s">
@@ -9795,7 +9877,7 @@
       </c>
     </row>
     <row r="272" customHeight="1" spans="1:5">
-      <c r="A272" s="1" t="s">
+      <c r="A272" s="4" t="s">
         <v>1101</v>
       </c>
       <c r="B272" t="s">
@@ -9812,7 +9894,7 @@
       </c>
     </row>
     <row r="273" customHeight="1" spans="1:5">
-      <c r="A273" s="1" t="s">
+      <c r="A273" s="4" t="s">
         <v>1105</v>
       </c>
       <c r="B273" t="s">
@@ -9829,7 +9911,7 @@
       </c>
     </row>
     <row r="274" customHeight="1" spans="1:5">
-      <c r="A274" s="1" t="s">
+      <c r="A274" s="4" t="s">
         <v>1109</v>
       </c>
       <c r="B274" t="s">
@@ -9846,7 +9928,7 @@
       </c>
     </row>
     <row r="275" customHeight="1" spans="1:5">
-      <c r="A275" s="1" t="s">
+      <c r="A275" s="4" t="s">
         <v>1113</v>
       </c>
       <c r="B275" t="s">
@@ -9863,7 +9945,7 @@
       </c>
     </row>
     <row r="276" customHeight="1" spans="1:5">
-      <c r="A276" s="1" t="s">
+      <c r="A276" s="4" t="s">
         <v>1117</v>
       </c>
       <c r="B276" t="s">
@@ -9880,7 +9962,7 @@
       </c>
     </row>
     <row r="277" customHeight="1" spans="1:5">
-      <c r="A277" s="1" t="s">
+      <c r="A277" s="4" t="s">
         <v>1121</v>
       </c>
       <c r="B277" t="s">
@@ -9897,7 +9979,7 @@
       </c>
     </row>
     <row r="278" customHeight="1" spans="1:5">
-      <c r="A278" s="1" t="s">
+      <c r="A278" s="4" t="s">
         <v>1125</v>
       </c>
       <c r="B278" t="s">
@@ -9914,7 +9996,7 @@
       </c>
     </row>
     <row r="279" customHeight="1" spans="1:5">
-      <c r="A279" s="1" t="s">
+      <c r="A279" s="4" t="s">
         <v>1129</v>
       </c>
       <c r="B279" t="s">
@@ -9931,7 +10013,7 @@
       </c>
     </row>
     <row r="280" customHeight="1" spans="1:5">
-      <c r="A280" s="1" t="s">
+      <c r="A280" s="4" t="s">
         <v>1133</v>
       </c>
       <c r="B280" t="s">
@@ -9948,7 +10030,7 @@
       </c>
     </row>
     <row r="281" customHeight="1" spans="1:5">
-      <c r="A281" s="1" t="s">
+      <c r="A281" s="4" t="s">
         <v>1137</v>
       </c>
       <c r="B281" t="s">
@@ -9965,7 +10047,7 @@
       </c>
     </row>
     <row r="282" customHeight="1" spans="1:5">
-      <c r="A282" s="1" t="s">
+      <c r="A282" s="4" t="s">
         <v>1141</v>
       </c>
       <c r="B282" t="s">
@@ -9982,7 +10064,7 @@
       </c>
     </row>
     <row r="283" customHeight="1" spans="1:5">
-      <c r="A283" s="1" t="s">
+      <c r="A283" s="4" t="s">
         <v>1146</v>
       </c>
       <c r="B283" t="s">
@@ -9999,7 +10081,7 @@
       </c>
     </row>
     <row r="284" customHeight="1" spans="1:5">
-      <c r="A284" s="1" t="s">
+      <c r="A284" s="4" t="s">
         <v>1150</v>
       </c>
       <c r="B284" t="s">
@@ -10016,7 +10098,7 @@
       </c>
     </row>
     <row r="285" customHeight="1" spans="1:5">
-      <c r="A285" s="1" t="s">
+      <c r="A285" s="4" t="s">
         <v>1155</v>
       </c>
       <c r="B285" t="s">
@@ -10033,7 +10115,7 @@
       </c>
     </row>
     <row r="286" customHeight="1" spans="1:5">
-      <c r="A286" s="1" t="s">
+      <c r="A286" s="4" t="s">
         <v>1160</v>
       </c>
       <c r="B286" t="s">
@@ -10050,7 +10132,7 @@
       </c>
     </row>
     <row r="287" customHeight="1" spans="1:5">
-      <c r="A287" s="1" t="s">
+      <c r="A287" s="4" t="s">
         <v>1164</v>
       </c>
       <c r="B287" t="s">
@@ -10067,7 +10149,7 @@
       </c>
     </row>
     <row r="288" customHeight="1" spans="1:5">
-      <c r="A288" s="1" t="s">
+      <c r="A288" s="4" t="s">
         <v>1169</v>
       </c>
       <c r="B288" t="s">
@@ -10084,7 +10166,7 @@
       </c>
     </row>
     <row r="289" customHeight="1" spans="1:5">
-      <c r="A289" s="1" t="s">
+      <c r="A289" s="4" t="s">
         <v>1173</v>
       </c>
       <c r="B289" t="s">
@@ -10101,7 +10183,7 @@
       </c>
     </row>
     <row r="290" customHeight="1" spans="1:5">
-      <c r="A290" s="1" t="s">
+      <c r="A290" s="4" t="s">
         <v>1178</v>
       </c>
       <c r="B290" t="s">
@@ -10118,7 +10200,7 @@
       </c>
     </row>
     <row r="291" customHeight="1" spans="1:5">
-      <c r="A291" s="1" t="s">
+      <c r="A291" s="4" t="s">
         <v>1182</v>
       </c>
       <c r="B291" t="s">
@@ -10135,7 +10217,7 @@
       </c>
     </row>
     <row r="292" customHeight="1" spans="1:5">
-      <c r="A292" s="1" t="s">
+      <c r="A292" s="4" t="s">
         <v>1186</v>
       </c>
       <c r="B292" t="s">
@@ -10152,7 +10234,7 @@
       </c>
     </row>
     <row r="293" customHeight="1" spans="1:5">
-      <c r="A293" s="1" t="s">
+      <c r="A293" s="4" t="s">
         <v>1190</v>
       </c>
       <c r="B293" t="s">
@@ -10169,7 +10251,7 @@
       </c>
     </row>
     <row r="294" customHeight="1" spans="1:5">
-      <c r="A294" s="1" t="s">
+      <c r="A294" s="4" t="s">
         <v>1195</v>
       </c>
       <c r="B294" t="s">
@@ -10186,7 +10268,7 @@
       </c>
     </row>
     <row r="295" customHeight="1" spans="1:5">
-      <c r="A295" s="1" t="s">
+      <c r="A295" s="4" t="s">
         <v>1199</v>
       </c>
       <c r="B295" t="s">
@@ -10203,7 +10285,7 @@
       </c>
     </row>
     <row r="296" customHeight="1" spans="1:5">
-      <c r="A296" s="1" t="s">
+      <c r="A296" s="4" t="s">
         <v>1203</v>
       </c>
       <c r="B296" t="s">
@@ -10220,7 +10302,7 @@
       </c>
     </row>
     <row r="297" customHeight="1" spans="1:5">
-      <c r="A297" s="1" t="s">
+      <c r="A297" s="4" t="s">
         <v>1207</v>
       </c>
       <c r="B297" t="s">
@@ -10237,7 +10319,7 @@
       </c>
     </row>
     <row r="298" customHeight="1" spans="1:5">
-      <c r="A298" s="1" t="s">
+      <c r="A298" s="4" t="s">
         <v>1211</v>
       </c>
       <c r="B298" t="s">
@@ -10254,7 +10336,7 @@
       </c>
     </row>
     <row r="299" customHeight="1" spans="1:5">
-      <c r="A299" s="1" t="s">
+      <c r="A299" s="4" t="s">
         <v>1215</v>
       </c>
       <c r="B299" t="s">
@@ -10271,7 +10353,7 @@
       </c>
     </row>
     <row r="300" customHeight="1" spans="1:5">
-      <c r="A300" s="1" t="s">
+      <c r="A300" s="4" t="s">
         <v>1219</v>
       </c>
       <c r="B300" t="s">
@@ -10288,7 +10370,7 @@
       </c>
     </row>
     <row r="301" customHeight="1" spans="1:5">
-      <c r="A301" s="1" t="s">
+      <c r="A301" s="4" t="s">
         <v>1222</v>
       </c>
       <c r="B301" t="s">
@@ -10305,7 +10387,7 @@
       </c>
     </row>
     <row r="302" customHeight="1" spans="1:5">
-      <c r="A302" s="1" t="s">
+      <c r="A302" s="4" t="s">
         <v>1225</v>
       </c>
       <c r="B302" t="s">
@@ -10322,7 +10404,7 @@
       </c>
     </row>
     <row r="303" customHeight="1" spans="1:5">
-      <c r="A303" s="1" t="s">
+      <c r="A303" s="4" t="s">
         <v>1228</v>
       </c>
       <c r="B303" t="s">
@@ -10339,7 +10421,7 @@
       </c>
     </row>
     <row r="304" customHeight="1" spans="1:5">
-      <c r="A304" s="1" t="s">
+      <c r="A304" s="4" t="s">
         <v>1231</v>
       </c>
       <c r="B304" t="s">
@@ -10356,7 +10438,7 @@
       </c>
     </row>
     <row r="305" customHeight="1" spans="1:5">
-      <c r="A305" s="1" t="s">
+      <c r="A305" s="4" t="s">
         <v>1234</v>
       </c>
       <c r="B305" t="s">
@@ -10373,7 +10455,7 @@
       </c>
     </row>
     <row r="306" customHeight="1" spans="1:5">
-      <c r="A306" s="1" t="s">
+      <c r="A306" s="4" t="s">
         <v>1237</v>
       </c>
       <c r="B306" t="s">
@@ -10390,7 +10472,7 @@
       </c>
     </row>
     <row r="307" customHeight="1" spans="1:5">
-      <c r="A307" s="1" t="s">
+      <c r="A307" s="4" t="s">
         <v>1240</v>
       </c>
       <c r="B307" t="s">
@@ -10407,7 +10489,7 @@
       </c>
     </row>
     <row r="308" customHeight="1" spans="1:5">
-      <c r="A308" s="1" t="s">
+      <c r="A308" s="4" t="s">
         <v>1243</v>
       </c>
       <c r="B308" t="s">
@@ -10424,7 +10506,7 @@
       </c>
     </row>
     <row r="309" customHeight="1" spans="1:5">
-      <c r="A309" s="1" t="s">
+      <c r="A309" s="4" t="s">
         <v>1246</v>
       </c>
       <c r="B309" t="s">
@@ -10441,7 +10523,7 @@
       </c>
     </row>
     <row r="310" customHeight="1" spans="1:5">
-      <c r="A310" s="1" t="s">
+      <c r="A310" s="4" t="s">
         <v>1249</v>
       </c>
       <c r="B310" t="s">
@@ -10458,7 +10540,7 @@
       </c>
     </row>
     <row r="311" customHeight="1" spans="1:5">
-      <c r="A311" s="1" t="s">
+      <c r="A311" s="4" t="s">
         <v>1252</v>
       </c>
       <c r="B311" t="s">
@@ -10475,7 +10557,7 @@
       </c>
     </row>
     <row r="312" customHeight="1" spans="1:5">
-      <c r="A312" s="1" t="s">
+      <c r="A312" s="4" t="s">
         <v>1255</v>
       </c>
       <c r="B312" t="s">
@@ -10492,7 +10574,7 @@
       </c>
     </row>
     <row r="313" customHeight="1" spans="1:5">
-      <c r="A313" s="1" t="s">
+      <c r="A313" s="4" t="s">
         <v>1258</v>
       </c>
       <c r="B313" t="s">
@@ -10509,7 +10591,7 @@
       </c>
     </row>
     <row r="314" customHeight="1" spans="1:5">
-      <c r="A314" s="1" t="s">
+      <c r="A314" s="4" t="s">
         <v>1261</v>
       </c>
       <c r="B314" t="s">
@@ -10526,7 +10608,7 @@
       </c>
     </row>
     <row r="315" customHeight="1" spans="1:5">
-      <c r="A315" s="1" t="s">
+      <c r="A315" s="4" t="s">
         <v>1264</v>
       </c>
       <c r="B315" t="s">
@@ -10543,7 +10625,7 @@
       </c>
     </row>
     <row r="316" customHeight="1" spans="1:5">
-      <c r="A316" s="1" t="s">
+      <c r="A316" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="B316" t="s">
@@ -10560,7 +10642,7 @@
       </c>
     </row>
     <row r="317" customHeight="1" spans="1:5">
-      <c r="A317" s="1" t="s">
+      <c r="A317" s="4" t="s">
         <v>1270</v>
       </c>
       <c r="B317" t="s">
@@ -10577,7 +10659,7 @@
       </c>
     </row>
     <row r="318" customHeight="1" spans="1:5">
-      <c r="A318" s="1" t="s">
+      <c r="A318" s="4" t="s">
         <v>1273</v>
       </c>
       <c r="B318" t="s">
@@ -10594,7 +10676,7 @@
       </c>
     </row>
     <row r="319" customHeight="1" spans="1:5">
-      <c r="A319" s="1" t="s">
+      <c r="A319" s="4" t="s">
         <v>1276</v>
       </c>
       <c r="B319" t="s">
@@ -10611,7 +10693,7 @@
       </c>
     </row>
     <row r="320" customHeight="1" spans="1:5">
-      <c r="A320" s="1" t="s">
+      <c r="A320" s="4" t="s">
         <v>1279</v>
       </c>
       <c r="B320" t="s">
@@ -10628,7 +10710,7 @@
       </c>
     </row>
     <row r="321" customHeight="1" spans="1:5">
-      <c r="A321" s="1" t="s">
+      <c r="A321" s="4" t="s">
         <v>1282</v>
       </c>
       <c r="B321" t="s">
@@ -10645,7 +10727,7 @@
       </c>
     </row>
     <row r="322" customHeight="1" spans="1:5">
-      <c r="A322" s="1" t="s">
+      <c r="A322" s="4" t="s">
         <v>1285</v>
       </c>
       <c r="B322" t="s">
@@ -10662,7 +10744,7 @@
       </c>
     </row>
     <row r="323" customHeight="1" spans="1:5">
-      <c r="A323" s="1" t="s">
+      <c r="A323" s="4" t="s">
         <v>1288</v>
       </c>
       <c r="B323" t="s">
@@ -10679,7 +10761,7 @@
       </c>
     </row>
     <row r="324" customHeight="1" spans="1:5">
-      <c r="A324" s="1" t="s">
+      <c r="A324" s="4" t="s">
         <v>1291</v>
       </c>
       <c r="B324" t="s">
@@ -10696,7 +10778,7 @@
       </c>
     </row>
     <row r="325" customHeight="1" spans="1:5">
-      <c r="A325" s="1" t="s">
+      <c r="A325" s="4" t="s">
         <v>1294</v>
       </c>
       <c r="B325" t="s">
@@ -10713,7 +10795,7 @@
       </c>
     </row>
     <row r="326" customHeight="1" spans="1:5">
-      <c r="A326" s="1" t="s">
+      <c r="A326" s="4" t="s">
         <v>1297</v>
       </c>
       <c r="B326" t="s">
@@ -10730,7 +10812,7 @@
       </c>
     </row>
     <row r="327" customHeight="1" spans="1:5">
-      <c r="A327" s="1" t="s">
+      <c r="A327" s="4" t="s">
         <v>1300</v>
       </c>
       <c r="B327" t="s">
@@ -10747,7 +10829,7 @@
       </c>
     </row>
     <row r="328" customHeight="1" spans="1:5">
-      <c r="A328" s="1" t="s">
+      <c r="A328" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="B328" t="s">
@@ -10764,7 +10846,7 @@
       </c>
     </row>
     <row r="329" customHeight="1" spans="1:5">
-      <c r="A329" s="1" t="s">
+      <c r="A329" s="4" t="s">
         <v>1306</v>
       </c>
       <c r="B329" t="s">
@@ -10781,7 +10863,7 @@
       </c>
     </row>
     <row r="330" customHeight="1" spans="1:5">
-      <c r="A330" s="1" t="s">
+      <c r="A330" s="4" t="s">
         <v>1309</v>
       </c>
       <c r="B330" t="s">
@@ -10798,7 +10880,7 @@
       </c>
     </row>
     <row r="331" customHeight="1" spans="1:5">
-      <c r="A331" s="1" t="s">
+      <c r="A331" s="4" t="s">
         <v>1312</v>
       </c>
       <c r="B331" t="s">
@@ -10815,7 +10897,7 @@
       </c>
     </row>
     <row r="332" customHeight="1" spans="1:5">
-      <c r="A332" s="1" t="s">
+      <c r="A332" s="4" t="s">
         <v>1315</v>
       </c>
       <c r="B332" t="s">
@@ -10832,7 +10914,7 @@
       </c>
     </row>
     <row r="333" customHeight="1" spans="1:5">
-      <c r="A333" s="1" t="s">
+      <c r="A333" s="4" t="s">
         <v>1318</v>
       </c>
       <c r="B333" t="s">
@@ -10849,7 +10931,7 @@
       </c>
     </row>
     <row r="334" customHeight="1" spans="1:5">
-      <c r="A334" s="1" t="s">
+      <c r="A334" s="4" t="s">
         <v>1321</v>
       </c>
       <c r="B334" t="s">
@@ -10866,7 +10948,7 @@
       </c>
     </row>
     <row r="335" customHeight="1" spans="1:5">
-      <c r="A335" s="1" t="s">
+      <c r="A335" s="4" t="s">
         <v>1324</v>
       </c>
       <c r="B335" t="s">
@@ -10883,7 +10965,7 @@
       </c>
     </row>
     <row r="336" customHeight="1" spans="1:5">
-      <c r="A336" s="1" t="s">
+      <c r="A336" s="4" t="s">
         <v>1327</v>
       </c>
       <c r="B336" t="s">
@@ -10900,7 +10982,7 @@
       </c>
     </row>
     <row r="337" customHeight="1" spans="1:5">
-      <c r="A337" s="1" t="s">
+      <c r="A337" s="4" t="s">
         <v>1330</v>
       </c>
       <c r="B337" t="s">
@@ -10917,7 +10999,7 @@
       </c>
     </row>
     <row r="338" customHeight="1" spans="1:5">
-      <c r="A338" s="1" t="s">
+      <c r="A338" s="4" t="s">
         <v>1333</v>
       </c>
       <c r="B338" t="s">
@@ -10934,7 +11016,7 @@
       </c>
     </row>
     <row r="339" customHeight="1" spans="1:5">
-      <c r="A339" s="1" t="s">
+      <c r="A339" s="4" t="s">
         <v>1336</v>
       </c>
       <c r="B339" t="s">
@@ -10951,7 +11033,7 @@
       </c>
     </row>
     <row r="340" customHeight="1" spans="1:5">
-      <c r="A340" s="1" t="s">
+      <c r="A340" s="4" t="s">
         <v>1339</v>
       </c>
       <c r="B340" t="s">
@@ -10968,7 +11050,7 @@
       </c>
     </row>
     <row r="341" customHeight="1" spans="1:5">
-      <c r="A341" s="1" t="s">
+      <c r="A341" s="4" t="s">
         <v>1342</v>
       </c>
       <c r="B341" t="s">
@@ -10985,7 +11067,7 @@
       </c>
     </row>
     <row r="342" customHeight="1" spans="1:5">
-      <c r="A342" s="1" t="s">
+      <c r="A342" s="4" t="s">
         <v>1345</v>
       </c>
       <c r="B342" t="s">
@@ -11002,7 +11084,7 @@
       </c>
     </row>
     <row r="343" customHeight="1" spans="1:5">
-      <c r="A343" s="1" t="s">
+      <c r="A343" s="4" t="s">
         <v>1348</v>
       </c>
       <c r="B343" t="s">
@@ -11019,7 +11101,7 @@
       </c>
     </row>
     <row r="344" customHeight="1" spans="1:5">
-      <c r="A344" s="1" t="s">
+      <c r="A344" s="4" t="s">
         <v>1351</v>
       </c>
       <c r="B344" t="s">
@@ -11036,7 +11118,7 @@
       </c>
     </row>
     <row r="345" customHeight="1" spans="1:5">
-      <c r="A345" s="1" t="s">
+      <c r="A345" s="4" t="s">
         <v>1354</v>
       </c>
       <c r="B345" t="s">
@@ -11053,7 +11135,7 @@
       </c>
     </row>
     <row r="346" customHeight="1" spans="1:5">
-      <c r="A346" s="1" t="s">
+      <c r="A346" s="4" t="s">
         <v>1357</v>
       </c>
       <c r="B346" t="s">
@@ -11070,7 +11152,7 @@
       </c>
     </row>
     <row r="347" customHeight="1" spans="1:5">
-      <c r="A347" s="1" t="s">
+      <c r="A347" s="4" t="s">
         <v>1360</v>
       </c>
       <c r="B347" t="s">
@@ -11087,7 +11169,7 @@
       </c>
     </row>
     <row r="348" customHeight="1" spans="1:5">
-      <c r="A348" s="1" t="s">
+      <c r="A348" s="4" t="s">
         <v>1363</v>
       </c>
       <c r="B348" t="s">
@@ -11104,7 +11186,7 @@
       </c>
     </row>
     <row r="349" customHeight="1" spans="1:5">
-      <c r="A349" s="1" t="s">
+      <c r="A349" s="4" t="s">
         <v>1366</v>
       </c>
       <c r="B349" t="s">
@@ -11121,7 +11203,7 @@
       </c>
     </row>
     <row r="350" customHeight="1" spans="1:5">
-      <c r="A350" s="1" t="s">
+      <c r="A350" s="4" t="s">
         <v>1369</v>
       </c>
       <c r="B350" t="s">
@@ -11138,7 +11220,7 @@
       </c>
     </row>
     <row r="351" customHeight="1" spans="1:5">
-      <c r="A351" s="1" t="s">
+      <c r="A351" s="4" t="s">
         <v>1372</v>
       </c>
       <c r="B351" t="s">
@@ -11155,7 +11237,7 @@
       </c>
     </row>
     <row r="352" customHeight="1" spans="1:5">
-      <c r="A352" s="1" t="s">
+      <c r="A352" s="4" t="s">
         <v>1375</v>
       </c>
       <c r="B352" t="s">
@@ -11169,6 +11251,122 @@
       </c>
       <c r="E352" t="s">
         <v>1378</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Y13"/>
+  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="16384" width="2.125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25">
+      <c r="A1" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
+      <c r="B2" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="C3" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="D4" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="E5" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="F6" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="G7" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="H8" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="I9" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="J10" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="K11" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="L12" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="M13" s="1" t="s">
+        <v>497</v>
       </c>
     </row>
   </sheetData>

--- a/SimonCani_glyphs.xlsx
+++ b/SimonCani_glyphs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26670" windowHeight="12765" activeTab="1"/>
+    <workbookView windowWidth="26670" windowHeight="12765"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/SimonCani_glyphs.xlsx
+++ b/SimonCani_glyphs.xlsx
@@ -4890,15 +4890,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5262,7 +5259,7 @@
   <dimension ref="A1:E352"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.25" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.25" style="3" customWidth="1"/>
     <col min="2" max="2" width="9.25" customWidth="1"/>
     <col min="3" max="3" width="54.875" customWidth="1"/>
     <col min="4" max="4" width="40.375" customWidth="1"/>
@@ -5270,24 +5267,24 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:5">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
@@ -5304,7 +5301,7 @@
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
@@ -5321,7 +5318,7 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:5">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
@@ -5338,7 +5335,7 @@
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:5">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B5" t="s">
@@ -5355,7 +5352,7 @@
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:5">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B6" t="s">
@@ -5372,7 +5369,7 @@
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:5">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B7" t="s">
@@ -5389,7 +5386,7 @@
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:5">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B8" t="s">
@@ -5406,7 +5403,7 @@
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:5">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B9" t="s">
@@ -5423,7 +5420,7 @@
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:5">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B10" t="s">
@@ -5440,7 +5437,7 @@
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:5">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B11" t="s">
@@ -5457,7 +5454,7 @@
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:5">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B12" t="s">
@@ -5474,7 +5471,7 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:5">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B13" t="s">
@@ -5491,7 +5488,7 @@
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:5">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B14" t="s">
@@ -5508,7 +5505,7 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:5">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B15" t="s">
@@ -5525,7 +5522,7 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:5">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B16" t="s">
@@ -5542,7 +5539,7 @@
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:5">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B17" t="s">
@@ -5559,7 +5556,7 @@
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:5">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B18" t="s">
@@ -5576,7 +5573,7 @@
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:5">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>74</v>
       </c>
       <c r="B19" t="s">
@@ -5593,7 +5590,7 @@
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:5">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B20" t="s">
@@ -5610,7 +5607,7 @@
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:5">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B21" t="s">
@@ -5627,7 +5624,7 @@
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:5">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B22" t="s">
@@ -5644,7 +5641,7 @@
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:5">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B23" t="s">
@@ -5661,7 +5658,7 @@
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:5">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>94</v>
       </c>
       <c r="B24" t="s">
@@ -5678,7 +5675,7 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:5">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>98</v>
       </c>
       <c r="B25" t="s">
@@ -5695,7 +5692,7 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:5">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>102</v>
       </c>
       <c r="B26" t="s">
@@ -5712,7 +5709,7 @@
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:5">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>106</v>
       </c>
       <c r="B27" t="s">
@@ -5729,7 +5726,7 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:5">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B28" t="s">
@@ -5746,7 +5743,7 @@
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:5">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>114</v>
       </c>
       <c r="B29" t="s">
@@ -5763,7 +5760,7 @@
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:5">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>118</v>
       </c>
       <c r="B30" t="s">
@@ -5780,7 +5777,7 @@
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:5">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="3" t="s">
         <v>122</v>
       </c>
       <c r="B31" t="s">
@@ -5797,7 +5794,7 @@
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:5">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
         <v>126</v>
       </c>
       <c r="B32" t="s">
@@ -5814,7 +5811,7 @@
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:5">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B33" t="s">
@@ -5831,7 +5828,7 @@
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:5">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>134</v>
       </c>
       <c r="B34" t="s">
@@ -5848,7 +5845,7 @@
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:5">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="3" t="s">
         <v>138</v>
       </c>
       <c r="B35" t="s">
@@ -5865,7 +5862,7 @@
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:5">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>142</v>
       </c>
       <c r="B36" t="s">
@@ -5882,7 +5879,7 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:5">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="3" t="s">
         <v>146</v>
       </c>
       <c r="B37" t="s">
@@ -5899,7 +5896,7 @@
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:5">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="3" t="s">
         <v>150</v>
       </c>
       <c r="B38" t="s">
@@ -5916,7 +5913,7 @@
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:5">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="3" t="s">
         <v>154</v>
       </c>
       <c r="B39" t="s">
@@ -5933,7 +5930,7 @@
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:5">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="3" t="s">
         <v>158</v>
       </c>
       <c r="B40" t="s">
@@ -5950,7 +5947,7 @@
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:5">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="3" t="s">
         <v>162</v>
       </c>
       <c r="B41" t="s">
@@ -5967,7 +5964,7 @@
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:5">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="3" t="s">
         <v>166</v>
       </c>
       <c r="B42" t="s">
@@ -5984,7 +5981,7 @@
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:5">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="3" t="s">
         <v>170</v>
       </c>
       <c r="B43" t="s">
@@ -6001,7 +5998,7 @@
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:5">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>174</v>
       </c>
       <c r="B44" t="s">
@@ -6018,7 +6015,7 @@
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:5">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="3" t="s">
         <v>178</v>
       </c>
       <c r="B45" t="s">
@@ -6035,7 +6032,7 @@
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:5">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>182</v>
       </c>
       <c r="B46" t="s">
@@ -6052,7 +6049,7 @@
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:5">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="3" t="s">
         <v>186</v>
       </c>
       <c r="B47" t="s">
@@ -6069,7 +6066,7 @@
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:5">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="3" t="s">
         <v>190</v>
       </c>
       <c r="B48" t="s">
@@ -6086,7 +6083,7 @@
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:5">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="3" t="s">
         <v>194</v>
       </c>
       <c r="B49" t="s">
@@ -6103,7 +6100,7 @@
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:5">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="3" t="s">
         <v>198</v>
       </c>
       <c r="B50" t="s">
@@ -6120,7 +6117,7 @@
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:5">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="3" t="s">
         <v>202</v>
       </c>
       <c r="B51" t="s">
@@ -6137,7 +6134,7 @@
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:5">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="3" t="s">
         <v>206</v>
       </c>
       <c r="B52" t="s">
@@ -6154,7 +6151,7 @@
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:5">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="3" t="s">
         <v>210</v>
       </c>
       <c r="B53" t="s">
@@ -6171,7 +6168,7 @@
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:5">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="3" t="s">
         <v>214</v>
       </c>
       <c r="B54" t="s">
@@ -6188,7 +6185,7 @@
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:5">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B55" t="s">
@@ -6205,7 +6202,7 @@
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:5">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="3" t="s">
         <v>222</v>
       </c>
       <c r="B56" t="s">
@@ -6222,7 +6219,7 @@
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:5">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="3" t="s">
         <v>226</v>
       </c>
       <c r="B57" t="s">
@@ -6239,7 +6236,7 @@
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:5">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="3" t="s">
         <v>230</v>
       </c>
       <c r="B58" t="s">
@@ -6256,7 +6253,7 @@
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:5">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="3" t="s">
         <v>234</v>
       </c>
       <c r="B59" t="s">
@@ -6273,7 +6270,7 @@
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:5">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="3" t="s">
         <v>238</v>
       </c>
       <c r="B60" t="s">
@@ -6290,7 +6287,7 @@
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:5">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="3" t="s">
         <v>242</v>
       </c>
       <c r="B61" t="s">
@@ -6307,7 +6304,7 @@
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:5">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="3" t="s">
         <v>246</v>
       </c>
       <c r="B62" t="s">
@@ -6324,7 +6321,7 @@
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:5">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="3" t="s">
         <v>250</v>
       </c>
       <c r="B63" t="s">
@@ -6341,7 +6338,7 @@
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:5">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="3" t="s">
         <v>254</v>
       </c>
       <c r="B64" t="s">
@@ -6358,7 +6355,7 @@
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:5">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="3" t="s">
         <v>258</v>
       </c>
       <c r="B65" t="s">
@@ -6375,7 +6372,7 @@
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:5">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="3" t="s">
         <v>262</v>
       </c>
       <c r="B66" t="s">
@@ -6392,7 +6389,7 @@
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:5">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="3" t="s">
         <v>266</v>
       </c>
       <c r="B67" t="s">
@@ -6409,7 +6406,7 @@
       </c>
     </row>
     <row r="68" customHeight="1" spans="1:5">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="3" t="s">
         <v>270</v>
       </c>
       <c r="B68" t="s">
@@ -6426,7 +6423,7 @@
       </c>
     </row>
     <row r="69" customHeight="1" spans="1:5">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="3" t="s">
         <v>274</v>
       </c>
       <c r="B69" t="s">
@@ -6443,7 +6440,7 @@
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:5">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="3" t="s">
         <v>278</v>
       </c>
       <c r="B70" t="s">
@@ -6460,7 +6457,7 @@
       </c>
     </row>
     <row r="71" customHeight="1" spans="1:5">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="3" t="s">
         <v>282</v>
       </c>
       <c r="B71" t="s">
@@ -6477,7 +6474,7 @@
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:5">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="3" t="s">
         <v>286</v>
       </c>
       <c r="B72" t="s">
@@ -6494,7 +6491,7 @@
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:5">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="3" t="s">
         <v>290</v>
       </c>
       <c r="B73" t="s">
@@ -6511,7 +6508,7 @@
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:5">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="3" t="s">
         <v>294</v>
       </c>
       <c r="B74" t="s">
@@ -6528,7 +6525,7 @@
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:5">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="3" t="s">
         <v>298</v>
       </c>
       <c r="B75" t="s">
@@ -6545,7 +6542,7 @@
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:5">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="3" t="s">
         <v>302</v>
       </c>
       <c r="B76" t="s">
@@ -6562,7 +6559,7 @@
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:5">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="3" t="s">
         <v>306</v>
       </c>
       <c r="B77" t="s">
@@ -6579,7 +6576,7 @@
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:5">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="3" t="s">
         <v>310</v>
       </c>
       <c r="B78" t="s">
@@ -6596,7 +6593,7 @@
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:5">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="3" t="s">
         <v>314</v>
       </c>
       <c r="B79" t="s">
@@ -6613,7 +6610,7 @@
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:5">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="3" t="s">
         <v>318</v>
       </c>
       <c r="B80" t="s">
@@ -6630,7 +6627,7 @@
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:5">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="3" t="s">
         <v>323</v>
       </c>
       <c r="B81" t="s">
@@ -6647,7 +6644,7 @@
       </c>
     </row>
     <row r="82" customHeight="1" spans="1:5">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="3" t="s">
         <v>327</v>
       </c>
       <c r="B82" t="s">
@@ -6664,7 +6661,7 @@
       </c>
     </row>
     <row r="83" customHeight="1" spans="1:5">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="3" t="s">
         <v>331</v>
       </c>
       <c r="B83" t="s">
@@ -6681,7 +6678,7 @@
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:5">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="3" t="s">
         <v>335</v>
       </c>
       <c r="B84" t="s">
@@ -6698,7 +6695,7 @@
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:5">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="3" t="s">
         <v>339</v>
       </c>
       <c r="B85" t="s">
@@ -6715,7 +6712,7 @@
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:5">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="3" t="s">
         <v>343</v>
       </c>
       <c r="B86" t="s">
@@ -6732,7 +6729,7 @@
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:5">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="3" t="s">
         <v>347</v>
       </c>
       <c r="B87" t="s">
@@ -6749,7 +6746,7 @@
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:5">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="3" t="s">
         <v>351</v>
       </c>
       <c r="B88" t="s">
@@ -6766,7 +6763,7 @@
       </c>
     </row>
     <row r="89" customHeight="1" spans="1:5">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="3" t="s">
         <v>355</v>
       </c>
       <c r="B89" t="s">
@@ -6783,7 +6780,7 @@
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:5">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="3" t="s">
         <v>359</v>
       </c>
       <c r="B90" t="s">
@@ -6800,7 +6797,7 @@
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:5">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B91" t="s">
@@ -6817,7 +6814,7 @@
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:5">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="3" t="s">
         <v>366</v>
       </c>
       <c r="B92" t="s">
@@ -6834,7 +6831,7 @@
       </c>
     </row>
     <row r="93" customHeight="1" spans="1:5">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="3" t="s">
         <v>370</v>
       </c>
       <c r="B93" t="s">
@@ -6851,7 +6848,7 @@
       </c>
     </row>
     <row r="94" customHeight="1" spans="1:5">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="3" t="s">
         <v>374</v>
       </c>
       <c r="B94" t="s">
@@ -6868,7 +6865,7 @@
       </c>
     </row>
     <row r="95" customHeight="1" spans="1:5">
-      <c r="A95" s="4" t="s">
+      <c r="A95" s="3" t="s">
         <v>378</v>
       </c>
       <c r="B95" t="s">
@@ -6885,7 +6882,7 @@
       </c>
     </row>
     <row r="96" customHeight="1" spans="1:5">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="3" t="s">
         <v>382</v>
       </c>
       <c r="B96" t="s">
@@ -6902,7 +6899,7 @@
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:5">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="3" t="s">
         <v>386</v>
       </c>
       <c r="B97" t="s">
@@ -6919,7 +6916,7 @@
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:5">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="3" t="s">
         <v>390</v>
       </c>
       <c r="B98" t="s">
@@ -6936,7 +6933,7 @@
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:5">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="3" t="s">
         <v>394</v>
       </c>
       <c r="B99" t="s">
@@ -6953,7 +6950,7 @@
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:5">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="3" t="s">
         <v>398</v>
       </c>
       <c r="B100" t="s">
@@ -6970,7 +6967,7 @@
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:5">
-      <c r="A101" s="4" t="s">
+      <c r="A101" s="3" t="s">
         <v>402</v>
       </c>
       <c r="B101" t="s">
@@ -6987,7 +6984,7 @@
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:5">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="3" t="s">
         <v>406</v>
       </c>
       <c r="B102" t="s">
@@ -7004,7 +7001,7 @@
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:5">
-      <c r="A103" s="4" t="s">
+      <c r="A103" s="3" t="s">
         <v>410</v>
       </c>
       <c r="B103" t="s">
@@ -7021,7 +7018,7 @@
       </c>
     </row>
     <row r="104" customHeight="1" spans="1:5">
-      <c r="A104" s="4" t="s">
+      <c r="A104" s="3" t="s">
         <v>414</v>
       </c>
       <c r="B104" t="s">
@@ -7038,7 +7035,7 @@
       </c>
     </row>
     <row r="105" customHeight="1" spans="1:5">
-      <c r="A105" s="4" t="s">
+      <c r="A105" s="3" t="s">
         <v>418</v>
       </c>
       <c r="B105" t="s">
@@ -7055,7 +7052,7 @@
       </c>
     </row>
     <row r="106" customHeight="1" spans="1:5">
-      <c r="A106" s="4" t="s">
+      <c r="A106" s="3" t="s">
         <v>422</v>
       </c>
       <c r="B106" t="s">
@@ -7072,7 +7069,7 @@
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:5">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="3" t="s">
         <v>426</v>
       </c>
       <c r="B107" t="s">
@@ -7089,7 +7086,7 @@
       </c>
     </row>
     <row r="108" customHeight="1" spans="1:5">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="3" t="s">
         <v>430</v>
       </c>
       <c r="B108" t="s">
@@ -7106,7 +7103,7 @@
       </c>
     </row>
     <row r="109" customHeight="1" spans="1:5">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="3" t="s">
         <v>434</v>
       </c>
       <c r="B109" t="s">
@@ -7123,7 +7120,7 @@
       </c>
     </row>
     <row r="110" customHeight="1" spans="1:5">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="3" t="s">
         <v>438</v>
       </c>
       <c r="B110" t="s">
@@ -7140,7 +7137,7 @@
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:5">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="3" t="s">
         <v>442</v>
       </c>
       <c r="B111" t="s">
@@ -7157,7 +7154,7 @@
       </c>
     </row>
     <row r="112" customHeight="1" spans="1:5">
-      <c r="A112" s="4" t="s">
+      <c r="A112" s="3" t="s">
         <v>446</v>
       </c>
       <c r="B112" t="s">
@@ -7174,7 +7171,7 @@
       </c>
     </row>
     <row r="113" customHeight="1" spans="1:5">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="3" t="s">
         <v>450</v>
       </c>
       <c r="B113" t="s">
@@ -7191,7 +7188,7 @@
       </c>
     </row>
     <row r="114" customHeight="1" spans="1:5">
-      <c r="A114" s="4" t="s">
+      <c r="A114" s="3" t="s">
         <v>454</v>
       </c>
       <c r="B114" t="s">
@@ -7208,7 +7205,7 @@
       </c>
     </row>
     <row r="115" customHeight="1" spans="1:5">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="3" t="s">
         <v>458</v>
       </c>
       <c r="B115" t="s">
@@ -7225,7 +7222,7 @@
       </c>
     </row>
     <row r="116" customHeight="1" spans="1:5">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="3" t="s">
         <v>463</v>
       </c>
       <c r="B116" t="s">
@@ -7242,7 +7239,7 @@
       </c>
     </row>
     <row r="117" customHeight="1" spans="1:5">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="3" t="s">
         <v>467</v>
       </c>
       <c r="B117" t="s">
@@ -7259,7 +7256,7 @@
       </c>
     </row>
     <row r="118" customHeight="1" spans="1:5">
-      <c r="A118" s="4" t="s">
+      <c r="A118" s="3" t="s">
         <v>471</v>
       </c>
       <c r="B118" t="s">
@@ -7276,7 +7273,7 @@
       </c>
     </row>
     <row r="119" customHeight="1" spans="1:5">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="3" t="s">
         <v>475</v>
       </c>
       <c r="B119" t="s">
@@ -7293,7 +7290,7 @@
       </c>
     </row>
     <row r="120" customHeight="1" spans="1:5">
-      <c r="A120" s="4" t="s">
+      <c r="A120" s="3" t="s">
         <v>479</v>
       </c>
       <c r="B120" t="s">
@@ -7310,7 +7307,7 @@
       </c>
     </row>
     <row r="121" customHeight="1" spans="1:5">
-      <c r="A121" s="4" t="s">
+      <c r="A121" s="3" t="s">
         <v>484</v>
       </c>
       <c r="B121" t="s">
@@ -7327,7 +7324,7 @@
       </c>
     </row>
     <row r="122" customHeight="1" spans="1:5">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="3" t="s">
         <v>488</v>
       </c>
       <c r="B122" t="s">
@@ -7344,7 +7341,7 @@
       </c>
     </row>
     <row r="123" customHeight="1" spans="1:5">
-      <c r="A123" s="4" t="s">
+      <c r="A123" s="3" t="s">
         <v>492</v>
       </c>
       <c r="B123" t="s">
@@ -7361,7 +7358,7 @@
       </c>
     </row>
     <row r="124" customHeight="1" spans="1:5">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="3" t="s">
         <v>497</v>
       </c>
       <c r="B124" t="s">
@@ -7378,7 +7375,7 @@
       </c>
     </row>
     <row r="125" customHeight="1" spans="1:5">
-      <c r="A125" s="4" t="s">
+      <c r="A125" s="3" t="s">
         <v>501</v>
       </c>
       <c r="B125" t="s">
@@ -7395,7 +7392,7 @@
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:5">
-      <c r="A126" s="4" t="s">
+      <c r="A126" s="3" t="s">
         <v>505</v>
       </c>
       <c r="B126" t="s">
@@ -7412,7 +7409,7 @@
       </c>
     </row>
     <row r="127" customHeight="1" spans="1:5">
-      <c r="A127" s="4" t="s">
+      <c r="A127" s="3" t="s">
         <v>509</v>
       </c>
       <c r="B127" t="s">
@@ -7429,7 +7426,7 @@
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:5">
-      <c r="A128" s="4" t="s">
+      <c r="A128" s="3" t="s">
         <v>513</v>
       </c>
       <c r="B128" t="s">
@@ -7446,7 +7443,7 @@
       </c>
     </row>
     <row r="129" customHeight="1" spans="1:5">
-      <c r="A129" s="4" t="s">
+      <c r="A129" s="3" t="s">
         <v>517</v>
       </c>
       <c r="B129" t="s">
@@ -7463,7 +7460,7 @@
       </c>
     </row>
     <row r="130" customHeight="1" spans="1:5">
-      <c r="A130" s="4" t="s">
+      <c r="A130" s="3" t="s">
         <v>521</v>
       </c>
       <c r="B130" t="s">
@@ -7480,7 +7477,7 @@
       </c>
     </row>
     <row r="131" customHeight="1" spans="1:5">
-      <c r="A131" s="4" t="s">
+      <c r="A131" s="3" t="s">
         <v>525</v>
       </c>
       <c r="B131" t="s">
@@ -7497,7 +7494,7 @@
       </c>
     </row>
     <row r="132" customHeight="1" spans="1:5">
-      <c r="A132" s="4" t="s">
+      <c r="A132" s="3" t="s">
         <v>529</v>
       </c>
       <c r="B132" t="s">
@@ -7514,7 +7511,7 @@
       </c>
     </row>
     <row r="133" customHeight="1" spans="1:5">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="3" t="s">
         <v>533</v>
       </c>
       <c r="B133" t="s">
@@ -7531,7 +7528,7 @@
       </c>
     </row>
     <row r="134" customHeight="1" spans="1:5">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="3" t="s">
         <v>537</v>
       </c>
       <c r="B134" t="s">
@@ -7548,7 +7545,7 @@
       </c>
     </row>
     <row r="135" customHeight="1" spans="1:5">
-      <c r="A135" s="4" t="s">
+      <c r="A135" s="3" t="s">
         <v>541</v>
       </c>
       <c r="B135" t="s">
@@ -7565,7 +7562,7 @@
       </c>
     </row>
     <row r="136" customHeight="1" spans="1:5">
-      <c r="A136" s="4" t="s">
+      <c r="A136" s="3" t="s">
         <v>545</v>
       </c>
       <c r="B136" t="s">
@@ -7582,7 +7579,7 @@
       </c>
     </row>
     <row r="137" customHeight="1" spans="1:5">
-      <c r="A137" s="4" t="s">
+      <c r="A137" s="3" t="s">
         <v>549</v>
       </c>
       <c r="B137" t="s">
@@ -7599,7 +7596,7 @@
       </c>
     </row>
     <row r="138" customHeight="1" spans="1:5">
-      <c r="A138" s="4" t="s">
+      <c r="A138" s="3" t="s">
         <v>553</v>
       </c>
       <c r="B138" t="s">
@@ -7616,7 +7613,7 @@
       </c>
     </row>
     <row r="139" customHeight="1" spans="1:5">
-      <c r="A139" s="4" t="s">
+      <c r="A139" s="3" t="s">
         <v>557</v>
       </c>
       <c r="B139" t="s">
@@ -7633,7 +7630,7 @@
       </c>
     </row>
     <row r="140" customHeight="1" spans="1:5">
-      <c r="A140" s="4" t="s">
+      <c r="A140" s="3" t="s">
         <v>561</v>
       </c>
       <c r="B140" t="s">
@@ -7650,7 +7647,7 @@
       </c>
     </row>
     <row r="141" customHeight="1" spans="1:5">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="3" t="s">
         <v>565</v>
       </c>
       <c r="B141" t="s">
@@ -7667,7 +7664,7 @@
       </c>
     </row>
     <row r="142" customHeight="1" spans="1:5">
-      <c r="A142" s="4" t="s">
+      <c r="A142" s="3" t="s">
         <v>569</v>
       </c>
       <c r="B142" t="s">
@@ -7684,7 +7681,7 @@
       </c>
     </row>
     <row r="143" customHeight="1" spans="1:5">
-      <c r="A143" s="4" t="s">
+      <c r="A143" s="3" t="s">
         <v>573</v>
       </c>
       <c r="B143" t="s">
@@ -7701,7 +7698,7 @@
       </c>
     </row>
     <row r="144" customHeight="1" spans="1:5">
-      <c r="A144" s="4" t="s">
+      <c r="A144" s="3" t="s">
         <v>577</v>
       </c>
       <c r="B144" t="s">
@@ -7718,7 +7715,7 @@
       </c>
     </row>
     <row r="145" customHeight="1" spans="1:5">
-      <c r="A145" s="4" t="s">
+      <c r="A145" s="3" t="s">
         <v>581</v>
       </c>
       <c r="B145" t="s">
@@ -7735,7 +7732,7 @@
       </c>
     </row>
     <row r="146" customHeight="1" spans="1:5">
-      <c r="A146" s="4" t="s">
+      <c r="A146" s="3" t="s">
         <v>585</v>
       </c>
       <c r="B146" t="s">
@@ -7752,7 +7749,7 @@
       </c>
     </row>
     <row r="147" customHeight="1" spans="1:5">
-      <c r="A147" s="4" t="s">
+      <c r="A147" s="3" t="s">
         <v>589</v>
       </c>
       <c r="B147" t="s">
@@ -7769,7 +7766,7 @@
       </c>
     </row>
     <row r="148" customHeight="1" spans="1:5">
-      <c r="A148" s="4" t="s">
+      <c r="A148" s="3" t="s">
         <v>593</v>
       </c>
       <c r="B148" t="s">
@@ -7786,7 +7783,7 @@
       </c>
     </row>
     <row r="149" customHeight="1" spans="1:5">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="3" t="s">
         <v>597</v>
       </c>
       <c r="B149" t="s">
@@ -7803,7 +7800,7 @@
       </c>
     </row>
     <row r="150" customHeight="1" spans="1:5">
-      <c r="A150" s="4" t="s">
+      <c r="A150" s="3" t="s">
         <v>601</v>
       </c>
       <c r="B150" t="s">
@@ -7820,7 +7817,7 @@
       </c>
     </row>
     <row r="151" customHeight="1" spans="1:5">
-      <c r="A151" s="4" t="s">
+      <c r="A151" s="3" t="s">
         <v>605</v>
       </c>
       <c r="B151" t="s">
@@ -7837,7 +7834,7 @@
       </c>
     </row>
     <row r="152" customHeight="1" spans="1:5">
-      <c r="A152" s="4" t="s">
+      <c r="A152" s="3" t="s">
         <v>609</v>
       </c>
       <c r="B152" t="s">
@@ -7854,7 +7851,7 @@
       </c>
     </row>
     <row r="153" customHeight="1" spans="1:5">
-      <c r="A153" s="4" t="s">
+      <c r="A153" s="3" t="s">
         <v>613</v>
       </c>
       <c r="B153" t="s">
@@ -7871,7 +7868,7 @@
       </c>
     </row>
     <row r="154" customHeight="1" spans="1:5">
-      <c r="A154" s="4" t="s">
+      <c r="A154" s="3" t="s">
         <v>617</v>
       </c>
       <c r="B154" t="s">
@@ -7888,7 +7885,7 @@
       </c>
     </row>
     <row r="155" customHeight="1" spans="1:5">
-      <c r="A155" s="4" t="s">
+      <c r="A155" s="3" t="s">
         <v>621</v>
       </c>
       <c r="B155" t="s">
@@ -7905,7 +7902,7 @@
       </c>
     </row>
     <row r="156" customHeight="1" spans="1:5">
-      <c r="A156" s="4" t="s">
+      <c r="A156" s="3" t="s">
         <v>625</v>
       </c>
       <c r="B156" t="s">
@@ -7922,7 +7919,7 @@
       </c>
     </row>
     <row r="157" customHeight="1" spans="1:5">
-      <c r="A157" s="4" t="s">
+      <c r="A157" s="3" t="s">
         <v>629</v>
       </c>
       <c r="B157" t="s">
@@ -7939,7 +7936,7 @@
       </c>
     </row>
     <row r="158" customHeight="1" spans="1:5">
-      <c r="A158" s="4" t="s">
+      <c r="A158" s="3" t="s">
         <v>633</v>
       </c>
       <c r="B158" t="s">
@@ -7956,7 +7953,7 @@
       </c>
     </row>
     <row r="159" customHeight="1" spans="1:5">
-      <c r="A159" s="4" t="s">
+      <c r="A159" s="3" t="s">
         <v>637</v>
       </c>
       <c r="B159" t="s">
@@ -7973,7 +7970,7 @@
       </c>
     </row>
     <row r="160" customHeight="1" spans="1:5">
-      <c r="A160" s="4" t="s">
+      <c r="A160" s="3" t="s">
         <v>641</v>
       </c>
       <c r="B160" t="s">
@@ -7990,7 +7987,7 @@
       </c>
     </row>
     <row r="161" customHeight="1" spans="1:5">
-      <c r="A161" s="4" t="s">
+      <c r="A161" s="3" t="s">
         <v>645</v>
       </c>
       <c r="B161" t="s">
@@ -8007,7 +8004,7 @@
       </c>
     </row>
     <row r="162" customHeight="1" spans="1:5">
-      <c r="A162" s="4" t="s">
+      <c r="A162" s="3" t="s">
         <v>649</v>
       </c>
       <c r="B162" t="s">
@@ -8024,7 +8021,7 @@
       </c>
     </row>
     <row r="163" customHeight="1" spans="1:5">
-      <c r="A163" s="4" t="s">
+      <c r="A163" s="3" t="s">
         <v>653</v>
       </c>
       <c r="B163" t="s">
@@ -8041,7 +8038,7 @@
       </c>
     </row>
     <row r="164" customHeight="1" spans="1:5">
-      <c r="A164" s="4" t="s">
+      <c r="A164" s="3" t="s">
         <v>657</v>
       </c>
       <c r="B164" t="s">
@@ -8058,7 +8055,7 @@
       </c>
     </row>
     <row r="165" customHeight="1" spans="1:5">
-      <c r="A165" s="4" t="s">
+      <c r="A165" s="3" t="s">
         <v>661</v>
       </c>
       <c r="B165" t="s">
@@ -8075,7 +8072,7 @@
       </c>
     </row>
     <row r="166" customHeight="1" spans="1:5">
-      <c r="A166" s="4" t="s">
+      <c r="A166" s="3" t="s">
         <v>665</v>
       </c>
       <c r="B166" t="s">
@@ -8092,7 +8089,7 @@
       </c>
     </row>
     <row r="167" customHeight="1" spans="1:5">
-      <c r="A167" s="4" t="s">
+      <c r="A167" s="3" t="s">
         <v>669</v>
       </c>
       <c r="B167" t="s">
@@ -8109,7 +8106,7 @@
       </c>
     </row>
     <row r="168" customHeight="1" spans="1:5">
-      <c r="A168" s="4" t="s">
+      <c r="A168" s="3" t="s">
         <v>673</v>
       </c>
       <c r="B168" t="s">
@@ -8126,7 +8123,7 @@
       </c>
     </row>
     <row r="169" customHeight="1" spans="1:5">
-      <c r="A169" s="4" t="s">
+      <c r="A169" s="3" t="s">
         <v>677</v>
       </c>
       <c r="B169" t="s">
@@ -8143,7 +8140,7 @@
       </c>
     </row>
     <row r="170" customHeight="1" spans="1:5">
-      <c r="A170" s="4" t="s">
+      <c r="A170" s="3" t="s">
         <v>681</v>
       </c>
       <c r="B170" t="s">
@@ -8160,7 +8157,7 @@
       </c>
     </row>
     <row r="171" customHeight="1" spans="1:5">
-      <c r="A171" s="4" t="s">
+      <c r="A171" s="3" t="s">
         <v>685</v>
       </c>
       <c r="B171" t="s">
@@ -8177,7 +8174,7 @@
       </c>
     </row>
     <row r="172" customHeight="1" spans="1:5">
-      <c r="A172" s="4" t="s">
+      <c r="A172" s="3" t="s">
         <v>689</v>
       </c>
       <c r="B172" t="s">
@@ -8194,7 +8191,7 @@
       </c>
     </row>
     <row r="173" customHeight="1" spans="1:5">
-      <c r="A173" s="4" t="s">
+      <c r="A173" s="3" t="s">
         <v>693</v>
       </c>
       <c r="B173" t="s">
@@ -8211,7 +8208,7 @@
       </c>
     </row>
     <row r="174" customHeight="1" spans="1:5">
-      <c r="A174" s="4" t="s">
+      <c r="A174" s="3" t="s">
         <v>697</v>
       </c>
       <c r="B174" t="s">
@@ -8228,7 +8225,7 @@
       </c>
     </row>
     <row r="175" customHeight="1" spans="1:5">
-      <c r="A175" s="4" t="s">
+      <c r="A175" s="3" t="s">
         <v>701</v>
       </c>
       <c r="B175" t="s">
@@ -8245,7 +8242,7 @@
       </c>
     </row>
     <row r="176" customHeight="1" spans="1:5">
-      <c r="A176" s="4" t="s">
+      <c r="A176" s="3" t="s">
         <v>705</v>
       </c>
       <c r="B176" t="s">
@@ -8262,7 +8259,7 @@
       </c>
     </row>
     <row r="177" customHeight="1" spans="1:5">
-      <c r="A177" s="4" t="s">
+      <c r="A177" s="3" t="s">
         <v>709</v>
       </c>
       <c r="B177" t="s">
@@ -8279,7 +8276,7 @@
       </c>
     </row>
     <row r="178" customHeight="1" spans="1:5">
-      <c r="A178" s="4" t="s">
+      <c r="A178" s="3" t="s">
         <v>713</v>
       </c>
       <c r="B178" t="s">
@@ -8296,7 +8293,7 @@
       </c>
     </row>
     <row r="179" customHeight="1" spans="1:5">
-      <c r="A179" s="4" t="s">
+      <c r="A179" s="3" t="s">
         <v>717</v>
       </c>
       <c r="B179" t="s">
@@ -8313,7 +8310,7 @@
       </c>
     </row>
     <row r="180" customHeight="1" spans="1:5">
-      <c r="A180" s="4" t="s">
+      <c r="A180" s="3" t="s">
         <v>721</v>
       </c>
       <c r="B180" t="s">
@@ -8330,7 +8327,7 @@
       </c>
     </row>
     <row r="181" customHeight="1" spans="1:5">
-      <c r="A181" s="4" t="s">
+      <c r="A181" s="3" t="s">
         <v>725</v>
       </c>
       <c r="B181" t="s">
@@ -8347,7 +8344,7 @@
       </c>
     </row>
     <row r="182" customHeight="1" spans="1:5">
-      <c r="A182" s="4" t="s">
+      <c r="A182" s="3" t="s">
         <v>729</v>
       </c>
       <c r="B182" t="s">
@@ -8364,7 +8361,7 @@
       </c>
     </row>
     <row r="183" customHeight="1" spans="1:5">
-      <c r="A183" s="4" t="s">
+      <c r="A183" s="3" t="s">
         <v>733</v>
       </c>
       <c r="B183" t="s">
@@ -8381,7 +8378,7 @@
       </c>
     </row>
     <row r="184" customHeight="1" spans="1:5">
-      <c r="A184" s="4" t="s">
+      <c r="A184" s="3" t="s">
         <v>737</v>
       </c>
       <c r="B184" t="s">
@@ -8398,7 +8395,7 @@
       </c>
     </row>
     <row r="185" customHeight="1" spans="1:5">
-      <c r="A185" s="4" t="s">
+      <c r="A185" s="3" t="s">
         <v>741</v>
       </c>
       <c r="B185" t="s">
@@ -8415,7 +8412,7 @@
       </c>
     </row>
     <row r="186" customHeight="1" spans="1:5">
-      <c r="A186" s="4" t="s">
+      <c r="A186" s="3" t="s">
         <v>745</v>
       </c>
       <c r="B186" t="s">
@@ -8432,7 +8429,7 @@
       </c>
     </row>
     <row r="187" customHeight="1" spans="1:5">
-      <c r="A187" s="4" t="s">
+      <c r="A187" s="3" t="s">
         <v>750</v>
       </c>
       <c r="B187" t="s">
@@ -8449,7 +8446,7 @@
       </c>
     </row>
     <row r="188" customHeight="1" spans="1:5">
-      <c r="A188" s="4" t="s">
+      <c r="A188" s="3" t="s">
         <v>754</v>
       </c>
       <c r="B188" t="s">
@@ -8466,7 +8463,7 @@
       </c>
     </row>
     <row r="189" customHeight="1" spans="1:5">
-      <c r="A189" s="4" t="s">
+      <c r="A189" s="3" t="s">
         <v>758</v>
       </c>
       <c r="B189" t="s">
@@ -8483,7 +8480,7 @@
       </c>
     </row>
     <row r="190" customHeight="1" spans="1:5">
-      <c r="A190" s="4" t="s">
+      <c r="A190" s="3" t="s">
         <v>762</v>
       </c>
       <c r="B190" t="s">
@@ -8500,7 +8497,7 @@
       </c>
     </row>
     <row r="191" customHeight="1" spans="1:5">
-      <c r="A191" s="4" t="s">
+      <c r="A191" s="3" t="s">
         <v>766</v>
       </c>
       <c r="B191" t="s">
@@ -8517,7 +8514,7 @@
       </c>
     </row>
     <row r="192" customHeight="1" spans="1:5">
-      <c r="A192" s="4" t="s">
+      <c r="A192" s="3" t="s">
         <v>770</v>
       </c>
       <c r="B192" t="s">
@@ -8534,7 +8531,7 @@
       </c>
     </row>
     <row r="193" customHeight="1" spans="1:5">
-      <c r="A193" s="4" t="s">
+      <c r="A193" s="3" t="s">
         <v>774</v>
       </c>
       <c r="B193" t="s">
@@ -8551,7 +8548,7 @@
       </c>
     </row>
     <row r="194" customHeight="1" spans="1:5">
-      <c r="A194" s="4" t="s">
+      <c r="A194" s="3" t="s">
         <v>778</v>
       </c>
       <c r="B194" t="s">
@@ -8568,7 +8565,7 @@
       </c>
     </row>
     <row r="195" customHeight="1" spans="1:5">
-      <c r="A195" s="4" t="s">
+      <c r="A195" s="3" t="s">
         <v>782</v>
       </c>
       <c r="B195" t="s">
@@ -8585,7 +8582,7 @@
       </c>
     </row>
     <row r="196" customHeight="1" spans="1:5">
-      <c r="A196" s="4" t="s">
+      <c r="A196" s="3" t="s">
         <v>786</v>
       </c>
       <c r="B196" t="s">
@@ -8602,7 +8599,7 @@
       </c>
     </row>
     <row r="197" customHeight="1" spans="1:5">
-      <c r="A197" s="4" t="s">
+      <c r="A197" s="3" t="s">
         <v>790</v>
       </c>
       <c r="B197" t="s">
@@ -8619,7 +8616,7 @@
       </c>
     </row>
     <row r="198" customHeight="1" spans="1:5">
-      <c r="A198" s="4" t="s">
+      <c r="A198" s="3" t="s">
         <v>794</v>
       </c>
       <c r="B198" t="s">
@@ -8636,7 +8633,7 @@
       </c>
     </row>
     <row r="199" customHeight="1" spans="1:5">
-      <c r="A199" s="4" t="s">
+      <c r="A199" s="3" t="s">
         <v>799</v>
       </c>
       <c r="B199" t="s">
@@ -8653,7 +8650,7 @@
       </c>
     </row>
     <row r="200" customHeight="1" spans="1:5">
-      <c r="A200" s="4" t="s">
+      <c r="A200" s="3" t="s">
         <v>803</v>
       </c>
       <c r="B200" t="s">
@@ -8670,7 +8667,7 @@
       </c>
     </row>
     <row r="201" customHeight="1" spans="1:5">
-      <c r="A201" s="4" t="s">
+      <c r="A201" s="3" t="s">
         <v>807</v>
       </c>
       <c r="B201" t="s">
@@ -8687,7 +8684,7 @@
       </c>
     </row>
     <row r="202" customHeight="1" spans="1:5">
-      <c r="A202" s="4" t="s">
+      <c r="A202" s="3" t="s">
         <v>811</v>
       </c>
       <c r="B202" t="s">
@@ -8704,7 +8701,7 @@
       </c>
     </row>
     <row r="203" customHeight="1" spans="1:5">
-      <c r="A203" s="4" t="s">
+      <c r="A203" s="3" t="s">
         <v>815</v>
       </c>
       <c r="B203" t="s">
@@ -8721,7 +8718,7 @@
       </c>
     </row>
     <row r="204" customHeight="1" spans="1:5">
-      <c r="A204" s="4" t="s">
+      <c r="A204" s="3" t="s">
         <v>819</v>
       </c>
       <c r="B204" t="s">
@@ -8738,7 +8735,7 @@
       </c>
     </row>
     <row r="205" customHeight="1" spans="1:5">
-      <c r="A205" s="4" t="s">
+      <c r="A205" s="3" t="s">
         <v>823</v>
       </c>
       <c r="B205" t="s">
@@ -8755,7 +8752,7 @@
       </c>
     </row>
     <row r="206" customHeight="1" spans="1:5">
-      <c r="A206" s="4" t="s">
+      <c r="A206" s="3" t="s">
         <v>827</v>
       </c>
       <c r="B206" t="s">
@@ -8772,7 +8769,7 @@
       </c>
     </row>
     <row r="207" customHeight="1" spans="1:5">
-      <c r="A207" s="4" t="s">
+      <c r="A207" s="3" t="s">
         <v>831</v>
       </c>
       <c r="B207" t="s">
@@ -8789,7 +8786,7 @@
       </c>
     </row>
     <row r="208" customHeight="1" spans="1:5">
-      <c r="A208" s="4" t="s">
+      <c r="A208" s="3" t="s">
         <v>835</v>
       </c>
       <c r="B208" t="s">
@@ -8806,7 +8803,7 @@
       </c>
     </row>
     <row r="209" customHeight="1" spans="1:5">
-      <c r="A209" s="4" t="s">
+      <c r="A209" s="3" t="s">
         <v>839</v>
       </c>
       <c r="B209" t="s">
@@ -8823,7 +8820,7 @@
       </c>
     </row>
     <row r="210" customHeight="1" spans="1:5">
-      <c r="A210" s="4" t="s">
+      <c r="A210" s="3" t="s">
         <v>843</v>
       </c>
       <c r="B210" t="s">
@@ -8840,7 +8837,7 @@
       </c>
     </row>
     <row r="211" customHeight="1" spans="1:5">
-      <c r="A211" s="4" t="s">
+      <c r="A211" s="3" t="s">
         <v>847</v>
       </c>
       <c r="B211" t="s">
@@ -8857,7 +8854,7 @@
       </c>
     </row>
     <row r="212" customHeight="1" spans="1:5">
-      <c r="A212" s="4" t="s">
+      <c r="A212" s="3" t="s">
         <v>851</v>
       </c>
       <c r="B212" t="s">
@@ -8874,7 +8871,7 @@
       </c>
     </row>
     <row r="213" customHeight="1" spans="1:5">
-      <c r="A213" s="4" t="s">
+      <c r="A213" s="3" t="s">
         <v>855</v>
       </c>
       <c r="B213" t="s">
@@ -8891,7 +8888,7 @@
       </c>
     </row>
     <row r="214" customHeight="1" spans="1:5">
-      <c r="A214" s="4" t="s">
+      <c r="A214" s="3" t="s">
         <v>859</v>
       </c>
       <c r="B214" t="s">
@@ -8908,7 +8905,7 @@
       </c>
     </row>
     <row r="215" customHeight="1" spans="1:5">
-      <c r="A215" s="4" t="s">
+      <c r="A215" s="3" t="s">
         <v>863</v>
       </c>
       <c r="B215" t="s">
@@ -8925,7 +8922,7 @@
       </c>
     </row>
     <row r="216" customHeight="1" spans="1:5">
-      <c r="A216" s="4" t="s">
+      <c r="A216" s="3" t="s">
         <v>867</v>
       </c>
       <c r="B216" t="s">
@@ -8942,7 +8939,7 @@
       </c>
     </row>
     <row r="217" customHeight="1" spans="1:5">
-      <c r="A217" s="4" t="s">
+      <c r="A217" s="3" t="s">
         <v>871</v>
       </c>
       <c r="B217" t="s">
@@ -8959,7 +8956,7 @@
       </c>
     </row>
     <row r="218" customHeight="1" spans="1:5">
-      <c r="A218" s="4" t="s">
+      <c r="A218" s="3" t="s">
         <v>875</v>
       </c>
       <c r="B218" t="s">
@@ -8976,7 +8973,7 @@
       </c>
     </row>
     <row r="219" customHeight="1" spans="1:5">
-      <c r="A219" s="4" t="s">
+      <c r="A219" s="3" t="s">
         <v>880</v>
       </c>
       <c r="B219" t="s">
@@ -8993,7 +8990,7 @@
       </c>
     </row>
     <row r="220" customHeight="1" spans="1:5">
-      <c r="A220" s="4" t="s">
+      <c r="A220" s="3" t="s">
         <v>884</v>
       </c>
       <c r="B220" t="s">
@@ -9010,7 +9007,7 @@
       </c>
     </row>
     <row r="221" customHeight="1" spans="1:5">
-      <c r="A221" s="4" t="s">
+      <c r="A221" s="3" t="s">
         <v>888</v>
       </c>
       <c r="B221" t="s">
@@ -9027,7 +9024,7 @@
       </c>
     </row>
     <row r="222" customHeight="1" spans="1:5">
-      <c r="A222" s="4" t="s">
+      <c r="A222" s="3" t="s">
         <v>892</v>
       </c>
       <c r="B222" t="s">
@@ -9044,7 +9041,7 @@
       </c>
     </row>
     <row r="223" customHeight="1" spans="1:5">
-      <c r="A223" s="4" t="s">
+      <c r="A223" s="3" t="s">
         <v>896</v>
       </c>
       <c r="B223" t="s">
@@ -9061,7 +9058,7 @@
       </c>
     </row>
     <row r="224" customHeight="1" spans="1:5">
-      <c r="A224" s="4" t="s">
+      <c r="A224" s="3" t="s">
         <v>900</v>
       </c>
       <c r="B224" t="s">
@@ -9078,7 +9075,7 @@
       </c>
     </row>
     <row r="225" customHeight="1" spans="1:5">
-      <c r="A225" s="4" t="s">
+      <c r="A225" s="3" t="s">
         <v>904</v>
       </c>
       <c r="B225" t="s">
@@ -9095,7 +9092,7 @@
       </c>
     </row>
     <row r="226" customHeight="1" spans="1:5">
-      <c r="A226" s="4" t="s">
+      <c r="A226" s="3" t="s">
         <v>909</v>
       </c>
       <c r="B226" t="s">
@@ -9112,7 +9109,7 @@
       </c>
     </row>
     <row r="227" customHeight="1" spans="1:5">
-      <c r="A227" s="4" t="s">
+      <c r="A227" s="3" t="s">
         <v>913</v>
       </c>
       <c r="B227" t="s">
@@ -9129,7 +9126,7 @@
       </c>
     </row>
     <row r="228" customHeight="1" spans="1:5">
-      <c r="A228" s="4" t="s">
+      <c r="A228" s="3" t="s">
         <v>918</v>
       </c>
       <c r="B228" t="s">
@@ -9146,7 +9143,7 @@
       </c>
     </row>
     <row r="229" customHeight="1" spans="1:5">
-      <c r="A229" s="4" t="s">
+      <c r="A229" s="3" t="s">
         <v>923</v>
       </c>
       <c r="B229" t="s">
@@ -9163,7 +9160,7 @@
       </c>
     </row>
     <row r="230" customHeight="1" spans="1:5">
-      <c r="A230" s="4" t="s">
+      <c r="A230" s="3" t="s">
         <v>927</v>
       </c>
       <c r="B230" t="s">
@@ -9180,7 +9177,7 @@
       </c>
     </row>
     <row r="231" customHeight="1" spans="1:5">
-      <c r="A231" s="4" t="s">
+      <c r="A231" s="3" t="s">
         <v>931</v>
       </c>
       <c r="B231" t="s">
@@ -9197,7 +9194,7 @@
       </c>
     </row>
     <row r="232" customHeight="1" spans="1:5">
-      <c r="A232" s="4" t="s">
+      <c r="A232" s="3" t="s">
         <v>935</v>
       </c>
       <c r="B232" t="s">
@@ -9214,7 +9211,7 @@
       </c>
     </row>
     <row r="233" customHeight="1" spans="1:5">
-      <c r="A233" s="4" t="s">
+      <c r="A233" s="3" t="s">
         <v>939</v>
       </c>
       <c r="B233" t="s">
@@ -9231,7 +9228,7 @@
       </c>
     </row>
     <row r="234" customHeight="1" spans="1:5">
-      <c r="A234" s="4" t="s">
+      <c r="A234" s="3" t="s">
         <v>943</v>
       </c>
       <c r="B234" t="s">
@@ -9248,7 +9245,7 @@
       </c>
     </row>
     <row r="235" customHeight="1" spans="1:5">
-      <c r="A235" s="4" t="s">
+      <c r="A235" s="3" t="s">
         <v>947</v>
       </c>
       <c r="B235" t="s">
@@ -9265,7 +9262,7 @@
       </c>
     </row>
     <row r="236" customHeight="1" spans="1:5">
-      <c r="A236" s="4" t="s">
+      <c r="A236" s="3" t="s">
         <v>951</v>
       </c>
       <c r="B236" t="s">
@@ -9282,7 +9279,7 @@
       </c>
     </row>
     <row r="237" customHeight="1" spans="1:5">
-      <c r="A237" s="4" t="s">
+      <c r="A237" s="3" t="s">
         <v>955</v>
       </c>
       <c r="B237" t="s">
@@ -9299,7 +9296,7 @@
       </c>
     </row>
     <row r="238" customHeight="1" spans="1:5">
-      <c r="A238" s="4" t="s">
+      <c r="A238" s="3" t="s">
         <v>959</v>
       </c>
       <c r="B238" t="s">
@@ -9316,7 +9313,7 @@
       </c>
     </row>
     <row r="239" customHeight="1" spans="1:5">
-      <c r="A239" s="4" t="s">
+      <c r="A239" s="3" t="s">
         <v>963</v>
       </c>
       <c r="B239" t="s">
@@ -9333,7 +9330,7 @@
       </c>
     </row>
     <row r="240" customHeight="1" spans="1:5">
-      <c r="A240" s="4" t="s">
+      <c r="A240" s="3" t="s">
         <v>967</v>
       </c>
       <c r="B240" t="s">
@@ -9350,7 +9347,7 @@
       </c>
     </row>
     <row r="241" customHeight="1" spans="1:5">
-      <c r="A241" s="4" t="s">
+      <c r="A241" s="3" t="s">
         <v>971</v>
       </c>
       <c r="B241" t="s">
@@ -9367,7 +9364,7 @@
       </c>
     </row>
     <row r="242" customHeight="1" spans="1:5">
-      <c r="A242" s="4" t="s">
+      <c r="A242" s="3" t="s">
         <v>975</v>
       </c>
       <c r="B242" t="s">
@@ -9384,7 +9381,7 @@
       </c>
     </row>
     <row r="243" customHeight="1" spans="1:5">
-      <c r="A243" s="4" t="s">
+      <c r="A243" s="3" t="s">
         <v>979</v>
       </c>
       <c r="B243" t="s">
@@ -9401,7 +9398,7 @@
       </c>
     </row>
     <row r="244" customHeight="1" spans="1:5">
-      <c r="A244" s="4" t="s">
+      <c r="A244" s="3" t="s">
         <v>983</v>
       </c>
       <c r="B244" t="s">
@@ -9418,7 +9415,7 @@
       </c>
     </row>
     <row r="245" customHeight="1" spans="1:5">
-      <c r="A245" s="4" t="s">
+      <c r="A245" s="3" t="s">
         <v>987</v>
       </c>
       <c r="B245" t="s">
@@ -9435,7 +9432,7 @@
       </c>
     </row>
     <row r="246" customHeight="1" spans="1:5">
-      <c r="A246" s="4" t="s">
+      <c r="A246" s="3" t="s">
         <v>992</v>
       </c>
       <c r="B246" t="s">
@@ -9452,7 +9449,7 @@
       </c>
     </row>
     <row r="247" customHeight="1" spans="1:5">
-      <c r="A247" s="4" t="s">
+      <c r="A247" s="3" t="s">
         <v>997</v>
       </c>
       <c r="B247" t="s">
@@ -9469,7 +9466,7 @@
       </c>
     </row>
     <row r="248" customHeight="1" spans="1:5">
-      <c r="A248" s="4" t="s">
+      <c r="A248" s="3" t="s">
         <v>1001</v>
       </c>
       <c r="B248" t="s">
@@ -9486,7 +9483,7 @@
       </c>
     </row>
     <row r="249" customHeight="1" spans="1:5">
-      <c r="A249" s="4" t="s">
+      <c r="A249" s="3" t="s">
         <v>1005</v>
       </c>
       <c r="B249" t="s">
@@ -9503,7 +9500,7 @@
       </c>
     </row>
     <row r="250" customHeight="1" spans="1:5">
-      <c r="A250" s="4" t="s">
+      <c r="A250" s="3" t="s">
         <v>1009</v>
       </c>
       <c r="B250" t="s">
@@ -9520,7 +9517,7 @@
       </c>
     </row>
     <row r="251" customHeight="1" spans="1:5">
-      <c r="A251" s="4" t="s">
+      <c r="A251" s="3" t="s">
         <v>1013</v>
       </c>
       <c r="B251" t="s">
@@ -9537,7 +9534,7 @@
       </c>
     </row>
     <row r="252" customHeight="1" spans="1:5">
-      <c r="A252" s="4" t="s">
+      <c r="A252" s="3" t="s">
         <v>1017</v>
       </c>
       <c r="B252" t="s">
@@ -9554,7 +9551,7 @@
       </c>
     </row>
     <row r="253" customHeight="1" spans="1:5">
-      <c r="A253" s="4" t="s">
+      <c r="A253" s="3" t="s">
         <v>1021</v>
       </c>
       <c r="B253" t="s">
@@ -9571,7 +9568,7 @@
       </c>
     </row>
     <row r="254" customHeight="1" spans="1:5">
-      <c r="A254" s="4" t="s">
+      <c r="A254" s="3" t="s">
         <v>1025</v>
       </c>
       <c r="B254" t="s">
@@ -9588,7 +9585,7 @@
       </c>
     </row>
     <row r="255" customHeight="1" spans="1:5">
-      <c r="A255" s="4" t="s">
+      <c r="A255" s="3" t="s">
         <v>1029</v>
       </c>
       <c r="B255" t="s">
@@ -9605,7 +9602,7 @@
       </c>
     </row>
     <row r="256" customHeight="1" spans="1:5">
-      <c r="A256" s="4" t="s">
+      <c r="A256" s="3" t="s">
         <v>1033</v>
       </c>
       <c r="B256" t="s">
@@ -9622,7 +9619,7 @@
       </c>
     </row>
     <row r="257" customHeight="1" spans="1:5">
-      <c r="A257" s="4" t="s">
+      <c r="A257" s="3" t="s">
         <v>1038</v>
       </c>
       <c r="B257" t="s">
@@ -9639,7 +9636,7 @@
       </c>
     </row>
     <row r="258" customHeight="1" spans="1:5">
-      <c r="A258" s="4" t="s">
+      <c r="A258" s="3" t="s">
         <v>1042</v>
       </c>
       <c r="B258" t="s">
@@ -9656,7 +9653,7 @@
       </c>
     </row>
     <row r="259" customHeight="1" spans="1:5">
-      <c r="A259" s="4" t="s">
+      <c r="A259" s="3" t="s">
         <v>1046</v>
       </c>
       <c r="B259" t="s">
@@ -9673,7 +9670,7 @@
       </c>
     </row>
     <row r="260" customHeight="1" spans="1:5">
-      <c r="A260" s="4" t="s">
+      <c r="A260" s="3" t="s">
         <v>1050</v>
       </c>
       <c r="B260" t="s">
@@ -9690,7 +9687,7 @@
       </c>
     </row>
     <row r="261" customHeight="1" spans="1:5">
-      <c r="A261" s="4" t="s">
+      <c r="A261" s="3" t="s">
         <v>1054</v>
       </c>
       <c r="B261" t="s">
@@ -9707,7 +9704,7 @@
       </c>
     </row>
     <row r="262" customHeight="1" spans="1:5">
-      <c r="A262" s="4" t="s">
+      <c r="A262" s="3" t="s">
         <v>1058</v>
       </c>
       <c r="B262" t="s">
@@ -9724,7 +9721,7 @@
       </c>
     </row>
     <row r="263" customHeight="1" spans="1:5">
-      <c r="A263" s="4" t="s">
+      <c r="A263" s="3" t="s">
         <v>1062</v>
       </c>
       <c r="B263" t="s">
@@ -9741,7 +9738,7 @@
       </c>
     </row>
     <row r="264" customHeight="1" spans="1:5">
-      <c r="A264" s="4" t="s">
+      <c r="A264" s="3" t="s">
         <v>1066</v>
       </c>
       <c r="B264" t="s">
@@ -9758,7 +9755,7 @@
       </c>
     </row>
     <row r="265" customHeight="1" spans="1:5">
-      <c r="A265" s="4" t="s">
+      <c r="A265" s="3" t="s">
         <v>1070</v>
       </c>
       <c r="B265" t="s">
@@ -9775,7 +9772,7 @@
       </c>
     </row>
     <row r="266" customHeight="1" spans="1:5">
-      <c r="A266" s="4" t="s">
+      <c r="A266" s="3" t="s">
         <v>1074</v>
       </c>
       <c r="B266" t="s">
@@ -9792,7 +9789,7 @@
       </c>
     </row>
     <row r="267" customHeight="1" spans="1:5">
-      <c r="A267" s="4" t="s">
+      <c r="A267" s="3" t="s">
         <v>1078</v>
       </c>
       <c r="B267" t="s">
@@ -9809,7 +9806,7 @@
       </c>
     </row>
     <row r="268" customHeight="1" spans="1:5">
-      <c r="A268" s="4" t="s">
+      <c r="A268" s="3" t="s">
         <v>1082</v>
       </c>
       <c r="B268" t="s">
@@ -9826,7 +9823,7 @@
       </c>
     </row>
     <row r="269" customHeight="1" spans="1:5">
-      <c r="A269" s="4" t="s">
+      <c r="A269" s="3" t="s">
         <v>1087</v>
       </c>
       <c r="B269" t="s">
@@ -9843,7 +9840,7 @@
       </c>
     </row>
     <row r="270" customHeight="1" spans="1:5">
-      <c r="A270" s="4" t="s">
+      <c r="A270" s="3" t="s">
         <v>1092</v>
       </c>
       <c r="B270" t="s">
@@ -9860,7 +9857,7 @@
       </c>
     </row>
     <row r="271" customHeight="1" spans="1:5">
-      <c r="A271" s="4" t="s">
+      <c r="A271" s="3" t="s">
         <v>1097</v>
       </c>
       <c r="B271" t="s">
@@ -9877,7 +9874,7 @@
       </c>
     </row>
     <row r="272" customHeight="1" spans="1:5">
-      <c r="A272" s="4" t="s">
+      <c r="A272" s="3" t="s">
         <v>1101</v>
       </c>
       <c r="B272" t="s">
@@ -9894,7 +9891,7 @@
       </c>
     </row>
     <row r="273" customHeight="1" spans="1:5">
-      <c r="A273" s="4" t="s">
+      <c r="A273" s="3" t="s">
         <v>1105</v>
       </c>
       <c r="B273" t="s">
@@ -9911,7 +9908,7 @@
       </c>
     </row>
     <row r="274" customHeight="1" spans="1:5">
-      <c r="A274" s="4" t="s">
+      <c r="A274" s="3" t="s">
         <v>1109</v>
       </c>
       <c r="B274" t="s">
@@ -9928,7 +9925,7 @@
       </c>
     </row>
     <row r="275" customHeight="1" spans="1:5">
-      <c r="A275" s="4" t="s">
+      <c r="A275" s="3" t="s">
         <v>1113</v>
       </c>
       <c r="B275" t="s">
@@ -9945,7 +9942,7 @@
       </c>
     </row>
     <row r="276" customHeight="1" spans="1:5">
-      <c r="A276" s="4" t="s">
+      <c r="A276" s="3" t="s">
         <v>1117</v>
       </c>
       <c r="B276" t="s">
@@ -9962,7 +9959,7 @@
       </c>
     </row>
     <row r="277" customHeight="1" spans="1:5">
-      <c r="A277" s="4" t="s">
+      <c r="A277" s="3" t="s">
         <v>1121</v>
       </c>
       <c r="B277" t="s">
@@ -9979,7 +9976,7 @@
       </c>
     </row>
     <row r="278" customHeight="1" spans="1:5">
-      <c r="A278" s="4" t="s">
+      <c r="A278" s="3" t="s">
         <v>1125</v>
       </c>
       <c r="B278" t="s">
@@ -9996,7 +9993,7 @@
       </c>
     </row>
     <row r="279" customHeight="1" spans="1:5">
-      <c r="A279" s="4" t="s">
+      <c r="A279" s="3" t="s">
         <v>1129</v>
       </c>
       <c r="B279" t="s">
@@ -10013,7 +10010,7 @@
       </c>
     </row>
     <row r="280" customHeight="1" spans="1:5">
-      <c r="A280" s="4" t="s">
+      <c r="A280" s="3" t="s">
         <v>1133</v>
       </c>
       <c r="B280" t="s">
@@ -10030,7 +10027,7 @@
       </c>
     </row>
     <row r="281" customHeight="1" spans="1:5">
-      <c r="A281" s="4" t="s">
+      <c r="A281" s="3" t="s">
         <v>1137</v>
       </c>
       <c r="B281" t="s">
@@ -10047,7 +10044,7 @@
       </c>
     </row>
     <row r="282" customHeight="1" spans="1:5">
-      <c r="A282" s="4" t="s">
+      <c r="A282" s="3" t="s">
         <v>1141</v>
       </c>
       <c r="B282" t="s">
@@ -10064,7 +10061,7 @@
       </c>
     </row>
     <row r="283" customHeight="1" spans="1:5">
-      <c r="A283" s="4" t="s">
+      <c r="A283" s="3" t="s">
         <v>1146</v>
       </c>
       <c r="B283" t="s">
@@ -10081,7 +10078,7 @@
       </c>
     </row>
     <row r="284" customHeight="1" spans="1:5">
-      <c r="A284" s="4" t="s">
+      <c r="A284" s="3" t="s">
         <v>1150</v>
       </c>
       <c r="B284" t="s">
@@ -10098,7 +10095,7 @@
       </c>
     </row>
     <row r="285" customHeight="1" spans="1:5">
-      <c r="A285" s="4" t="s">
+      <c r="A285" s="3" t="s">
         <v>1155</v>
       </c>
       <c r="B285" t="s">
@@ -10115,7 +10112,7 @@
       </c>
     </row>
     <row r="286" customHeight="1" spans="1:5">
-      <c r="A286" s="4" t="s">
+      <c r="A286" s="3" t="s">
         <v>1160</v>
       </c>
       <c r="B286" t="s">
@@ -10132,7 +10129,7 @@
       </c>
     </row>
     <row r="287" customHeight="1" spans="1:5">
-      <c r="A287" s="4" t="s">
+      <c r="A287" s="3" t="s">
         <v>1164</v>
       </c>
       <c r="B287" t="s">
@@ -10149,7 +10146,7 @@
       </c>
     </row>
     <row r="288" customHeight="1" spans="1:5">
-      <c r="A288" s="4" t="s">
+      <c r="A288" s="3" t="s">
         <v>1169</v>
       </c>
       <c r="B288" t="s">
@@ -10166,7 +10163,7 @@
       </c>
     </row>
     <row r="289" customHeight="1" spans="1:5">
-      <c r="A289" s="4" t="s">
+      <c r="A289" s="3" t="s">
         <v>1173</v>
       </c>
       <c r="B289" t="s">
@@ -10183,7 +10180,7 @@
       </c>
     </row>
     <row r="290" customHeight="1" spans="1:5">
-      <c r="A290" s="4" t="s">
+      <c r="A290" s="3" t="s">
         <v>1178</v>
       </c>
       <c r="B290" t="s">
@@ -10200,7 +10197,7 @@
       </c>
     </row>
     <row r="291" customHeight="1" spans="1:5">
-      <c r="A291" s="4" t="s">
+      <c r="A291" s="3" t="s">
         <v>1182</v>
       </c>
       <c r="B291" t="s">
@@ -10217,7 +10214,7 @@
       </c>
     </row>
     <row r="292" customHeight="1" spans="1:5">
-      <c r="A292" s="4" t="s">
+      <c r="A292" s="3" t="s">
         <v>1186</v>
       </c>
       <c r="B292" t="s">
@@ -10234,7 +10231,7 @@
       </c>
     </row>
     <row r="293" customHeight="1" spans="1:5">
-      <c r="A293" s="4" t="s">
+      <c r="A293" s="3" t="s">
         <v>1190</v>
       </c>
       <c r="B293" t="s">
@@ -10251,7 +10248,7 @@
       </c>
     </row>
     <row r="294" customHeight="1" spans="1:5">
-      <c r="A294" s="4" t="s">
+      <c r="A294" s="3" t="s">
         <v>1195</v>
       </c>
       <c r="B294" t="s">
@@ -10268,7 +10265,7 @@
       </c>
     </row>
     <row r="295" customHeight="1" spans="1:5">
-      <c r="A295" s="4" t="s">
+      <c r="A295" s="3" t="s">
         <v>1199</v>
       </c>
       <c r="B295" t="s">
@@ -10285,7 +10282,7 @@
       </c>
     </row>
     <row r="296" customHeight="1" spans="1:5">
-      <c r="A296" s="4" t="s">
+      <c r="A296" s="3" t="s">
         <v>1203</v>
       </c>
       <c r="B296" t="s">
@@ -10302,7 +10299,7 @@
       </c>
     </row>
     <row r="297" customHeight="1" spans="1:5">
-      <c r="A297" s="4" t="s">
+      <c r="A297" s="3" t="s">
         <v>1207</v>
       </c>
       <c r="B297" t="s">
@@ -10319,7 +10316,7 @@
       </c>
     </row>
     <row r="298" customHeight="1" spans="1:5">
-      <c r="A298" s="4" t="s">
+      <c r="A298" s="3" t="s">
         <v>1211</v>
       </c>
       <c r="B298" t="s">
@@ -10336,7 +10333,7 @@
       </c>
     </row>
     <row r="299" customHeight="1" spans="1:5">
-      <c r="A299" s="4" t="s">
+      <c r="A299" s="3" t="s">
         <v>1215</v>
       </c>
       <c r="B299" t="s">
@@ -10353,7 +10350,7 @@
       </c>
     </row>
     <row r="300" customHeight="1" spans="1:5">
-      <c r="A300" s="4" t="s">
+      <c r="A300" s="3" t="s">
         <v>1219</v>
       </c>
       <c r="B300" t="s">
@@ -10370,7 +10367,7 @@
       </c>
     </row>
     <row r="301" customHeight="1" spans="1:5">
-      <c r="A301" s="4" t="s">
+      <c r="A301" s="3" t="s">
         <v>1222</v>
       </c>
       <c r="B301" t="s">
@@ -10387,7 +10384,7 @@
       </c>
     </row>
     <row r="302" customHeight="1" spans="1:5">
-      <c r="A302" s="4" t="s">
+      <c r="A302" s="3" t="s">
         <v>1225</v>
       </c>
       <c r="B302" t="s">
@@ -10404,7 +10401,7 @@
       </c>
     </row>
     <row r="303" customHeight="1" spans="1:5">
-      <c r="A303" s="4" t="s">
+      <c r="A303" s="3" t="s">
         <v>1228</v>
       </c>
       <c r="B303" t="s">
@@ -10421,7 +10418,7 @@
       </c>
     </row>
     <row r="304" customHeight="1" spans="1:5">
-      <c r="A304" s="4" t="s">
+      <c r="A304" s="3" t="s">
         <v>1231</v>
       </c>
       <c r="B304" t="s">
@@ -10438,7 +10435,7 @@
       </c>
     </row>
     <row r="305" customHeight="1" spans="1:5">
-      <c r="A305" s="4" t="s">
+      <c r="A305" s="3" t="s">
         <v>1234</v>
       </c>
       <c r="B305" t="s">
@@ -10455,7 +10452,7 @@
       </c>
     </row>
     <row r="306" customHeight="1" spans="1:5">
-      <c r="A306" s="4" t="s">
+      <c r="A306" s="3" t="s">
         <v>1237</v>
       </c>
       <c r="B306" t="s">
@@ -10472,7 +10469,7 @@
       </c>
     </row>
     <row r="307" customHeight="1" spans="1:5">
-      <c r="A307" s="4" t="s">
+      <c r="A307" s="3" t="s">
         <v>1240</v>
       </c>
       <c r="B307" t="s">
@@ -10489,7 +10486,7 @@
       </c>
     </row>
     <row r="308" customHeight="1" spans="1:5">
-      <c r="A308" s="4" t="s">
+      <c r="A308" s="3" t="s">
         <v>1243</v>
       </c>
       <c r="B308" t="s">
@@ -10506,7 +10503,7 @@
       </c>
     </row>
     <row r="309" customHeight="1" spans="1:5">
-      <c r="A309" s="4" t="s">
+      <c r="A309" s="3" t="s">
         <v>1246</v>
       </c>
       <c r="B309" t="s">
@@ -10523,7 +10520,7 @@
       </c>
     </row>
     <row r="310" customHeight="1" spans="1:5">
-      <c r="A310" s="4" t="s">
+      <c r="A310" s="3" t="s">
         <v>1249</v>
       </c>
       <c r="B310" t="s">
@@ -10540,7 +10537,7 @@
       </c>
     </row>
     <row r="311" customHeight="1" spans="1:5">
-      <c r="A311" s="4" t="s">
+      <c r="A311" s="3" t="s">
         <v>1252</v>
       </c>
       <c r="B311" t="s">
@@ -10557,7 +10554,7 @@
       </c>
     </row>
     <row r="312" customHeight="1" spans="1:5">
-      <c r="A312" s="4" t="s">
+      <c r="A312" s="3" t="s">
         <v>1255</v>
       </c>
       <c r="B312" t="s">
@@ -10574,7 +10571,7 @@
       </c>
     </row>
     <row r="313" customHeight="1" spans="1:5">
-      <c r="A313" s="4" t="s">
+      <c r="A313" s="3" t="s">
         <v>1258</v>
       </c>
       <c r="B313" t="s">
@@ -10591,7 +10588,7 @@
       </c>
     </row>
     <row r="314" customHeight="1" spans="1:5">
-      <c r="A314" s="4" t="s">
+      <c r="A314" s="3" t="s">
         <v>1261</v>
       </c>
       <c r="B314" t="s">
@@ -10608,7 +10605,7 @@
       </c>
     </row>
     <row r="315" customHeight="1" spans="1:5">
-      <c r="A315" s="4" t="s">
+      <c r="A315" s="3" t="s">
         <v>1264</v>
       </c>
       <c r="B315" t="s">
@@ -10625,7 +10622,7 @@
       </c>
     </row>
     <row r="316" customHeight="1" spans="1:5">
-      <c r="A316" s="4" t="s">
+      <c r="A316" s="3" t="s">
         <v>1267</v>
       </c>
       <c r="B316" t="s">
@@ -10642,7 +10639,7 @@
       </c>
     </row>
     <row r="317" customHeight="1" spans="1:5">
-      <c r="A317" s="4" t="s">
+      <c r="A317" s="3" t="s">
         <v>1270</v>
       </c>
       <c r="B317" t="s">
@@ -10659,7 +10656,7 @@
       </c>
     </row>
     <row r="318" customHeight="1" spans="1:5">
-      <c r="A318" s="4" t="s">
+      <c r="A318" s="3" t="s">
         <v>1273</v>
       </c>
       <c r="B318" t="s">
@@ -10676,7 +10673,7 @@
       </c>
     </row>
     <row r="319" customHeight="1" spans="1:5">
-      <c r="A319" s="4" t="s">
+      <c r="A319" s="3" t="s">
         <v>1276</v>
       </c>
       <c r="B319" t="s">
@@ -10693,7 +10690,7 @@
       </c>
     </row>
     <row r="320" customHeight="1" spans="1:5">
-      <c r="A320" s="4" t="s">
+      <c r="A320" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="B320" t="s">
@@ -10710,7 +10707,7 @@
       </c>
     </row>
     <row r="321" customHeight="1" spans="1:5">
-      <c r="A321" s="4" t="s">
+      <c r="A321" s="3" t="s">
         <v>1282</v>
       </c>
       <c r="B321" t="s">
@@ -10727,7 +10724,7 @@
       </c>
     </row>
     <row r="322" customHeight="1" spans="1:5">
-      <c r="A322" s="4" t="s">
+      <c r="A322" s="3" t="s">
         <v>1285</v>
       </c>
       <c r="B322" t="s">
@@ -10744,7 +10741,7 @@
       </c>
     </row>
     <row r="323" customHeight="1" spans="1:5">
-      <c r="A323" s="4" t="s">
+      <c r="A323" s="3" t="s">
         <v>1288</v>
       </c>
       <c r="B323" t="s">
@@ -10761,7 +10758,7 @@
       </c>
     </row>
     <row r="324" customHeight="1" spans="1:5">
-      <c r="A324" s="4" t="s">
+      <c r="A324" s="3" t="s">
         <v>1291</v>
       </c>
       <c r="B324" t="s">
@@ -10778,7 +10775,7 @@
       </c>
     </row>
     <row r="325" customHeight="1" spans="1:5">
-      <c r="A325" s="4" t="s">
+      <c r="A325" s="3" t="s">
         <v>1294</v>
       </c>
       <c r="B325" t="s">
@@ -10795,7 +10792,7 @@
       </c>
     </row>
     <row r="326" customHeight="1" spans="1:5">
-      <c r="A326" s="4" t="s">
+      <c r="A326" s="3" t="s">
         <v>1297</v>
       </c>
       <c r="B326" t="s">
@@ -10812,7 +10809,7 @@
       </c>
     </row>
     <row r="327" customHeight="1" spans="1:5">
-      <c r="A327" s="4" t="s">
+      <c r="A327" s="3" t="s">
         <v>1300</v>
       </c>
       <c r="B327" t="s">
@@ -10829,7 +10826,7 @@
       </c>
     </row>
     <row r="328" customHeight="1" spans="1:5">
-      <c r="A328" s="4" t="s">
+      <c r="A328" s="3" t="s">
         <v>1303</v>
       </c>
       <c r="B328" t="s">
@@ -10846,7 +10843,7 @@
       </c>
     </row>
     <row r="329" customHeight="1" spans="1:5">
-      <c r="A329" s="4" t="s">
+      <c r="A329" s="3" t="s">
         <v>1306</v>
       </c>
       <c r="B329" t="s">
@@ -10863,7 +10860,7 @@
       </c>
     </row>
     <row r="330" customHeight="1" spans="1:5">
-      <c r="A330" s="4" t="s">
+      <c r="A330" s="3" t="s">
         <v>1309</v>
       </c>
       <c r="B330" t="s">
@@ -10880,7 +10877,7 @@
       </c>
     </row>
     <row r="331" customHeight="1" spans="1:5">
-      <c r="A331" s="4" t="s">
+      <c r="A331" s="3" t="s">
         <v>1312</v>
       </c>
       <c r="B331" t="s">
@@ -10897,7 +10894,7 @@
       </c>
     </row>
     <row r="332" customHeight="1" spans="1:5">
-      <c r="A332" s="4" t="s">
+      <c r="A332" s="3" t="s">
         <v>1315</v>
       </c>
       <c r="B332" t="s">
@@ -10914,7 +10911,7 @@
       </c>
     </row>
     <row r="333" customHeight="1" spans="1:5">
-      <c r="A333" s="4" t="s">
+      <c r="A333" s="3" t="s">
         <v>1318</v>
       </c>
       <c r="B333" t="s">
@@ -10931,7 +10928,7 @@
       </c>
     </row>
     <row r="334" customHeight="1" spans="1:5">
-      <c r="A334" s="4" t="s">
+      <c r="A334" s="3" t="s">
         <v>1321</v>
       </c>
       <c r="B334" t="s">
@@ -10948,7 +10945,7 @@
       </c>
     </row>
     <row r="335" customHeight="1" spans="1:5">
-      <c r="A335" s="4" t="s">
+      <c r="A335" s="3" t="s">
         <v>1324</v>
       </c>
       <c r="B335" t="s">
@@ -10965,7 +10962,7 @@
       </c>
     </row>
     <row r="336" customHeight="1" spans="1:5">
-      <c r="A336" s="4" t="s">
+      <c r="A336" s="3" t="s">
         <v>1327</v>
       </c>
       <c r="B336" t="s">
@@ -10982,7 +10979,7 @@
       </c>
     </row>
     <row r="337" customHeight="1" spans="1:5">
-      <c r="A337" s="4" t="s">
+      <c r="A337" s="3" t="s">
         <v>1330</v>
       </c>
       <c r="B337" t="s">
@@ -10999,7 +10996,7 @@
       </c>
     </row>
     <row r="338" customHeight="1" spans="1:5">
-      <c r="A338" s="4" t="s">
+      <c r="A338" s="3" t="s">
         <v>1333</v>
       </c>
       <c r="B338" t="s">
@@ -11016,7 +11013,7 @@
       </c>
     </row>
     <row r="339" customHeight="1" spans="1:5">
-      <c r="A339" s="4" t="s">
+      <c r="A339" s="3" t="s">
         <v>1336</v>
       </c>
       <c r="B339" t="s">
@@ -11033,7 +11030,7 @@
       </c>
     </row>
     <row r="340" customHeight="1" spans="1:5">
-      <c r="A340" s="4" t="s">
+      <c r="A340" s="3" t="s">
         <v>1339</v>
       </c>
       <c r="B340" t="s">
@@ -11050,7 +11047,7 @@
       </c>
     </row>
     <row r="341" customHeight="1" spans="1:5">
-      <c r="A341" s="4" t="s">
+      <c r="A341" s="3" t="s">
         <v>1342</v>
       </c>
       <c r="B341" t="s">
@@ -11067,7 +11064,7 @@
       </c>
     </row>
     <row r="342" customHeight="1" spans="1:5">
-      <c r="A342" s="4" t="s">
+      <c r="A342" s="3" t="s">
         <v>1345</v>
       </c>
       <c r="B342" t="s">
@@ -11084,7 +11081,7 @@
       </c>
     </row>
     <row r="343" customHeight="1" spans="1:5">
-      <c r="A343" s="4" t="s">
+      <c r="A343" s="3" t="s">
         <v>1348</v>
       </c>
       <c r="B343" t="s">
@@ -11101,7 +11098,7 @@
       </c>
     </row>
     <row r="344" customHeight="1" spans="1:5">
-      <c r="A344" s="4" t="s">
+      <c r="A344" s="3" t="s">
         <v>1351</v>
       </c>
       <c r="B344" t="s">
@@ -11118,7 +11115,7 @@
       </c>
     </row>
     <row r="345" customHeight="1" spans="1:5">
-      <c r="A345" s="4" t="s">
+      <c r="A345" s="3" t="s">
         <v>1354</v>
       </c>
       <c r="B345" t="s">
@@ -11135,7 +11132,7 @@
       </c>
     </row>
     <row r="346" customHeight="1" spans="1:5">
-      <c r="A346" s="4" t="s">
+      <c r="A346" s="3" t="s">
         <v>1357</v>
       </c>
       <c r="B346" t="s">
@@ -11152,7 +11149,7 @@
       </c>
     </row>
     <row r="347" customHeight="1" spans="1:5">
-      <c r="A347" s="4" t="s">
+      <c r="A347" s="3" t="s">
         <v>1360</v>
       </c>
       <c r="B347" t="s">
@@ -11169,7 +11166,7 @@
       </c>
     </row>
     <row r="348" customHeight="1" spans="1:5">
-      <c r="A348" s="4" t="s">
+      <c r="A348" s="3" t="s">
         <v>1363</v>
       </c>
       <c r="B348" t="s">
@@ -11186,7 +11183,7 @@
       </c>
     </row>
     <row r="349" customHeight="1" spans="1:5">
-      <c r="A349" s="4" t="s">
+      <c r="A349" s="3" t="s">
         <v>1366</v>
       </c>
       <c r="B349" t="s">
@@ -11203,7 +11200,7 @@
       </c>
     </row>
     <row r="350" customHeight="1" spans="1:5">
-      <c r="A350" s="4" t="s">
+      <c r="A350" s="3" t="s">
         <v>1369</v>
       </c>
       <c r="B350" t="s">
@@ -11220,7 +11217,7 @@
       </c>
     </row>
     <row r="351" customHeight="1" spans="1:5">
-      <c r="A351" s="4" t="s">
+      <c r="A351" s="3" t="s">
         <v>1372</v>
       </c>
       <c r="B351" t="s">
@@ -11237,7 +11234,7 @@
       </c>
     </row>
     <row r="352" customHeight="1" spans="1:5">
-      <c r="A352" s="4" t="s">
+      <c r="A352" s="3" t="s">
         <v>1375</v>
       </c>
       <c r="B352" t="s">
@@ -11277,7 +11274,7 @@
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>230</v>
       </c>
       <c r="X2" s="1" t="s">

--- a/SimonCani_glyphs.xlsx
+++ b/SimonCani_glyphs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26670" windowHeight="12765"/>
+    <workbookView windowWidth="12915" windowHeight="12765"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/SimonCani_glyphs.xlsx
+++ b/SimonCani_glyphs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12915" windowHeight="12765"/>
+    <workbookView windowWidth="26670" windowHeight="12765"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
